--- a/results/consolidated/Stress_Testing.xlsx
+++ b/results/consolidated/Stress_Testing.xlsx
@@ -2199,10 +2199,10 @@
         <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000193466076864602</v>
+        <v>0.000169877455158598</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0104256602740424</v>
+        <v>0.00984288750182562</v>
       </c>
       <c r="G2" t="n">
         <v>0.000181010224401328</v>
@@ -2211,7 +2211,7 @@
         <v>0.0101754695102639</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.88129773026386</v>
+        <v>6.15035381539929</v>
       </c>
       <c r="J2" t="n">
         <v>143</v>
@@ -2231,10 +2231,10 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000169425484974936</v>
+        <v>0.000168172289255699</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00979488622446878</v>
+        <v>0.0097582433333083</v>
       </c>
       <c r="G3" t="n">
         <v>0.000173084082239777</v>
@@ -2243,7 +2243,7 @@
         <v>0.00986452620090229</v>
       </c>
       <c r="I3" t="n">
-        <v>2.11376876342279</v>
+        <v>2.83780745203027</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2263,10 +2263,10 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000198798394368036</v>
+        <v>0.000186272688888849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0107681123773646</v>
+        <v>0.0101156799314045</v>
       </c>
       <c r="G4" t="n">
         <v>0.000186382694559611</v>
@@ -2275,7 +2275,7 @@
         <v>0.0103607114259397</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.66140160585282</v>
+        <v>0.0590213973572735</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2295,10 +2295,10 @@
         <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000158897306880347</v>
+        <v>0.0000391106811833536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00817413515243943</v>
+        <v>0.0046428961532884</v>
       </c>
       <c r="G5" t="n">
         <v>0.0000713100425525571</v>
@@ -2307,7 +2307,7 @@
         <v>0.00691952806751367</v>
       </c>
       <c r="I5" t="n">
-        <v>-122.825988027193</v>
+        <v>45.1540347146362</v>
       </c>
       <c r="J5" t="n">
         <v>59</v>
@@ -2327,10 +2327,10 @@
         <v>48</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000523438343597986</v>
+        <v>0.0000842948574186675</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00564241359788745</v>
+        <v>0.00627068068523909</v>
       </c>
       <c r="G6" t="n">
         <v>0.000121020868400151</v>
@@ -2339,7 +2339,7 @@
         <v>0.00828901839589263</v>
       </c>
       <c r="I6" t="n">
-        <v>56.7480922490774</v>
+        <v>30.3468413894123</v>
       </c>
       <c r="J6" t="n">
         <v>59</v>
@@ -2359,10 +2359,10 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000390604229152326</v>
+        <v>0.000038799377829785</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0047689201121424</v>
+        <v>0.00471193762349396</v>
       </c>
       <c r="G7" t="n">
         <v>0.0000455688503947384</v>
@@ -2371,7 +2371,7 @@
         <v>0.00539792332968993</v>
       </c>
       <c r="I7" t="n">
-        <v>14.282623816767</v>
+        <v>14.8554824322166</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2391,10 +2391,10 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000464292659016968</v>
+        <v>0.0000437411660469645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00523921061157367</v>
+        <v>0.00513783575080229</v>
       </c>
       <c r="G8" t="n">
         <v>0.00005021437716793</v>
@@ -2403,7 +2403,7 @@
         <v>0.00575846949939422</v>
       </c>
       <c r="I8" t="n">
-        <v>7.53790344461469</v>
+        <v>12.8911508736181</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2411,487 +2411,487 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000238581683572729</v>
+        <v>0.000100667806358764</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0116446228302278</v>
+        <v>0.00449189893642634</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000268794051743971</v>
+        <v>0.000140712503876815</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0126665192032668</v>
+        <v>0.00644545603954121</v>
       </c>
       <c r="I9" t="n">
-        <v>11.2399690302743</v>
+        <v>28.4585210374109</v>
       </c>
       <c r="J9" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000239797963023127</v>
+        <v>0.0000928480321311417</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0118100724216768</v>
+        <v>0.00366790601017871</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000277952200925356</v>
+        <v>0.000132085021288518</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0129521549551023</v>
+        <v>0.00605424925084791</v>
       </c>
       <c r="I10" t="n">
-        <v>13.7269062001332</v>
+        <v>29.7058582226895</v>
       </c>
       <c r="J10" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000259834047738169</v>
+        <v>0.0000999279350679915</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0122554825288964</v>
+        <v>0.0044814525737719</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000270698736847279</v>
+        <v>0.000138579116845906</v>
       </c>
       <c r="H11" t="n">
-        <v>0.012726673787497</v>
+        <v>0.00631687863580676</v>
       </c>
       <c r="I11" t="n">
-        <v>4.01357214874623</v>
+        <v>27.8910579441007</v>
       </c>
       <c r="J11" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000102230042513433</v>
+        <v>0.000220028781498017</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00793309736000618</v>
+        <v>0.00463939156179508</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000128900220381869</v>
+        <v>0.000260639563268616</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00892895322360497</v>
+        <v>0.00659294866490994</v>
       </c>
       <c r="I12" t="n">
-        <v>20.6905603337417</v>
+        <v>15.5812038898889</v>
       </c>
       <c r="J12" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>16615069116756601806484600262820600426680064442008044262626264442042</v>
+        <v>0.000213760586337385</v>
       </c>
       <c r="F13" t="n">
-        <v>530670652072916271166268404240040</v>
+        <v>0.00381539863554744</v>
       </c>
       <c r="G13" t="n">
-        <v>2544252433649152005028242606608002424082846284482680000644420468024</v>
+        <v>0.000252014571340813</v>
       </c>
       <c r="H13" t="n">
-        <v>207660595292609154788688088666846</v>
+        <v>0.00620174187621664</v>
       </c>
       <c r="I13" t="n">
-        <v>-553.043263200344</v>
+        <v>15.1792750712399</v>
       </c>
       <c r="J13" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000097487182849055</v>
+        <v>0.000219419824695114</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00741374138269694</v>
+        <v>0.00462894519914064</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000110318976936474</v>
+        <v>0.000258470368491299</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00804924149941966</v>
+        <v>0.00646437126117549</v>
       </c>
       <c r="I14" t="n">
-        <v>11.6315383298086</v>
+        <v>15.1083251918294</v>
       </c>
       <c r="J14" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000123386967173028</v>
+        <v>0.0000323057033516642</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00863570424856497</v>
+        <v>0.00427471571781723</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000118060464060201</v>
+        <v>0.0000715168405499028</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00843634518344065</v>
+        <v>0.0062282728209321</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.51167387425393</v>
+        <v>54.8278376068332</v>
       </c>
       <c r="J15" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000487978114862318</v>
+        <v>0.0000222012255000275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0155851181259128</v>
+        <v>0.00345072279156959</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000550054096063248</v>
+        <v>0.000062885690458495</v>
       </c>
       <c r="H16" t="n">
-        <v>0.016849816265974</v>
+        <v>0.0058370660322388</v>
       </c>
       <c r="I16" t="n">
-        <v>11.2854320411772</v>
+        <v>64.6959024570455</v>
       </c>
       <c r="J16" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000509855248883742</v>
+        <v>0.0000313730601865907</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0164319444074425</v>
+        <v>0.00426426935516279</v>
       </c>
       <c r="G17" t="n">
-        <v>0.000531996674448781</v>
+        <v>0.0000694361805051519</v>
       </c>
       <c r="H17" t="n">
-        <v>0.016530264480168</v>
+        <v>0.00609969541719765</v>
       </c>
       <c r="I17" t="n">
-        <v>4.16194811517958</v>
+        <v>54.8174165710873</v>
       </c>
       <c r="J17" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000559702439995254</v>
+        <v>0.0000324102033357809</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0177720146197229</v>
+        <v>0.00427877143726121</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005513104399593</v>
+        <v>0.0000716369065930292</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0168826766920618</v>
+        <v>0.00623232854037608</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.52219138759178</v>
+        <v>54.7576732760057</v>
       </c>
       <c r="J18" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000295513550777303</v>
+        <v>0.0000223483904606143</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0132668614433611</v>
+        <v>0.00345477851101357</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00028108105450633</v>
+        <v>0.0000630058249892503</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0128032922190265</v>
+        <v>0.00584112175168278</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.13463858185708</v>
+        <v>64.5296439425605</v>
       </c>
       <c r="J19" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000256669488959662</v>
+        <v>0.0000314811600282095</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0120457132953336</v>
+        <v>0.00426832507460677</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000267026517801658</v>
+        <v>0.000069555261914823</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0123546488861435</v>
+        <v>0.00610375113664163</v>
       </c>
       <c r="I20" t="n">
-        <v>3.87865180105016</v>
+        <v>54.7393552097306</v>
       </c>
       <c r="J20" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000371387209522612</v>
+        <v>0.000125943124770252</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0154132641829075</v>
+        <v>0.0100064308539749</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000274294887771454</v>
+        <v>0.000175484866792018</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0125742679007307</v>
+        <v>0.011140217197272</v>
       </c>
       <c r="I21" t="n">
-        <v>-35.3970584504866</v>
+        <v>28.2313471967257</v>
       </c>
       <c r="J21" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00388387544426621</v>
+        <v>0.000116445322251574</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0497142938711272</v>
+        <v>0.00988286343195439</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00385100225626609</v>
+        <v>0.000170202710936037</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0502176849755694</v>
+        <v>0.0110288287909985</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.853626817450772</v>
+        <v>31.5843316412656</v>
       </c>
       <c r="J22" t="n">
-        <v>143</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00361802739699608</v>
+        <v>0.000126851639379112</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0490900930827672</v>
+        <v>0.0101199152696027</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00378278415584369</v>
+        <v>0.000172821852682763</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0499573680231899</v>
+        <v>0.0110861347942344</v>
       </c>
       <c r="I23" t="n">
-        <v>4.35543642089887</v>
+        <v>26.5997688313384</v>
       </c>
       <c r="J23" t="n">
-        <v>143</v>
+        <v>904</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2900,22 +2900,22 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00390352126140878</v>
+        <v>0.000237350550920791</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0503200474584419</v>
+        <v>0.0117255241459545</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00383979907176212</v>
+        <v>0.000268794051743971</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0501822976079199</v>
+        <v>0.0126665192032668</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.65951885647544</v>
+        <v>11.697989824987</v>
       </c>
       <c r="J24" t="n">
         <v>143</v>
@@ -2923,71 +2923,71 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0036261728306563</v>
+        <v>0.000238933486300796</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0462201789705684</v>
+        <v>0.0117449908325899</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00381240336070278</v>
+        <v>0.000277952200925356</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0465621612053509</v>
+        <v>0.0129521549551023</v>
       </c>
       <c r="I25" t="n">
-        <v>4.88485903580131</v>
+        <v>14.0379225257648</v>
       </c>
       <c r="J25" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>2238252498900.45</v>
+        <v>0.000243944971333021</v>
       </c>
       <c r="F26" t="n">
-        <v>195129.753283825</v>
+        <v>0.0120427642576078</v>
       </c>
       <c r="G26" t="n">
-        <v>683473306874205952</v>
+        <v>0.000270698736847279</v>
       </c>
       <c r="H26" t="n">
-        <v>111320949.59593</v>
+        <v>0.012726673787497</v>
       </c>
       <c r="I26" t="n">
-        <v>99.999672517935</v>
+        <v>9.88322510324513</v>
       </c>
       <c r="J26" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2996,22 +2996,22 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00375317292037897</v>
+        <v>0.000100194002285498</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0477601368932166</v>
+        <v>0.00780524424627289</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00374329014461856</v>
+        <v>0.000128900220381869</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0461813385621833</v>
+        <v>0.00892895322360497</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.264013084174577</v>
+        <v>22.2701078487906</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3028,22 +3028,22 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00378568216544514</v>
+        <v>16931677905804742915242264222466008200804686644842086648088864868408</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0467788914917555</v>
+        <v>535702894921099953288480260848200</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00359492075854226</v>
+        <v>2544252433649152005028242606608002424082846284482680000644420468024</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0455432845826272</v>
+        <v>207660595292609154788688088666846</v>
       </c>
       <c r="I28" t="n">
-        <v>-5.30641479230367</v>
+        <v>-565.487342445816</v>
       </c>
       <c r="J28" t="n">
         <v>59</v>
@@ -3051,418 +3051,3478 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00163714308440836</v>
+        <v>0.0000963709712885494</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0302262168754486</v>
+        <v>0.00732306688708626</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00173007537746993</v>
+        <v>0.000110318976936474</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0317794961965484</v>
+        <v>0.00804924149941966</v>
       </c>
       <c r="I29" t="n">
-        <v>5.37157480372189</v>
+        <v>12.6433420933156</v>
       </c>
       <c r="J29" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00193033154355349</v>
+        <v>0.000110203109918176</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0332876981172616</v>
+        <v>0.00797633111959574</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0017565286796778</v>
+        <v>0.000118060464060201</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0321060024949954</v>
+        <v>0.00843634518344065</v>
       </c>
       <c r="I30" t="n">
-        <v>-9.89467840101408</v>
+        <v>6.65536443937592</v>
       </c>
       <c r="J30" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00175123397383295</v>
+        <v>0.000116828446028292</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0316055741569909</v>
+        <v>0.00543008862264813</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00172525893052165</v>
+        <v>0.000166102723105755</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0317189261617256</v>
+        <v>0.00752615367777901</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.5055736186479</v>
+        <v>29.6649423658697</v>
       </c>
       <c r="J31" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00220493111291235</v>
+        <v>0.000101271203530313</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0342582596807023</v>
+        <v>0.00455796453787871</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00214112976167384</v>
+        <v>0.00016039890651099</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0348499281950622</v>
+        <v>0.00730880772610952</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.97979844008303</v>
+        <v>36.8629090227782</v>
       </c>
       <c r="J32" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00298156935239599</v>
+        <v>0.000114679339841286</v>
       </c>
       <c r="F33" t="n">
-        <v>0.041525336502617</v>
+        <v>0.0053080546749923</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00214161421595604</v>
+        <v>0.000164595240271774</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0348338665005722</v>
+        <v>0.00744535576713739</v>
       </c>
       <c r="I33" t="n">
-        <v>-39.2206556242432</v>
+        <v>30.3264543665231</v>
       </c>
       <c r="J33" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00232791613326987</v>
+        <v>0.000235497356209997</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0370370225186266</v>
+        <v>0.00557758124801686</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00214606847390455</v>
+        <v>0.000285128337308196</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0348823262051082</v>
+        <v>0.00767364630314774</v>
       </c>
       <c r="I34" t="n">
-        <v>-8.47352549914083</v>
+        <v>17.406541056827</v>
       </c>
       <c r="J34" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00320777622580832</v>
+        <v>0.000218887525932935</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0444468533635436</v>
+        <v>0.00470545716324745</v>
       </c>
       <c r="G35" t="n">
-        <v>0.00343609047654079</v>
+        <v>0.000279442791203369</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0431945002207375</v>
+        <v>0.00745630035147825</v>
       </c>
       <c r="I35" t="n">
-        <v>6.64459368259486</v>
+        <v>21.6700044433652</v>
       </c>
       <c r="J35" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00266850938247974</v>
+        <v>0.000234468734985342</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0399697183411929</v>
+        <v>0.00545554730036103</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00335032619018976</v>
+        <v>0.000283675050182929</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0428265570563388</v>
+        <v>0.00759284839250612</v>
       </c>
       <c r="I36" t="n">
-        <v>20.3507589710662</v>
+        <v>17.3460144506384</v>
       </c>
       <c r="J36" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00288238442430727</v>
+        <v>0.0000494723489130972</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0426919977922853</v>
+        <v>0.0052119945214582</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0034375067249464</v>
+        <v>0.0000982191756004193</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0432185949428478</v>
+        <v>0.00730805957658908</v>
       </c>
       <c r="I37" t="n">
-        <v>16.1489807892021</v>
+        <v>49.6306616191086</v>
       </c>
       <c r="J37" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00265463512677057</v>
+        <v>0.0000354715448135019</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0398228539890259</v>
+        <v>0.00433987043668879</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002049776669016</v>
+        <v>0.0000924883428340249</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0322109390321017</v>
+        <v>0.00709071362491959</v>
       </c>
       <c r="I38" t="n">
-        <v>-29.5085053360926</v>
+        <v>61.64755067873</v>
       </c>
       <c r="J38" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00352067592483066</v>
+        <v>0.0000456664062561306</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0507865193511613</v>
+        <v>0.00508996057380237</v>
       </c>
       <c r="G39" t="n">
-        <v>0.00325706987894512</v>
+        <v>0.000096631554763942</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0487731170286883</v>
+        <v>0.00722726166594746</v>
       </c>
       <c r="I39" t="n">
-        <v>-8.09334941167794</v>
+        <v>52.7417246181255</v>
       </c>
       <c r="J39" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00110249239849438</v>
+        <v>0.000049526969720916</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0252750734662646</v>
+        <v>0.00521513935832137</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00263331395073391</v>
+        <v>0.0000982814020492039</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0349598022116142</v>
+        <v>0.00731120441345225</v>
       </c>
       <c r="I40" t="n">
-        <v>58.1328918951305</v>
+        <v>49.6069768152874</v>
       </c>
       <c r="J40" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0000355037223510819</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.00434301527355195</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0000925509588460851</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.00709385846178276</v>
+      </c>
+      <c r="I41" t="n">
+        <v>61.6387309286275</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0000457449180375179</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.00509310541066554</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.000096694936773299</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.00723040650281063</v>
+      </c>
+      <c r="I42" t="n">
+        <v>52.6915063352626</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.000146613777055881</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0105322471503872</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.000190508211838887</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0113950181118176</v>
+      </c>
+      <c r="I43" t="n">
+        <v>23.0407048385545</v>
+      </c>
+      <c r="J43" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.185006901319567</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0213392733177438</v>
+      </c>
+      <c r="G44" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H44" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I44" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="J44" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.000141695411297161</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0106294957558388</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.000175189559160512</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0111414370606521</v>
+      </c>
+      <c r="I45" t="n">
+        <v>19.1188036683525</v>
+      </c>
+      <c r="J45" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.000139746580180446</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0102723586500772</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.00018997681060315</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0113847693416966</v>
+      </c>
+      <c r="I46" t="n">
+        <v>26.4401903912535</v>
+      </c>
+      <c r="J46" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.000556050365673469</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0167858165390371</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.000550054096063248</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.016849816265974</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1.0901236175017</v>
+      </c>
+      <c r="J47" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.000509390063673173</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0164130757187827</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.000531996674448781</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.016530264480168</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.24938949083299</v>
+      </c>
+      <c r="J48" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.000576469413019139</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0176219863100532</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0005513104399593</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0168826766920618</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-4.56348569450207</v>
+      </c>
+      <c r="J49" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.000420890379375277</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0159627905299692</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.00028108105450633</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0128032922190265</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-49.7398606656349</v>
+      </c>
+      <c r="J50" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.000260482181928622</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0123032069621714</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.000267026517801658</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.0123546488861435</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.45081871527699</v>
+      </c>
+      <c r="J51" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.000317399918252121</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.0140867486566905</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.000274294887771454</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0125742679007307</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-15.7148501129132</v>
+      </c>
+      <c r="J52" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.000209516796399268</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.00931266488520251</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.000312790997410662</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0117982214882979</v>
+      </c>
+      <c r="I53" t="n">
+        <v>33.0169991675963</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.000162484789235042</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.00777145286340774</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.000330880268737716</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.0122156513465442</v>
+      </c>
+      <c r="I54" t="n">
+        <v>50.8931765998288</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.000216465081450478</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0100658251387201</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.000311529549216292</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0117797267913513</v>
+      </c>
+      <c r="I55" t="n">
+        <v>30.5153934851336</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.000326441918426816</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.00946015751057124</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.000433427030264193</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.0119457141136666</v>
+      </c>
+      <c r="I56" t="n">
+        <v>24.6835347975794</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.000281711591138534</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.00791894548877647</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.000451526384420775</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.012363143971913</v>
+      </c>
+      <c r="I57" t="n">
+        <v>37.6090521266176</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.000328738557390183</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.0102133177640888</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.00043187382078764</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.01192721941672</v>
+      </c>
+      <c r="I58" t="n">
+        <v>23.8808787273471</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.000144740390148402</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.00909514743705313</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.000242541857515252</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.0115807040401485</v>
+      </c>
+      <c r="I59" t="n">
+        <v>40.3235418285273</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.0000943139384699477</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.00755393541525836</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.000260616259004959</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.0119981338983949</v>
+      </c>
+      <c r="I60" t="n">
+        <v>63.8111839875066</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.000158548775385584</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.00986946783253966</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.000241710689610561</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0115622093432019</v>
+      </c>
+      <c r="I61" t="n">
+        <v>34.4055591248221</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.000144769757721335</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.00909886892695685</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.000242664857682614</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.0115844255300522</v>
+      </c>
+      <c r="I62" t="n">
+        <v>40.341688078015</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>46</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.0000944013813425672</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.00755765690516207</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.000260739513579266</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.0120018553882986</v>
+      </c>
+      <c r="I63" t="n">
+        <v>63.7947543712554</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.000158460774012725</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.00986574634263594</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.000241826328144328</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.0115659308331056</v>
+      </c>
+      <c r="I64" t="n">
+        <v>34.4733159417813</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.000256099841787</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.0128739722949922</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.000403994715789486</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0156500939501962</v>
+      </c>
+      <c r="I65" t="n">
+        <v>36.6081209041237</v>
+      </c>
+      <c r="J65" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.000226936695689189</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0126548410435967</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.000397975554644745</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0155526717755929</v>
+      </c>
+      <c r="I66" t="n">
+        <v>42.977227359664</v>
+      </c>
+      <c r="J66" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.000278057912846305</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.0136484744795844</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.000404615433846274</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0156658902000642</v>
+      </c>
+      <c r="I67" t="n">
+        <v>31.2784709661007</v>
+      </c>
+      <c r="J67" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.00485476491096186</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.0559198621875515</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.00385100225626609</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0502176849755694</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-26.0649718670642</v>
+      </c>
+      <c r="J68" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.00359502508773665</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.0493967352119226</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.00378278415584369</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.0499573680231899</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4.96351524093681</v>
+      </c>
+      <c r="J69" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>31</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.00409439837896595</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.0522119540095549</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.00383979907176212</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0501822976079199</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-6.63053723503782</v>
+      </c>
+      <c r="J70" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>31</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" t="s">
+        <v>45</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.00748645286197498</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.0599965585758948</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.00381240336070278</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0465621612053509</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-96.3709543209226</v>
+      </c>
+      <c r="J71" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" t="n">
+        <v>734700142238945</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3536088.50144429</v>
+      </c>
+      <c r="G72" t="n">
+        <v>683473306874205952</v>
+      </c>
+      <c r="H72" t="n">
+        <v>111320949.59593</v>
+      </c>
+      <c r="I72" t="n">
+        <v>99.8925049252327</v>
+      </c>
+      <c r="J72" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>31</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.00358777915912415</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0470630078299815</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.00374329014461856</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0461813385621833</v>
+      </c>
+      <c r="I73" t="n">
+        <v>4.15439304692902</v>
+      </c>
+      <c r="J73" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" t="s">
+        <v>47</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.00343863465896731</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.0444839095579722</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.00359492075854226</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0455432845826272</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4.3474143123621</v>
+      </c>
+      <c r="J74" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.0016219827326845</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.0292101682227151</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.00263679652120027</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0381378111641497</v>
+      </c>
+      <c r="I75" t="n">
+        <v>38.4866173918428</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.00288992326088907</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.0322079600146473</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.00338537724287846</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0430818689718989</v>
+      </c>
+      <c r="I76" t="n">
+        <v>14.6351188196718</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.00127657322845217</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.0253044396117033</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.00253531254414684</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0372320840190633</v>
+      </c>
+      <c r="I77" t="n">
+        <v>49.6482896596186</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>47</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.00139438947680937</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.026772456292686</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.00264540859636174</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0381622202714385</v>
+      </c>
+      <c r="I78" t="n">
+        <v>47.290203913033</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.00175024940387552</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.0293576608480838</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.00276888095802158</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0382853037895185</v>
+      </c>
+      <c r="I79" t="n">
+        <v>36.7885643907888</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>31</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" t="s">
+        <v>48</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.00300201472520252</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.032355452640016</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.00352000526075389</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0432293615972677</v>
+      </c>
+      <c r="I80" t="n">
+        <v>14.7156182215599</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.00141164001676363</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.025451932237072</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.00266748451175617</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.037379576644432</v>
+      </c>
+      <c r="I81" t="n">
+        <v>47.0797295900978</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.00153534739473891</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.0269199489180547</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.002780911669261</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0383097128968073</v>
+      </c>
+      <c r="I82" t="n">
+        <v>44.7897820089009</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>31</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.00154312988396053</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.0290163383312944</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.00255292649215465</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0379439812727291</v>
+      </c>
+      <c r="I83" t="n">
+        <v>39.5544725356294</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>31</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>48</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.00283232732982418</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.0320141301232266</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.00329816452440475</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0428880390804783</v>
+      </c>
+      <c r="I84" t="n">
+        <v>14.1241345340298</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>46</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.00118878389249837</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.0251106097202826</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.00245132748505754</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0370382541276426</v>
+      </c>
+      <c r="I85" t="n">
+        <v>51.5044848252715</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" t="s">
+        <v>47</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.00129885821469916</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.0265786264012653</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0025570459097467</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0379683903800178</v>
+      </c>
+      <c r="I86" t="n">
+        <v>49.2047362251768</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.00154809497882729</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.0290437473779268</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.00255860105514519</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0379713903193615</v>
+      </c>
+      <c r="I87" t="n">
+        <v>39.4944758693753</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.00283428653203367</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.032041539169859</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.00330431176954839</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0429154481271107</v>
+      </c>
+      <c r="I88" t="n">
+        <v>14.2246031941156</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.00119501267581595</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.025138018766915</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.00245701831418644</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.037065663174275</v>
+      </c>
+      <c r="I89" t="n">
+        <v>51.3632979894315</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" t="s">
+        <v>25</v>
+      </c>
+      <c r="D90" t="s">
+        <v>47</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.00130618176628747</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.0266060354478977</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.00256335576928475</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0379957994266503</v>
+      </c>
+      <c r="I90" t="n">
+        <v>49.0440702013076</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" t="s">
+        <v>45</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00149196403265601</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.0277274823493627</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.00285185203003691</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.0385599327736465</v>
+      </c>
+      <c r="I91" t="n">
+        <v>47.684381344403</v>
+      </c>
+      <c r="J91" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" t="s">
+        <v>46</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.00107352397055155</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.0230408675039497</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.00273641830210051</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0374694524309948</v>
+      </c>
+      <c r="I92" t="n">
+        <v>60.7690107273622</v>
+      </c>
+      <c r="J92" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" t="s">
+        <v>47</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.00115599700211062</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.0243987542495274</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.00258416312401812</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.0365453685073359</v>
+      </c>
+      <c r="I93" t="n">
+        <v>55.2660978958186</v>
+      </c>
+      <c r="J93" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.00182795519587862</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.0327918001764892</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.00173007537746993</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.0317794961965484</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-5.65754646782057</v>
+      </c>
+      <c r="J94" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
+        <v>46</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.00168024133668274</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.0309507950457873</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0017565286796778</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0321060024949954</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4.34307414832796</v>
+      </c>
+      <c r="J95" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" t="s">
+        <v>47</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00169016647840709</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.0316935371019174</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.00172525893052165</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.0317189261617256</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2.03403973129713</v>
+      </c>
+      <c r="J96" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.0027273074213395</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.0392693161868151</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.00214112976167384</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0348499281950622</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-27.3770263791678</v>
+      </c>
+      <c r="J97" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" t="s">
+        <v>46</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00221123024898648</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.0351223466626641</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.00214161421595604</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.0348338665005722</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-3.25063368144334</v>
+      </c>
+      <c r="J98" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>47</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.00223339247494314</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.0363845012398214</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.00214606847390455</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.0348823262051082</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-4.06902212582771</v>
+      </c>
+      <c r="J99" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.000501400487938108</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.0155983853190011</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.000807570718953943</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.0199077316434905</v>
+      </c>
+      <c r="I100" t="n">
+        <v>37.9124977949202</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.000441216693958818</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.0138141814984548</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.000825036854744102</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.0201764093012488</v>
+      </c>
+      <c r="I101" t="n">
+        <v>46.5215776214423</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" t="s">
+        <v>47</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.000466645080847626</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.0149171974457808</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.00080546917926962</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0199067480401192</v>
+      </c>
+      <c r="I102" t="n">
+        <v>42.0654330596773</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>45</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.000602356981550879</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.0157458779443698</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.000929497609839179</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0200552242688592</v>
+      </c>
+      <c r="I103" t="n">
+        <v>35.195424369612</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" t="s">
+        <v>46</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.000560709493739727</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.0139616741238235</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.000946231072092032</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0203239019266176</v>
+      </c>
+      <c r="I104" t="n">
+        <v>40.7428576087606</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" t="s">
+        <v>47</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.000571386211561908</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.0150646900711495</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.000926088160426024</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0200542406654879</v>
+      </c>
+      <c r="I105" t="n">
+        <v>38.301099616795</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" t="s">
+        <v>45</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.000460427888688699</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0154609499446772</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.00073533936671709</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0196878771751192</v>
+      </c>
+      <c r="I106" t="n">
+        <v>37.3856603456073</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" t="s">
+        <v>46</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.00037261363028467</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.0135943270300836</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.000753897635423257</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.0199565548328776</v>
+      </c>
+      <c r="I107" t="n">
+        <v>50.575036612832</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.000420031051215847</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.0147608388859493</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.000735187414663951</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.019686893571748</v>
+      </c>
+      <c r="I108" t="n">
+        <v>42.8674861895126</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" t="s">
+        <v>45</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.000460275759074983</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0154595654749953</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.000735384080024626</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.0196892616448011</v>
+      </c>
+      <c r="I109" t="n">
+        <v>37.4101545603803</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" t="s">
+        <v>46</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.000372635495498422</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.0135957114997655</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.000753935471340845</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0199579393025595</v>
+      </c>
+      <c r="I110" t="n">
+        <v>50.5746168387986</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>25</v>
+      </c>
+      <c r="D111" t="s">
+        <v>47</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.000419914446872027</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.0147594544162674</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.000735219851009424</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.0196882780414298</v>
+      </c>
+      <c r="I111" t="n">
+        <v>42.8858665478763</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D112" t="s">
+        <v>45</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.000556976662982256</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.0169489803740928</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.000950515010948565</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0211287599650894</v>
+      </c>
+      <c r="I112" t="n">
+        <v>41.4026441911293</v>
+      </c>
+      <c r="J112" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" t="s">
+        <v>48</v>
+      </c>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113" t="n">
+        <v>1768531608388.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>60662.5350541879</v>
+      </c>
+      <c r="I113"/>
+      <c r="J113" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" t="s">
+        <v>46</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.000475030824112494</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.0158137921898062</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.000893115052846344</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.0204773957244897</v>
+      </c>
+      <c r="I114" t="n">
+        <v>46.8119115674315</v>
+      </c>
+      <c r="J114" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>32</v>
+      </c>
+      <c r="B115" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" t="s">
+        <v>27</v>
+      </c>
+      <c r="D115" t="s">
+        <v>47</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.000452900106800729</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.01511371327175</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.000948842693042261</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.0211014650212186</v>
+      </c>
+      <c r="I115" t="n">
+        <v>52.268156763836</v>
+      </c>
+      <c r="J115" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
         <v>33</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B116" t="s">
         <v>13</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C116" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" t="s">
+        <v>45</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.00304336952537612</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.0419078785036758</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.00343609047654079</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.0431945002207375</v>
+      </c>
+      <c r="I116" t="n">
+        <v>11.4292959933939</v>
+      </c>
+      <c r="J116" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" t="s">
+        <v>46</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.00265249259145161</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.0398489481441051</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.00335032619018976</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0428265570563388</v>
+      </c>
+      <c r="I117" t="n">
+        <v>20.8288255866402</v>
+      </c>
+      <c r="J117" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.00291073655636375</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.0406406323655378</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0034375067249464</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.0432185949428478</v>
+      </c>
+      <c r="I118" t="n">
+        <v>15.3241931065855</v>
+      </c>
+      <c r="J118" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
         <v>16</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D119" t="s">
+        <v>45</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.00127105199934514</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.0280532916236113</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.002049776669016</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.0322109390321017</v>
+      </c>
+      <c r="I119" t="n">
+        <v>37.9907080338022</v>
+      </c>
+      <c r="J119" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" t="s">
+        <v>48</v>
+      </c>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120" t="n">
+        <v>0.00325706987894512</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.0487731170286883</v>
+      </c>
+      <c r="I120"/>
+      <c r="J120" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" t="s">
+        <v>46</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.00114272630182692</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.0256183597323261</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.00263331395073391</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.0349598022116142</v>
+      </c>
+      <c r="I121" t="n">
+        <v>56.6050109023863</v>
+      </c>
+      <c r="J121" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" t="s">
         <v>47</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.00117708108713315</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.026428042064265</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="E122" t="n">
+        <v>0.0011952008913465</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.0265416745844629</v>
+      </c>
+      <c r="G122" t="n">
         <v>0.00146819505729097</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H122" t="n">
         <v>0.0268634058876088</v>
       </c>
-      <c r="I41" t="n">
-        <v>19.8280173136511</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="I122" t="n">
+        <v>18.5938622112097</v>
+      </c>
+      <c r="J122" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" t="s">
+        <v>18</v>
+      </c>
+      <c r="C123" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" t="s">
+        <v>45</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.000834640060914697</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.0203156602440779</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.00149328715761598</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.0266914786575965</v>
+      </c>
+      <c r="I123" t="n">
+        <v>44.1071962175585</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>33</v>
+      </c>
+      <c r="B124" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" t="s">
+        <v>46</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.000592385827291352</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.0164963569444326</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.00162159938843061</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0276969657539496</v>
+      </c>
+      <c r="I124" t="n">
+        <v>63.4690397938135</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" t="s">
+        <v>47</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.000695978345772829</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.0185735745112158</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0014846285618468</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0266212297714026</v>
+      </c>
+      <c r="I125" t="n">
+        <v>53.1210456501612</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>33</v>
+      </c>
+      <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>45</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.00095791899027418</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.0204631528694467</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.00161359173085168</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0268389712829653</v>
+      </c>
+      <c r="I126" t="n">
+        <v>40.6343641976541</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>33</v>
+      </c>
+      <c r="B127" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>46</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.000714478016389551</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.0166438495698014</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.00174154205285966</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0278444583793183</v>
+      </c>
+      <c r="I127" t="n">
+        <v>58.9744034480041</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>33</v>
+      </c>
+      <c r="B128" t="s">
+        <v>18</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>47</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.00081724874693477</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.0187210671365845</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.00160416785931435</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.0267687223967713</v>
+      </c>
+      <c r="I128" t="n">
+        <v>49.0546614439667</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>33</v>
+      </c>
+      <c r="B129" t="s">
+        <v>18</v>
+      </c>
+      <c r="C129" t="s">
+        <v>23</v>
+      </c>
+      <c r="D129" t="s">
+        <v>45</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.000760349947994583</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.0200946649926265</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.00142345366466475</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.0264704834061451</v>
+      </c>
+      <c r="I129" t="n">
+        <v>46.5841448254193</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130" t="s">
+        <v>18</v>
+      </c>
+      <c r="C130" t="s">
+        <v>23</v>
+      </c>
+      <c r="D130" t="s">
+        <v>46</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.000519873864036648</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.0162753616929812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.00155230816074539</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.0274759705024981</v>
+      </c>
+      <c r="I130" t="n">
+        <v>66.5096224330216</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>33</v>
+      </c>
+      <c r="B131" t="s">
+        <v>18</v>
+      </c>
+      <c r="C131" t="s">
+        <v>23</v>
+      </c>
+      <c r="D131" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.000624697706668463</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.0183525792597643</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.00141594171816286</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.0264002345199511</v>
+      </c>
+      <c r="I131" t="n">
+        <v>55.8811144092154</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>33</v>
+      </c>
+      <c r="B132" t="s">
+        <v>18</v>
+      </c>
+      <c r="C132" t="s">
+        <v>25</v>
+      </c>
+      <c r="D132" t="s">
+        <v>45</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.000760358921134274</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.0200949086792281</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.00142345772358765</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.0264707270927467</v>
+      </c>
+      <c r="I132" t="n">
+        <v>46.5836667619546</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B133" t="s">
+        <v>18</v>
+      </c>
+      <c r="C133" t="s">
+        <v>25</v>
+      </c>
+      <c r="D133" t="s">
+        <v>46</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.000519880876449824</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.0162756053795828</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.00155231162172431</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.0274762141890998</v>
+      </c>
+      <c r="I133" t="n">
+        <v>66.5092453619371</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>33</v>
+      </c>
+      <c r="B134" t="s">
+        <v>18</v>
+      </c>
+      <c r="C134" t="s">
+        <v>25</v>
+      </c>
+      <c r="D134" t="s">
+        <v>47</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.000624703361327589</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.018352822946366</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.00141594451270085</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.0264004782065528</v>
+      </c>
+      <c r="I134" t="n">
+        <v>55.8808021271965</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>33</v>
+      </c>
+      <c r="B135" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.000656438659693344</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.0193480765924229</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.00158607731286337</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.0280659856877547</v>
+      </c>
+      <c r="I135" t="n">
+        <v>58.6124425102414</v>
+      </c>
+      <c r="J135" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>33</v>
+      </c>
+      <c r="B136" t="s">
+        <v>18</v>
+      </c>
+      <c r="C136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136" t="s">
+        <v>46</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.000489024284254164</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.0163417846277859</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.00141619698839945</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.026345669505885</v>
+      </c>
+      <c r="I136" t="n">
+        <v>65.4691904968074</v>
+      </c>
+      <c r="J136" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>33</v>
+      </c>
+      <c r="B137" t="s">
+        <v>18</v>
+      </c>
+      <c r="C137" t="s">
+        <v>27</v>
+      </c>
+      <c r="D137" t="s">
+        <v>47</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.000595357264073576</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0183082485829566</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.00154520165160374</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.0275704790218442</v>
+      </c>
+      <c r="I137" t="n">
+        <v>61.4705780662566</v>
+      </c>
+      <c r="J137" t="n">
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -3507,13 +6567,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00137174196099888</v>
+        <v>0.00122289804016409</v>
       </c>
       <c r="E2" t="n">
         <v>0.00149018877607356</v>
       </c>
       <c r="F2" t="n">
-        <v>8.07350618905641</v>
+        <v>14.5764022514469</v>
       </c>
     </row>
     <row r="3">
@@ -3527,13 +6587,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4153767279189150451626400848280400684420046668002066848484846668068</v>
+        <v>5643892635268247638808646400268444866604422246662886446064668886866</v>
       </c>
       <c r="E3" t="n">
         <v>636063108412288001582868404402008686028264826628420000466680642086</v>
       </c>
       <c r="F3" t="n">
-        <v>-101.097211961252</v>
+        <v>-145.082665377057</v>
       </c>
     </row>
     <row r="4">
@@ -3547,13 +6607,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00130531380474092</v>
+        <v>0.00122309536991237</v>
       </c>
       <c r="E4" t="n">
         <v>0.00127529233645623</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.3871253096532</v>
+        <v>3.78398659963748</v>
       </c>
     </row>
     <row r="5">
@@ -3567,13 +6627,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00150706332841838</v>
+        <v>0.00200750122425062</v>
       </c>
       <c r="E5" t="n">
         <v>0.00141410018480556</v>
       </c>
       <c r="F5" t="n">
-        <v>-22.4789185026138</v>
+        <v>-11.345498461416</v>
       </c>
     </row>
     <row r="6">
@@ -3587,13 +6647,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00152265783665185</v>
+        <v>0.00147404247585011</v>
       </c>
       <c r="E6" t="n">
         <v>0.00164544533055419</v>
       </c>
       <c r="F6" t="n">
-        <v>5.80235667828108</v>
+        <v>8.54342240742218</v>
       </c>
     </row>
     <row r="7">
@@ -3607,13 +6667,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00159257909027508</v>
+        <v>0.00161699808116297</v>
       </c>
       <c r="E7" t="n">
         <v>0.00166849276643273</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4689779115634</v>
+        <v>2.68440940149086</v>
       </c>
     </row>
     <row r="8">
@@ -3627,13 +6687,413 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00160813677163042</v>
+        <v>0.00178156133399491</v>
       </c>
       <c r="E8" t="n">
         <v>0.00166950441374756</v>
       </c>
       <c r="F8" t="n">
-        <v>4.46777416834226</v>
+        <v>-0.589167053101053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000420442751359355</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.000964849694681266</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.4550792434805</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.185006901319567</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.000458151750898465</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.000974270260966051</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.2205438191006</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.000539006016490791</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.00102640535804487</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39.2632734975296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.000444463295766473</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00093421883064313</v>
+      </c>
+      <c r="F13" t="n">
+        <v>46.1834751533618</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.00288992326088907</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.00338537724287846</v>
+      </c>
+      <c r="F14" t="n">
+        <v>14.6351188196718</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.00049801420996493</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.000925035040635355</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38.5349314031048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.000564172721720605</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.000926210103693905</v>
+      </c>
+      <c r="F16" t="n">
+        <v>35.2744623291997</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.000566864538383626</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00105637356394547</v>
+      </c>
+      <c r="F17" t="n">
+        <v>36.8758870480142</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.00300201472520252</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00352000526075389</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14.7156182215599</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.000617768245051037</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00104753115474387</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31.4134602399129</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.000682082238639235</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.00104852753825891</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28.3816054503917</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.000372209682600528</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.000862253928920611</v>
+      </c>
+      <c r="F21" t="n">
+        <v>59.7906301657345</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.00283232732982418</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.00329816452440475</v>
+      </c>
+      <c r="F22" t="n">
+        <v>14.1241345340298</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.000429862535735296</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.000852658911242194</v>
+      </c>
+      <c r="F23" t="n">
+        <v>48.3196728563233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.000498404360509496</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.000853999566200343</v>
+      </c>
+      <c r="F24" t="n">
+        <v>44.7177197935208</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.000373297090319744</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.000863260284111033</v>
+      </c>
+      <c r="F25" t="n">
+        <v>59.7350482387684</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.00283428653203367</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.00330431176954839</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.2246031941156</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.000431081071094256</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.000853766109971245</v>
+      </c>
+      <c r="F27" t="n">
+        <v>48.2858193938591</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.000499239431635763</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000855004337513719</v>
+      </c>
+      <c r="F28" t="n">
+        <v>44.699105893503</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Stress_Testing.xlsx
+++ b/results/consolidated/Stress_Testing.xlsx
@@ -2199,19 +2199,19 @@
         <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000169877455158598</v>
+        <v>0.000166975655869404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00984288750182562</v>
+        <v>0.00971884369055118</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000181010224401328</v>
+        <v>0.000167029188787356</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0101754695102639</v>
+        <v>0.00972204490336474</v>
       </c>
       <c r="I2" t="n">
-        <v>6.15035381539929</v>
+        <v>0.0320500376853902</v>
       </c>
       <c r="J2" t="n">
         <v>143</v>
@@ -2231,19 +2231,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000168172289255699</v>
+        <v>0.000166623099547765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0097582433333083</v>
+        <v>0.00968673040252878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000173084082239777</v>
+        <v>0.000166658220256576</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00986452620090229</v>
+        <v>0.00968888945248574</v>
       </c>
       <c r="I3" t="n">
-        <v>2.83780745203027</v>
+        <v>0.0210734932587545</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2263,19 +2263,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000186272688888849</v>
+        <v>0.000166779464254165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0101156799314045</v>
+        <v>0.00971431830743773</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000186382694559611</v>
+        <v>0.000167656262280561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0103607114259397</v>
+        <v>0.00972477388730238</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0590213973572735</v>
+        <v>0.522973621426244</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2295,19 +2295,19 @@
         <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000391106811833536</v>
+        <v>0.0000387529867485644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0046428961532884</v>
+        <v>0.0047560746412279</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0000713100425525571</v>
+        <v>0.0000388761729144754</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00691952806751367</v>
+        <v>0.00475593030482492</v>
       </c>
       <c r="I5" t="n">
-        <v>45.1540347146362</v>
+        <v>0.316868036835829</v>
       </c>
       <c r="J5" t="n">
         <v>59</v>
@@ -2327,19 +2327,19 @@
         <v>48</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000842948574186675</v>
+        <v>0.00005188244047529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00627068068523909</v>
+        <v>0.00560945424675768</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000121020868400151</v>
+        <v>0.0000519156255095034</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00828901839589263</v>
+        <v>0.00561282084118335</v>
       </c>
       <c r="I6" t="n">
-        <v>30.3468413894123</v>
+        <v>0.063921090977316</v>
       </c>
       <c r="J6" t="n">
         <v>59</v>
@@ -2359,19 +2359,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000038799377829785</v>
+        <v>0.000038789703972998</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00471193762349396</v>
+        <v>0.00474498436217047</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0000455688503947384</v>
+        <v>0.0000388226486434652</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00539792332968993</v>
+        <v>0.00474836262751274</v>
       </c>
       <c r="I7" t="n">
-        <v>14.8554824322166</v>
+        <v>0.0848594096958848</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2391,19 +2391,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000437411660469645</v>
+        <v>0.0000388322277887795</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00513783575080229</v>
+        <v>0.00476963030530809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00005021437716793</v>
+        <v>0.0000390652226066273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00575846949939422</v>
+        <v>0.00478304488823398</v>
       </c>
       <c r="I8" t="n">
-        <v>12.8911508736181</v>
+        <v>0.59642516361405</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2423,19 +2423,19 @@
         <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000100667806358764</v>
+        <v>0.0000908500432055289</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00449189893642634</v>
+        <v>0.00366144759262836</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000140712503876815</v>
+        <v>0.0000909047514344009</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00644545603954121</v>
+        <v>0.00365937401654808</v>
       </c>
       <c r="I9" t="n">
-        <v>28.4585210374109</v>
+        <v>0.0601819244965666</v>
       </c>
       <c r="J9" t="n">
         <v>1356</v>
@@ -2455,19 +2455,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000928480321311417</v>
+        <v>0.0000907881022416117</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00366790601017871</v>
+        <v>0.00366274543637718</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000132085021288518</v>
+        <v>0.0000908255312470966</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00605424925084791</v>
+        <v>0.00366243203274201</v>
       </c>
       <c r="I10" t="n">
-        <v>29.7058582226895</v>
+        <v>0.0412097842654498</v>
       </c>
       <c r="J10" t="n">
         <v>1356</v>
@@ -2487,19 +2487,19 @@
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000999279350679915</v>
+        <v>0.0000908659761228335</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0044814525737719</v>
+        <v>0.00366422488581416</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000138579116845906</v>
+        <v>0.0000909124217328905</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00631687863580676</v>
+        <v>0.0036662156162488</v>
       </c>
       <c r="I11" t="n">
-        <v>27.8910579441007</v>
+        <v>0.0510882992353598</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2519,19 +2519,19 @@
         <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000220028781498017</v>
+        <v>0.000210487894573113</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00463939156179508</v>
+        <v>0.00380404588370665</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000260639563268616</v>
+        <v>0.00021055999906374</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00659294866490994</v>
+        <v>0.00380876291675883</v>
       </c>
       <c r="I12" t="n">
-        <v>15.5812038898889</v>
+        <v>0.0342441541353146</v>
       </c>
       <c r="J12" t="n">
         <v>1356</v>
@@ -2551,19 +2551,19 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000213760586337385</v>
+        <v>0.000210365644683591</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00381539863554744</v>
+        <v>0.00380965898302289</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000252014571340813</v>
+        <v>0.000210254566395277</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00620174187621664</v>
+        <v>0.00380964040699412</v>
       </c>
       <c r="I13" t="n">
-        <v>15.1792750712399</v>
+        <v>-0.0528303809131359</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2583,19 +2583,19 @@
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000219419824695114</v>
+        <v>0.000210445822558821</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00462894519914064</v>
+        <v>0.00381416811668865</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000258470368491299</v>
+        <v>0.000210599898708509</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00646437126117549</v>
+        <v>0.00381185189380868</v>
       </c>
       <c r="I14" t="n">
-        <v>15.1083251918294</v>
+        <v>0.0731606000916672</v>
       </c>
       <c r="J14" t="n">
         <v>1356</v>
@@ -2615,19 +2615,19 @@
         <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000323057033516642</v>
+        <v>0.0000221013282657426</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00427471571781723</v>
+        <v>0.00344483672031824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000715168405499028</v>
+        <v>0.000022050045074368</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0062282728209321</v>
+        <v>0.00344311381585274</v>
       </c>
       <c r="I15" t="n">
-        <v>54.8278376068332</v>
+        <v>-0.232576356200572</v>
       </c>
       <c r="J15" t="n">
         <v>1356</v>
@@ -2647,19 +2647,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000222012255000275</v>
+        <v>0.0000220856600770798</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00345072279156959</v>
+        <v>0.00344589947323064</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000062885690458495</v>
+        <v>0.0000220794946898927</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0058370660322388</v>
+        <v>0.00344529895644092</v>
       </c>
       <c r="I16" t="n">
-        <v>64.6959024570455</v>
+        <v>-0.0279235882599467</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2679,19 +2679,19 @@
         <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000313730601865907</v>
+        <v>0.0000220744797670718</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00426426935516279</v>
+        <v>0.00344320429605973</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000694361805051519</v>
+        <v>0.0000221126924486366</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00609969541719765</v>
+        <v>0.00345014366094921</v>
       </c>
       <c r="I17" t="n">
-        <v>54.8174165710873</v>
+        <v>0.172808814004054</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2711,19 +2711,19 @@
         <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0000324102033357809</v>
+        <v>0.0000222198005873354</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00427877143726121</v>
+        <v>0.00345413849557914</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0000716369065930292</v>
+        <v>0.0000221860582840762</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00623232854037608</v>
+        <v>0.00345218027556308</v>
       </c>
       <c r="I18" t="n">
-        <v>54.7576732760057</v>
+        <v>-0.152087868998985</v>
       </c>
       <c r="J18" t="n">
         <v>1356</v>
@@ -2743,19 +2743,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000223483904606143</v>
+        <v>0.0000221935207418048</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00345477851101357</v>
+        <v>0.00344952925812622</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000630058249892503</v>
+        <v>0.0000221873690607457</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00584112175168278</v>
+        <v>0.00344901448342143</v>
       </c>
       <c r="I19" t="n">
-        <v>64.5296439425605</v>
+        <v>-0.0277260500885203</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2775,19 +2775,19 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000314811600282095</v>
+        <v>0.0000222512168252761</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00426832507460677</v>
+        <v>0.00345906227230867</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000069555261914823</v>
+        <v>0.0000222355213399453</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00610375113664163</v>
+        <v>0.00345531687924491</v>
       </c>
       <c r="I20" t="n">
-        <v>54.7393552097306</v>
+        <v>-0.0705874402078275</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2807,19 +2807,19 @@
         <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000125943124770252</v>
+        <v>0.000116862525201323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0100064308539749</v>
+        <v>0.00991193503139734</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000175484866792018</v>
+        <v>0.000117018105317552</v>
       </c>
       <c r="H21" t="n">
-        <v>0.011140217197272</v>
+        <v>0.00991772106130117</v>
       </c>
       <c r="I21" t="n">
-        <v>28.2313471967257</v>
+        <v>0.132953884193425</v>
       </c>
       <c r="J21" t="n">
         <v>904</v>
@@ -2839,19 +2839,19 @@
         <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000116445322251574</v>
+        <v>0.000116124435981526</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00988286343195439</v>
+        <v>0.00987579603880344</v>
       </c>
       <c r="G22" t="n">
-        <v>0.000170202710936037</v>
+        <v>0.000116087830766764</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0110288287909985</v>
+        <v>0.00987493499361322</v>
       </c>
       <c r="I22" t="n">
-        <v>31.5843316412656</v>
+        <v>-0.0315323445365218</v>
       </c>
       <c r="J22" t="n">
         <v>904</v>
@@ -2871,19 +2871,19 @@
         <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000126851639379112</v>
+        <v>0.000119676038804887</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0101199152696027</v>
+        <v>0.0100502253803307</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000172821852682763</v>
+        <v>0.000119709692720434</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0110861347942344</v>
+        <v>0.0100505312813093</v>
       </c>
       <c r="I23" t="n">
-        <v>26.5997688313384</v>
+        <v>0.0281129412187687</v>
       </c>
       <c r="J23" t="n">
         <v>904</v>
@@ -2903,19 +2903,19 @@
         <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000237350550920791</v>
+        <v>0.000238433575010785</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0117255241459545</v>
+        <v>0.0116980409942627</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000268794051743971</v>
+        <v>0.000238237291908681</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0126665192032668</v>
+        <v>0.0116865692551256</v>
       </c>
       <c r="I24" t="n">
-        <v>11.697989824987</v>
+        <v>-0.08238974701692</v>
       </c>
       <c r="J24" t="n">
         <v>143</v>
@@ -2935,19 +2935,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000238933486300796</v>
+        <v>0.000240210439988377</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0117449908325899</v>
+        <v>0.0117459522096261</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000277952200925356</v>
+        <v>0.000240203684583164</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0129521549551023</v>
+        <v>0.0117485267320475</v>
       </c>
       <c r="I25" t="n">
-        <v>14.0379225257648</v>
+        <v>-0.00281236535753252</v>
       </c>
       <c r="J25" t="n">
         <v>143</v>
@@ -2967,19 +2967,19 @@
         <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000243944971333021</v>
+        <v>0.000238330500883258</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0120427642576078</v>
+        <v>0.0116789856809294</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000270698736847279</v>
+        <v>0.00023782144737888</v>
       </c>
       <c r="H26" t="n">
-        <v>0.012726673787497</v>
+        <v>0.0116983580133469</v>
       </c>
       <c r="I26" t="n">
-        <v>9.88322510324513</v>
+        <v>-0.214048610833162</v>
       </c>
       <c r="J26" t="n">
         <v>143</v>
@@ -2999,19 +2999,19 @@
         <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000100194002285498</v>
+        <v>0.0000963882221354587</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00780524424627289</v>
+        <v>0.00736458489875018</v>
       </c>
       <c r="G27" t="n">
-        <v>0.000128900220381869</v>
+        <v>0.0000963673756623975</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00892895322360497</v>
+        <v>0.00737103094844691</v>
       </c>
       <c r="I27" t="n">
-        <v>22.2701078487906</v>
+        <v>-0.0216322930015033</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -3031,19 +3031,19 @@
         <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>16931677905804742915242264222466008200804686644842086648088864868408</v>
+        <v>612204287747896810964022862642648446286204606266886448642622288</v>
       </c>
       <c r="F28" t="n">
-        <v>535702894921099953288480260848200</v>
+        <v>3221233282482193816646060260448</v>
       </c>
       <c r="G28" t="n">
-        <v>2544252433649152005028242606608002424082846284482680000644420468024</v>
+        <v>689388705932256358982286242068620624466088444608028280668266228</v>
       </c>
       <c r="H28" t="n">
-        <v>207660595292609154788688088666846</v>
+        <v>3418267739420846032424404222606</v>
       </c>
       <c r="I28" t="n">
-        <v>-565.487342445816</v>
+        <v>11.1960665325933</v>
       </c>
       <c r="J28" t="n">
         <v>59</v>
@@ -3063,19 +3063,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000963709712885494</v>
+        <v>0.0000969790974229639</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00732306688708626</v>
+        <v>0.00737412319549455</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000110318976936474</v>
+        <v>0.000097007669782765</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00804924149941966</v>
+        <v>0.00737491167293084</v>
       </c>
       <c r="I29" t="n">
-        <v>12.6433420933156</v>
+        <v>0.0294537121293056</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -3095,19 +3095,19 @@
         <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.000110203109918176</v>
+        <v>0.0000966635055018119</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00797633111959574</v>
+        <v>0.00736185351195423</v>
       </c>
       <c r="G30" t="n">
-        <v>0.000118060464060201</v>
+        <v>0.000097004870398268</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00843634518344065</v>
+        <v>0.00739429506696414</v>
       </c>
       <c r="I30" t="n">
-        <v>6.65536443937592</v>
+        <v>0.351904904418262</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -3127,19 +3127,19 @@
         <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000116828446028292</v>
+        <v>0.000103412008896841</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00543008862264813</v>
+        <v>0.00454089266379086</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000166102723105755</v>
+        <v>0.000103216771941774</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00752615367777901</v>
+        <v>0.00454904266084343</v>
       </c>
       <c r="I31" t="n">
-        <v>29.6649423658697</v>
+        <v>-0.189152355177928</v>
       </c>
       <c r="J31" t="n">
         <v>1356</v>
@@ -3159,19 +3159,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000101271203530313</v>
+        <v>0.000103488761085417</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00455796453787871</v>
+        <v>0.0045485746511353</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00016039890651099</v>
+        <v>0.000103471462951834</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00730880772610952</v>
+        <v>0.00454828929035417</v>
       </c>
       <c r="I32" t="n">
-        <v>36.8629090227782</v>
+        <v>-0.0167177819757007</v>
       </c>
       <c r="J32" t="n">
         <v>1356</v>
@@ -3191,19 +3191,19 @@
         <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000114679339841286</v>
+        <v>0.000103384723050186</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0053080546749923</v>
+        <v>0.00454416547755314</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000164595240271774</v>
+        <v>0.00010341731907531</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00744535576713739</v>
+        <v>0.00454751898718663</v>
       </c>
       <c r="I33" t="n">
-        <v>30.3264543665231</v>
+        <v>0.0315189229575538</v>
       </c>
       <c r="J33" t="n">
         <v>1356</v>
@@ -3223,19 +3223,19 @@
         <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000235497356209997</v>
+        <v>0.000222504719111438</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00557758124801686</v>
+        <v>0.00469565026177085</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000285128337308196</v>
+        <v>0.000222716544460445</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00767364630314774</v>
+        <v>0.00469862990205204</v>
       </c>
       <c r="I34" t="n">
-        <v>17.406541056827</v>
+        <v>0.0951098399627156</v>
       </c>
       <c r="J34" t="n">
         <v>1356</v>
@@ -3255,19 +3255,19 @@
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000218887525932935</v>
+        <v>0.000222782784816604</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00470545716324745</v>
+        <v>0.00469545401808677</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000279442791203369</v>
+        <v>0.000222994993646178</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00745630035147825</v>
+        <v>0.00469607553390421</v>
       </c>
       <c r="I35" t="n">
-        <v>21.6700044433652</v>
+        <v>0.0951630465348463</v>
       </c>
       <c r="J35" t="n">
         <v>1356</v>
@@ -3287,19 +3287,19 @@
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000234468734985342</v>
+        <v>0.00022267611953299</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00545554730036103</v>
+        <v>0.00469255800349099</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000283675050182929</v>
+        <v>0.000222790312671865</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00759284839250612</v>
+        <v>0.00469432823552905</v>
       </c>
       <c r="I36" t="n">
-        <v>17.3460144506384</v>
+        <v>0.0512558815981108</v>
       </c>
       <c r="J36" t="n">
         <v>1356</v>
@@ -3319,19 +3319,19 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0000494723489130972</v>
+        <v>0.0000352106424578699</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0052119945214582</v>
+        <v>0.00432578147147118</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0000982191756004193</v>
+        <v>0.000035225587417495</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00730805957658908</v>
+        <v>0.00433223868747209</v>
       </c>
       <c r="I37" t="n">
-        <v>49.6306616191086</v>
+        <v>0.0424264312414262</v>
       </c>
       <c r="J37" t="n">
         <v>1356</v>
@@ -3351,19 +3351,19 @@
         <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000354715448135019</v>
+        <v>0.0000352777641430168</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00433987043668879</v>
+        <v>0.00433104936916655</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000924883428340249</v>
+        <v>0.0000352728063311057</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00709071362491959</v>
+        <v>0.00433055528120916</v>
       </c>
       <c r="I38" t="n">
-        <v>61.64755067873</v>
+        <v>-0.0140556208216387</v>
       </c>
       <c r="J38" t="n">
         <v>1356</v>
@@ -3383,19 +3383,19 @@
         <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000456664062561306</v>
+        <v>0.0000352544369019043</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00508996057380237</v>
+        <v>0.00433091566399898</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000096631554763942</v>
+        <v>0.0000352005574784481</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00722726166594746</v>
+        <v>0.00432983392803921</v>
       </c>
       <c r="I39" t="n">
-        <v>52.7417246181255</v>
+        <v>-0.153064119763288</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3415,19 +3415,19 @@
         <v>45</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000049526969720916</v>
+        <v>0.0000352639620878871</v>
       </c>
       <c r="F40" t="n">
-        <v>0.00521513935832137</v>
+        <v>0.00433302368838828</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000982814020492039</v>
+        <v>0.0000352594939516534</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00731120441345225</v>
+        <v>0.00433066709372014</v>
       </c>
       <c r="I40" t="n">
-        <v>49.6069768152874</v>
+        <v>-0.0126721507684874</v>
       </c>
       <c r="J40" t="n">
         <v>1356</v>
@@ -3447,19 +3447,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000355037223510819</v>
+        <v>0.0000353267430775126</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00434301527355195</v>
+        <v>0.00433236727156954</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000925509588460851</v>
+        <v>0.0000353377960853952</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00709385846178276</v>
+        <v>0.00433364119492039</v>
       </c>
       <c r="I41" t="n">
-        <v>61.6387309286275</v>
+        <v>0.0312781472161651</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3479,19 +3479,19 @@
         <v>47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000457449180375179</v>
+        <v>0.0000352613726673386</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00509310541066554</v>
+        <v>0.00433019146758099</v>
       </c>
       <c r="G42" t="n">
-        <v>0.000096694936773299</v>
+        <v>0.0000353512393979318</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00723040650281063</v>
+        <v>0.00433518527011683</v>
       </c>
       <c r="I42" t="n">
-        <v>52.6915063352626</v>
+        <v>0.254210975693382</v>
       </c>
       <c r="J42" t="n">
         <v>1356</v>
@@ -3511,19 +3511,19 @@
         <v>45</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000146613777055881</v>
+        <v>0.000131633261572373</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0105322471503872</v>
+        <v>0.0101685698362659</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000190508211838887</v>
+        <v>0.000131613341682797</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0113950181118176</v>
+        <v>0.0101676381933407</v>
       </c>
       <c r="I43" t="n">
-        <v>23.0407048385545</v>
+        <v>-0.0151351597954805</v>
       </c>
       <c r="J43" t="n">
         <v>904</v>
@@ -3543,19 +3543,19 @@
         <v>48</v>
       </c>
       <c r="E44" t="n">
-        <v>0.185006901319567</v>
+        <v>0.000077465382529251</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0213392733177438</v>
-      </c>
-      <c r="G44" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H44" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I44" t="e">
-        <v>#NUM!</v>
+        <v>0.00711849067465625</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0000970764824235429</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.00720892912690086</v>
+      </c>
+      <c r="I44" t="n">
+        <v>20.2017001488878</v>
       </c>
       <c r="J44" t="n">
         <v>904</v>
@@ -3575,19 +3575,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000141695411297161</v>
+        <v>0.000141496954720349</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106294957558388</v>
+        <v>0.0106223569086999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000175189559160512</v>
+        <v>0.000141490832642518</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0111414370606521</v>
+        <v>0.0106225236769855</v>
       </c>
       <c r="I45" t="n">
-        <v>19.1188036683525</v>
+        <v>-0.0043268370935821</v>
       </c>
       <c r="J45" t="n">
         <v>904</v>
@@ -3607,19 +3607,19 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000139746580180446</v>
+        <v>0.000132421764575771</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0102723586500772</v>
+        <v>0.0102031709782539</v>
       </c>
       <c r="G46" t="n">
-        <v>0.00018997681060315</v>
+        <v>0.000132459368149486</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0113847693416966</v>
+        <v>0.0102070433375184</v>
       </c>
       <c r="I46" t="n">
-        <v>26.4401903912535</v>
+        <v>0.0283887612031127</v>
       </c>
       <c r="J46" t="n">
         <v>904</v>
@@ -3639,19 +3639,19 @@
         <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000556050365673469</v>
+        <v>0.000513634953433287</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0167858165390371</v>
+        <v>0.0163887856590667</v>
       </c>
       <c r="G47" t="n">
-        <v>0.000550054096063248</v>
+        <v>0.000515061057736428</v>
       </c>
       <c r="H47" t="n">
-        <v>0.016849816265974</v>
+        <v>0.0164191249369147</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.0901236175017</v>
+        <v>0.276880630309853</v>
       </c>
       <c r="J47" t="n">
         <v>143</v>
@@ -3671,19 +3671,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000509390063673173</v>
+        <v>0.000512420613474496</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0164130757187827</v>
+        <v>0.0165023326369671</v>
       </c>
       <c r="G48" t="n">
-        <v>0.000531996674448781</v>
+        <v>0.00051253702683908</v>
       </c>
       <c r="H48" t="n">
-        <v>0.016530264480168</v>
+        <v>0.0165034993382382</v>
       </c>
       <c r="I48" t="n">
-        <v>4.24938949083299</v>
+        <v>0.0227131618767188</v>
       </c>
       <c r="J48" t="n">
         <v>143</v>
@@ -3703,19 +3703,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000576469413019139</v>
+        <v>0.000515500557734305</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0176219863100532</v>
+        <v>0.0163775155955427</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0005513104399593</v>
+        <v>0.000516327501169937</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0168826766920618</v>
+        <v>0.0164027625450333</v>
       </c>
       <c r="I49" t="n">
-        <v>-4.56348569450207</v>
+        <v>0.160158704263957</v>
       </c>
       <c r="J49" t="n">
         <v>143</v>
@@ -3735,19 +3735,19 @@
         <v>45</v>
       </c>
       <c r="E50" t="n">
-        <v>0.000420890379375277</v>
+        <v>0.000259075197226633</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0159627905299692</v>
+        <v>0.0121467247127419</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00028108105450633</v>
+        <v>0.000259594127605636</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0128032922190265</v>
+        <v>0.0121257200722259</v>
       </c>
       <c r="I50" t="n">
-        <v>-49.7398606656349</v>
+        <v>0.199900661771232</v>
       </c>
       <c r="J50" t="n">
         <v>59</v>
@@ -3767,19 +3767,19 @@
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000260482181928622</v>
+        <v>0.000256387712229557</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0123032069621714</v>
+        <v>0.012046976225777</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000267026517801658</v>
+        <v>0.000256439953420989</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0123546488861435</v>
+        <v>0.0120476809335599</v>
       </c>
       <c r="I51" t="n">
-        <v>2.45081871527699</v>
+        <v>0.0203717052414264</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -3799,19 +3799,19 @@
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000317399918252121</v>
+        <v>0.000259161899672062</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0140867486566905</v>
+        <v>0.0121223043326171</v>
       </c>
       <c r="G52" t="n">
-        <v>0.000274294887771454</v>
+        <v>0.000259258311222197</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0125742679007307</v>
+        <v>0.0121315531126409</v>
       </c>
       <c r="I52" t="n">
-        <v>-15.7148501129132</v>
+        <v>0.0371874481787432</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -3831,19 +3831,19 @@
         <v>45</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000209516796399268</v>
+        <v>0.000162387417615191</v>
       </c>
       <c r="F53" t="n">
-        <v>0.00931266488520251</v>
+        <v>0.00771083590853</v>
       </c>
       <c r="G53" t="n">
-        <v>0.000312790997410662</v>
+        <v>0.000162216879884625</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0117982214882979</v>
+        <v>0.00770719465294139</v>
       </c>
       <c r="I53" t="n">
-        <v>33.0169991675963</v>
+        <v>-0.1051294604401</v>
       </c>
       <c r="J53" t="n">
         <v>1356</v>
@@ -3863,19 +3863,19 @@
         <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000162484789235042</v>
+        <v>0.000163090445932847</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00777145286340774</v>
+        <v>0.00777030568950593</v>
       </c>
       <c r="G54" t="n">
-        <v>0.000330880268737716</v>
+        <v>0.000163193764237668</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0122156513465442</v>
+        <v>0.00777158450559627</v>
       </c>
       <c r="I54" t="n">
-        <v>50.8931765998288</v>
+        <v>0.063310203856969</v>
       </c>
       <c r="J54" t="n">
         <v>1356</v>
@@ -3895,19 +3895,19 @@
         <v>47</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000216465081450478</v>
+        <v>0.000162365700272085</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0100658251387201</v>
+        <v>0.00770775530677447</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000311529549216292</v>
+        <v>0.000162161556343121</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0117797267913513</v>
+        <v>0.00770914884765274</v>
       </c>
       <c r="I55" t="n">
-        <v>30.5153934851336</v>
+        <v>-0.125889226501892</v>
       </c>
       <c r="J55" t="n">
         <v>1356</v>
@@ -3927,19 +3927,19 @@
         <v>45</v>
       </c>
       <c r="E56" t="n">
-        <v>0.000326441918426816</v>
+        <v>0.000281953746038375</v>
       </c>
       <c r="F56" t="n">
-        <v>0.00946015751057124</v>
+        <v>0.00784839686136849</v>
       </c>
       <c r="G56" t="n">
-        <v>0.000433427030264193</v>
+        <v>0.000281571714960163</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0119457141136666</v>
+        <v>0.00784888747889857</v>
       </c>
       <c r="I56" t="n">
-        <v>24.6835347975794</v>
+        <v>-0.135678073440989</v>
       </c>
       <c r="J56" t="n">
         <v>1356</v>
@@ -3959,19 +3959,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000281711591138534</v>
+        <v>0.000283168488724989</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00791894548877647</v>
+        <v>0.00792060821505393</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000451526384420775</v>
+        <v>0.000282785382435605</v>
       </c>
       <c r="H57" t="n">
-        <v>0.012363143971913</v>
+        <v>0.0079191046915603</v>
       </c>
       <c r="I57" t="n">
-        <v>37.6090521266176</v>
+        <v>-0.135475987508478</v>
       </c>
       <c r="J57" t="n">
         <v>1356</v>
@@ -3991,19 +3991,19 @@
         <v>47</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000328738557390183</v>
+        <v>0.000281842886108609</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0102133177640888</v>
+        <v>0.00785243779506888</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00043187382078764</v>
+        <v>0.000281618324319048</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01192721941672</v>
+        <v>0.00785159540277762</v>
       </c>
       <c r="I58" t="n">
-        <v>23.8808787273471</v>
+        <v>-0.0797397648408809</v>
       </c>
       <c r="J58" t="n">
         <v>1356</v>
@@ -4023,19 +4023,19 @@
         <v>45</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000144740390148402</v>
+        <v>0.000093650537012908</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00909514743705313</v>
+        <v>0.00749000546595306</v>
       </c>
       <c r="G59" t="n">
-        <v>0.000242541857515252</v>
+        <v>0.0000936083195331897</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0115807040401485</v>
+        <v>0.00749222813993131</v>
       </c>
       <c r="I59" t="n">
-        <v>40.3235418285273</v>
+        <v>-0.0451001363220467</v>
       </c>
       <c r="J59" t="n">
         <v>1356</v>
@@ -4055,19 +4055,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000943139384699477</v>
+        <v>0.0000941131161883826</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00755393541525836</v>
+        <v>0.00755450332212559</v>
       </c>
       <c r="G60" t="n">
-        <v>0.000260616259004959</v>
+        <v>0.0000940820034171474</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0119981338983949</v>
+        <v>0.0075531979911619</v>
       </c>
       <c r="I60" t="n">
-        <v>63.8111839875066</v>
+        <v>-0.033069843439938</v>
       </c>
       <c r="J60" t="n">
         <v>1356</v>
@@ -4087,19 +4087,19 @@
         <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>0.000158548775385584</v>
+        <v>0.0000935582587996006</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00986946783253966</v>
+        <v>0.00748673256073213</v>
       </c>
       <c r="G61" t="n">
-        <v>0.000241710689610561</v>
+        <v>0.0000938058467000785</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0115622093432019</v>
+        <v>0.00750256257840865</v>
       </c>
       <c r="I61" t="n">
-        <v>34.4055591248221</v>
+        <v>0.263936534008903</v>
       </c>
       <c r="J61" t="n">
         <v>1356</v>
@@ -4119,19 +4119,19 @@
         <v>45</v>
       </c>
       <c r="E62" t="n">
-        <v>0.000144769757721335</v>
+        <v>0.0000937892842699788</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00909886892695685</v>
+        <v>0.00749913675084782</v>
       </c>
       <c r="G62" t="n">
-        <v>0.000242664857682614</v>
+        <v>0.000093703895094768</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0115844255300522</v>
+        <v>0.00749744734017311</v>
       </c>
       <c r="I62" t="n">
-        <v>40.341688078015</v>
+        <v>-0.0911266016470713</v>
       </c>
       <c r="J62" t="n">
         <v>1356</v>
@@ -4151,19 +4151,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000944013813425672</v>
+        <v>0.0000942545915039134</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00755765690516207</v>
+        <v>0.00755899640407504</v>
       </c>
       <c r="G63" t="n">
-        <v>0.000260739513579266</v>
+        <v>0.0000942251996567323</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0120018553882986</v>
+        <v>0.00755813979959274</v>
       </c>
       <c r="I63" t="n">
-        <v>63.7947543712554</v>
+        <v>-0.0311931917237968</v>
       </c>
       <c r="J63" t="n">
         <v>1356</v>
@@ -4183,19 +4183,19 @@
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000158460774012725</v>
+        <v>0.000093784760405989</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00986574634263594</v>
+        <v>0.00749224168741644</v>
       </c>
       <c r="G64" t="n">
-        <v>0.000241826328144328</v>
+        <v>0.0000939409172444899</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0115659308331056</v>
+        <v>0.00750530345037232</v>
       </c>
       <c r="I64" t="n">
-        <v>34.4733159417813</v>
+        <v>0.166228777705527</v>
       </c>
       <c r="J64" t="n">
         <v>1356</v>
@@ -4215,19 +4215,19 @@
         <v>45</v>
       </c>
       <c r="E65" t="n">
-        <v>0.000256099841787</v>
+        <v>0.000210915795851206</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0128739722949922</v>
+        <v>0.0120824872299155</v>
       </c>
       <c r="G65" t="n">
-        <v>0.000403994715789486</v>
+        <v>0.000210723521187492</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0156500939501962</v>
+        <v>0.0120821328586473</v>
       </c>
       <c r="I65" t="n">
-        <v>36.6081209041237</v>
+        <v>-0.0912449937385992</v>
       </c>
       <c r="J65" t="n">
         <v>904</v>
@@ -4247,19 +4247,19 @@
         <v>46</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000226936695689189</v>
+        <v>0.000226771873595338</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126548410435967</v>
+        <v>0.0126567783717109</v>
       </c>
       <c r="G66" t="n">
-        <v>0.000397975554644745</v>
+        <v>0.00022673317812646</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0155526717755929</v>
+        <v>0.0126563933660829</v>
       </c>
       <c r="I66" t="n">
-        <v>42.977227359664</v>
+        <v>-0.0170665225080432</v>
       </c>
       <c r="J66" t="n">
         <v>904</v>
@@ -4279,19 +4279,19 @@
         <v>47</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000278057912846305</v>
+        <v>0.000209598483836291</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0136484744795844</v>
+        <v>0.0120244544670814</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000404615433846274</v>
+        <v>0.000209235213268818</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0156658902000642</v>
+        <v>0.0120262433067877</v>
       </c>
       <c r="I67" t="n">
-        <v>31.2784709661007</v>
+        <v>-0.173618274762424</v>
       </c>
       <c r="J67" t="n">
         <v>904</v>
@@ -4311,19 +4311,19 @@
         <v>45</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00485476491096186</v>
+        <v>0.00358831963302271</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0559198621875515</v>
+        <v>0.049352249036705</v>
       </c>
       <c r="G68" t="n">
-        <v>0.00385100225626609</v>
+        <v>0.00358854016147951</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0502176849755694</v>
+        <v>0.0493736119703092</v>
       </c>
       <c r="I68" t="n">
-        <v>-26.0649718670642</v>
+        <v>0.00614535289769085</v>
       </c>
       <c r="J68" t="n">
         <v>143</v>
@@ -4343,19 +4343,19 @@
         <v>46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00359502508773665</v>
+        <v>0.00359372246920314</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493967352119226</v>
+        <v>0.0493701156250663</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00378278415584369</v>
+        <v>0.00359246003044369</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0499573680231899</v>
+        <v>0.0493534074943766</v>
       </c>
       <c r="I69" t="n">
-        <v>4.96351524093681</v>
+        <v>-0.0351413446150215</v>
       </c>
       <c r="J69" t="n">
         <v>143</v>
@@ -4375,19 +4375,19 @@
         <v>47</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00409439837896595</v>
+        <v>0.00357941998493728</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0522119540095549</v>
+        <v>0.0493382234908209</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00383979907176212</v>
+        <v>0.00357620020383322</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0501822976079199</v>
+        <v>0.0492959819944264</v>
       </c>
       <c r="I70" t="n">
-        <v>-6.63053723503782</v>
+        <v>-0.0900335809111892</v>
       </c>
       <c r="J70" t="n">
         <v>143</v>
@@ -4407,19 +4407,19 @@
         <v>45</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00748645286197498</v>
+        <v>0.00346619295684648</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0599965585758948</v>
+        <v>0.045522417557489</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00381240336070278</v>
+        <v>0.0034569158472051</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0465621612053509</v>
+        <v>0.0454668090346793</v>
       </c>
       <c r="I71" t="n">
-        <v>-96.3709543209226</v>
+        <v>-0.26836376849837</v>
       </c>
       <c r="J71" t="n">
         <v>59</v>
@@ -4439,19 +4439,19 @@
         <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>734700142238945</v>
+        <v>164973292377.312</v>
       </c>
       <c r="F72" t="n">
-        <v>3536088.50144429</v>
+        <v>52891.6448218613</v>
       </c>
       <c r="G72" t="n">
-        <v>683473306874205952</v>
+        <v>14280204136.97</v>
       </c>
       <c r="H72" t="n">
-        <v>111320949.59593</v>
+        <v>15585.1734490631</v>
       </c>
       <c r="I72" t="n">
-        <v>99.8925049252327</v>
+        <v>-1055.25864192804</v>
       </c>
       <c r="J72" t="n">
         <v>59</v>
@@ -4471,19 +4471,19 @@
         <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00358777915912415</v>
+        <v>0.00346451598006494</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0470630078299815</v>
+        <v>0.0454618197385731</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00374329014461856</v>
+        <v>0.00346841488231196</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0461813385621833</v>
+        <v>0.0455020007603141</v>
       </c>
       <c r="I73" t="n">
-        <v>4.15439304692902</v>
+        <v>0.112411645645508</v>
       </c>
       <c r="J73" t="n">
         <v>59</v>
@@ -4503,19 +4503,19 @@
         <v>47</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00343863465896731</v>
+        <v>0.00347175170535522</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0444839095579722</v>
+        <v>0.0455466503000288</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00359492075854226</v>
+        <v>0.00348447291649426</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0455432845826272</v>
+        <v>0.0456351055023932</v>
       </c>
       <c r="I74" t="n">
-        <v>4.3474143123621</v>
+        <v>0.365082795702598</v>
       </c>
       <c r="J74" t="n">
         <v>59</v>
@@ -4535,19 +4535,19 @@
         <v>45</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0016219827326845</v>
+        <v>0.00126814074662105</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0292101682227151</v>
+        <v>0.0253224037176126</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00263679652120027</v>
+        <v>0.00126830098205465</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0381378111641497</v>
+        <v>0.0253008155919592</v>
       </c>
       <c r="I75" t="n">
-        <v>38.4866173918428</v>
+        <v>0.0126338649793709</v>
       </c>
       <c r="J75" t="n">
         <v>1356</v>
@@ -4567,19 +4567,19 @@
         <v>48</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00288992326088907</v>
+        <v>0.00126737962284537</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0322079600146473</v>
+        <v>0.0253396543796739</v>
       </c>
       <c r="G76" t="n">
-        <v>0.00338537724287846</v>
+        <v>0.0476740802699269</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0430818689718989</v>
+        <v>0.086950006724609</v>
       </c>
       <c r="I76" t="n">
-        <v>14.6351188196718</v>
+        <v>97.3415750955874</v>
       </c>
       <c r="J76" t="n">
         <v>1356</v>
@@ -4599,19 +4599,19 @@
         <v>46</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00127657322845217</v>
+        <v>0.00126790280520765</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0253044396117033</v>
+        <v>0.0252632634526161</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00253531254414684</v>
+        <v>0.00126869256733436</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0372320840190633</v>
+        <v>0.0252667249380251</v>
       </c>
       <c r="I77" t="n">
-        <v>49.6482896596186</v>
+        <v>0.062250079100793</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4631,19 +4631,19 @@
         <v>47</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00139438947680937</v>
+        <v>0.00126871855780403</v>
       </c>
       <c r="F78" t="n">
-        <v>0.026772456292686</v>
+        <v>0.025350417074483</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00264540859636174</v>
+        <v>0.00126725713720342</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0381622202714385</v>
+        <v>0.0253373841693409</v>
       </c>
       <c r="I78" t="n">
-        <v>47.290203913033</v>
+        <v>-0.115321552169981</v>
       </c>
       <c r="J78" t="n">
         <v>1356</v>
@@ -4663,19 +4663,19 @@
         <v>45</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00175024940387552</v>
+        <v>0.00139747804311291</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0293576608480838</v>
+        <v>0.0254540198754749</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00276888095802158</v>
+        <v>0.00139650843874228</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0382853037895185</v>
+        <v>0.0254599863261398</v>
       </c>
       <c r="I79" t="n">
-        <v>36.7885643907888</v>
+        <v>-0.0694306130723901</v>
       </c>
       <c r="J79" t="n">
         <v>1356</v>
@@ -4695,19 +4695,19 @@
         <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00300201472520252</v>
+        <v>0.00139923667934089</v>
       </c>
       <c r="F80" t="n">
-        <v>0.032355452640016</v>
+        <v>0.0254945276878685</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00352000526075389</v>
+        <v>0.0401467513215883</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0432293615972677</v>
+        <v>0.084425542768168</v>
       </c>
       <c r="I80" t="n">
-        <v>14.7156182215599</v>
+        <v>96.5146951290465</v>
       </c>
       <c r="J80" t="n">
         <v>1356</v>
@@ -4727,19 +4727,19 @@
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00141164001676363</v>
+        <v>0.00139762228241484</v>
       </c>
       <c r="F81" t="n">
-        <v>0.025451932237072</v>
+        <v>0.0254116454194006</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00266748451175617</v>
+        <v>0.00139797367528815</v>
       </c>
       <c r="H81" t="n">
-        <v>0.037379576644432</v>
+        <v>0.0254136981068695</v>
       </c>
       <c r="I81" t="n">
-        <v>47.0797295900978</v>
+        <v>0.0251358719782645</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4759,19 +4759,19 @@
         <v>47</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00153534739473891</v>
+        <v>0.00139727300982023</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0269199489180547</v>
+        <v>0.0254941635545517</v>
       </c>
       <c r="G82" t="n">
-        <v>0.002780911669261</v>
+        <v>0.00139822107399483</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0383097128968073</v>
+        <v>0.0255160695676328</v>
       </c>
       <c r="I82" t="n">
-        <v>44.7897820089009</v>
+        <v>0.0678050268466785</v>
       </c>
       <c r="J82" t="n">
         <v>1356</v>
@@ -4791,19 +4791,19 @@
         <v>45</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00154312988396053</v>
+        <v>0.00118665269433373</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0290163383312944</v>
+        <v>0.0251061204978485</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00255292649215465</v>
+        <v>0.00118703387208131</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0379439812727291</v>
+        <v>0.0251184418312433</v>
       </c>
       <c r="I83" t="n">
-        <v>39.5544725356294</v>
+        <v>0.0321117835429696</v>
       </c>
       <c r="J83" t="n">
         <v>1356</v>
@@ -4823,19 +4823,19 @@
         <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00283232732982418</v>
+        <v>0.0011909338917502</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0320141301232266</v>
+        <v>0.0251811060622614</v>
       </c>
       <c r="G84" t="n">
-        <v>0.00329816452440475</v>
+        <v>0.077263352385427</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0428880390804783</v>
+        <v>0.0936994652377659</v>
       </c>
       <c r="I84" t="n">
-        <v>14.1241345340298</v>
+        <v>98.4586044289028</v>
       </c>
       <c r="J84" t="n">
         <v>1356</v>
@@ -4855,19 +4855,19 @@
         <v>46</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118878389249837</v>
+        <v>0.00118765357717191</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0251106097202826</v>
+        <v>0.0250722273406622</v>
       </c>
       <c r="G85" t="n">
-        <v>0.00245132748505754</v>
+        <v>0.00118744332279492</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0370382541276426</v>
+        <v>0.0250709158498084</v>
       </c>
       <c r="I85" t="n">
-        <v>51.5044848252715</v>
+        <v>-0.0177064768445678</v>
       </c>
       <c r="J85" t="n">
         <v>1356</v>
@@ -4887,19 +4887,19 @@
         <v>47</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00129885821469916</v>
+        <v>0.00118934171838292</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0265786264012653</v>
+        <v>0.0251559367898753</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0025570459097467</v>
+        <v>0.00118910353401773</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0379683903800178</v>
+        <v>0.0251537757484337</v>
       </c>
       <c r="I86" t="n">
-        <v>49.2047362251768</v>
+        <v>-0.0200305825676022</v>
       </c>
       <c r="J86" t="n">
         <v>1356</v>
@@ -4919,19 +4919,19 @@
         <v>45</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00154809497882729</v>
+        <v>0.00119471316276271</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0290437473779268</v>
+        <v>0.0251767449313413</v>
       </c>
       <c r="G87" t="n">
-        <v>0.00255860105514519</v>
+        <v>0.00119335871728846</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0379713903193615</v>
+        <v>0.0251405650844172</v>
       </c>
       <c r="I87" t="n">
-        <v>39.4944758693753</v>
+        <v>-0.113498603112869</v>
       </c>
       <c r="J87" t="n">
         <v>1356</v>
@@ -4951,19 +4951,19 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00283428653203367</v>
+        <v>0.00119384242110496</v>
       </c>
       <c r="F88" t="n">
-        <v>0.032041539169859</v>
+        <v>0.0251674930444885</v>
       </c>
       <c r="G88" t="n">
-        <v>0.00330431176954839</v>
+        <v>0.0549912899133693</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0429154481271107</v>
+        <v>0.0836052192825909</v>
       </c>
       <c r="I88" t="n">
-        <v>14.2246031941156</v>
+        <v>97.8290336106215</v>
       </c>
       <c r="J88" t="n">
         <v>1356</v>
@@ -4983,19 +4983,19 @@
         <v>46</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00119501267581595</v>
+        <v>0.00119267366317441</v>
       </c>
       <c r="F89" t="n">
-        <v>0.025138018766915</v>
+        <v>0.0250987995034159</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00245701831418644</v>
+        <v>0.00119290067715493</v>
       </c>
       <c r="H89" t="n">
-        <v>0.037065663174275</v>
+        <v>0.025099507536383</v>
       </c>
       <c r="I89" t="n">
-        <v>51.3632979894315</v>
+        <v>0.0190304176089771</v>
       </c>
       <c r="J89" t="n">
         <v>1356</v>
@@ -5015,19 +5015,19 @@
         <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00130618176628747</v>
+        <v>0.00119424778728295</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0266060354478977</v>
+        <v>0.0251954808661812</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00256335576928475</v>
+        <v>0.00119378244991306</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0379957994266503</v>
+        <v>0.0251905143398555</v>
       </c>
       <c r="I90" t="n">
-        <v>49.0440702013076</v>
+        <v>-0.0389800813305539</v>
       </c>
       <c r="J90" t="n">
         <v>1356</v>
@@ -5047,19 +5047,19 @@
         <v>45</v>
       </c>
       <c r="E91" t="n">
-        <v>0.00149196403265601</v>
+        <v>0.00106108860116156</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0277274823493627</v>
+        <v>0.0228016195775198</v>
       </c>
       <c r="G91" t="n">
-        <v>0.00285185203003691</v>
+        <v>0.00105968350556643</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0385599327736465</v>
+        <v>0.0227512079558229</v>
       </c>
       <c r="I91" t="n">
-        <v>47.684381344403</v>
+        <v>-0.132595778621249</v>
       </c>
       <c r="J91" t="n">
         <v>904</v>
@@ -5079,19 +5079,19 @@
         <v>46</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00107352397055155</v>
+        <v>0.0010758857086025</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230408675039497</v>
+        <v>0.0230213549370511</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00273641830210051</v>
+        <v>0.00107583566575547</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0374694524309948</v>
+        <v>0.0230232013750546</v>
       </c>
       <c r="I92" t="n">
-        <v>60.7690107273622</v>
+        <v>-0.00465153262938542</v>
       </c>
       <c r="J92" t="n">
         <v>904</v>
@@ -5111,19 +5111,19 @@
         <v>47</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00115599700211062</v>
+        <v>0.00105092433122067</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0243987542495274</v>
+        <v>0.0226246196536464</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00258416312401812</v>
+        <v>0.00105106800880114</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0365453685073359</v>
+        <v>0.0226222921257745</v>
       </c>
       <c r="I93" t="n">
-        <v>55.2660978958186</v>
+        <v>0.013669674965221</v>
       </c>
       <c r="J93" t="n">
         <v>904</v>
@@ -5143,19 +5143,19 @@
         <v>45</v>
       </c>
       <c r="E94" t="n">
-        <v>0.00182795519587862</v>
+        <v>0.00165845108229663</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0327918001764892</v>
+        <v>0.0306081458789955</v>
       </c>
       <c r="G94" t="n">
-        <v>0.00173007537746993</v>
+        <v>0.00166243846658631</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0317794961965484</v>
+        <v>0.0306598247835027</v>
       </c>
       <c r="I94" t="n">
-        <v>-5.65754646782057</v>
+        <v>0.23985154156494</v>
       </c>
       <c r="J94" t="n">
         <v>143</v>
@@ -5175,19 +5175,19 @@
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00168024133668274</v>
+        <v>0.0016747977302822</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0309507950457873</v>
+        <v>0.0308221842130781</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0017565286796778</v>
+        <v>0.00167471172799621</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0321060024949954</v>
+        <v>0.030815115252802</v>
       </c>
       <c r="I95" t="n">
-        <v>4.34307414832796</v>
+        <v>-0.005135348642522</v>
       </c>
       <c r="J95" t="n">
         <v>143</v>
@@ -5207,19 +5207,19 @@
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00169016647840709</v>
+        <v>0.00166345829012489</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0316935371019174</v>
+        <v>0.0306345735104619</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00172525893052165</v>
+        <v>0.00166549116584759</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0317189261617256</v>
+        <v>0.0306791271618645</v>
       </c>
       <c r="I96" t="n">
-        <v>2.03403973129713</v>
+        <v>0.122058631374667</v>
       </c>
       <c r="J96" t="n">
         <v>143</v>
@@ -5239,19 +5239,19 @@
         <v>45</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0027273074213395</v>
+        <v>0.0022086031825195</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0392693161868151</v>
+        <v>0.0350079796666746</v>
       </c>
       <c r="G97" t="n">
-        <v>0.00214112976167384</v>
+        <v>0.00221661493946969</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0348499281950622</v>
+        <v>0.0350961492671635</v>
       </c>
       <c r="I97" t="n">
-        <v>-27.3770263791678</v>
+        <v>0.361441078806009</v>
       </c>
       <c r="J97" t="n">
         <v>59</v>
@@ -5271,19 +5271,19 @@
         <v>46</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00221123024898648</v>
+        <v>0.00221583433755109</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0351223466626641</v>
+        <v>0.0350624018790841</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00214161421595604</v>
+        <v>0.00221509688720289</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0348338665005722</v>
+        <v>0.0350428452614733</v>
       </c>
       <c r="I98" t="n">
-        <v>-3.25063368144334</v>
+        <v>-0.0332920132053774</v>
       </c>
       <c r="J98" t="n">
         <v>59</v>
@@ -5303,19 +5303,19 @@
         <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00223339247494314</v>
+        <v>0.00221931495735858</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0363845012398214</v>
+        <v>0.0350702991969525</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00214606847390455</v>
+        <v>0.00221846812942584</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0348823262051082</v>
+        <v>0.0350930821033542</v>
       </c>
       <c r="I99" t="n">
-        <v>-4.06902212582771</v>
+        <v>-0.03817174209104</v>
       </c>
       <c r="J99" t="n">
         <v>59</v>
@@ -5335,19 +5335,19 @@
         <v>45</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000501400487938108</v>
+        <v>0.000439493721144453</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0155983853190011</v>
+        <v>0.0138083178066177</v>
       </c>
       <c r="G100" t="n">
-        <v>0.000807570718953943</v>
+        <v>0.000439854421840459</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0199077316434905</v>
+        <v>0.0138251144451137</v>
       </c>
       <c r="I100" t="n">
-        <v>37.9124977949202</v>
+        <v>0.0820045628952869</v>
       </c>
       <c r="J100" t="n">
         <v>1356</v>
@@ -5367,19 +5367,19 @@
         <v>46</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000441216693958818</v>
+        <v>0.000439372612740038</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0138141814984548</v>
+        <v>0.0138085522023891</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000825036854744102</v>
+        <v>0.000439932837548017</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0201764093012488</v>
+        <v>0.013813507073151</v>
       </c>
       <c r="I101" t="n">
-        <v>46.5215776214423</v>
+        <v>0.127343257916698</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5399,19 +5399,19 @@
         <v>47</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000466645080847626</v>
+        <v>0.000440227741137358</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0149171974457808</v>
+        <v>0.0138392780569769</v>
       </c>
       <c r="G102" t="n">
-        <v>0.00080546917926962</v>
+        <v>0.000439889037385186</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0199067480401192</v>
+        <v>0.0138201674235698</v>
       </c>
       <c r="I102" t="n">
-        <v>42.0654330596773</v>
+        <v>-0.076997543331736</v>
       </c>
       <c r="J102" t="n">
         <v>1356</v>
@@ -5431,19 +5431,19 @@
         <v>45</v>
       </c>
       <c r="E103" t="n">
-        <v>0.000602356981550879</v>
+        <v>0.000559170442558627</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0157458779443698</v>
+        <v>0.0139902568196337</v>
       </c>
       <c r="G103" t="n">
-        <v>0.000929497609839179</v>
+        <v>0.000558716114995292</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0200552242688592</v>
+        <v>0.0139783759557194</v>
       </c>
       <c r="I103" t="n">
-        <v>35.195424369612</v>
+        <v>-0.0813163521044881</v>
       </c>
       <c r="J103" t="n">
         <v>1356</v>
@@ -5463,19 +5463,19 @@
         <v>46</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000560709493739727</v>
+        <v>0.000557490577643694</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139616741238235</v>
+        <v>0.0139575795695807</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000946231072092032</v>
+        <v>0.000557542241815354</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0203239019266176</v>
+        <v>0.013957339772375</v>
       </c>
       <c r="I104" t="n">
-        <v>40.7428576087606</v>
+        <v>0.00926641387605065</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5495,19 +5495,19 @@
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000571386211561908</v>
+        <v>0.00055751307365491</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0150646900711495</v>
+        <v>0.0139653203313397</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000926088160426024</v>
+        <v>0.000557596869377783</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0200542406654879</v>
+        <v>0.0139731596377678</v>
       </c>
       <c r="I105" t="n">
-        <v>38.301099616795</v>
+        <v>0.0150280117185506</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5527,19 +5527,19 @@
         <v>45</v>
       </c>
       <c r="E106" t="n">
-        <v>0.000460427888688699</v>
+        <v>0.000371895565795647</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0154609499446772</v>
+        <v>0.0135897678788862</v>
       </c>
       <c r="G106" t="n">
-        <v>0.00073533936671709</v>
+        <v>0.000372624597465856</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0196878771751192</v>
+        <v>0.0136089745245126</v>
       </c>
       <c r="I106" t="n">
-        <v>37.3856603456073</v>
+        <v>0.195647757868694</v>
       </c>
       <c r="J106" t="n">
         <v>1356</v>
@@ -5559,19 +5559,19 @@
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.00037261363028467</v>
+        <v>0.000372242456245276</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0135943270300836</v>
+        <v>0.0135937467540886</v>
       </c>
       <c r="G107" t="n">
-        <v>0.000753897635423257</v>
+        <v>0.000372215449220261</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0199565548328776</v>
+        <v>0.0135938511228356</v>
       </c>
       <c r="I107" t="n">
-        <v>50.575036612832</v>
+        <v>-0.00725575068721788</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5591,19 +5591,19 @@
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000420031051215847</v>
+        <v>0.000372775603828952</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0147608388859493</v>
+        <v>0.0136278137891505</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000735187414663951</v>
+        <v>0.000372350386067935</v>
       </c>
       <c r="H108" t="n">
-        <v>0.019686893571748</v>
+        <v>0.0136145057252948</v>
       </c>
       <c r="I108" t="n">
-        <v>42.8674861895126</v>
+        <v>-0.114198286594205</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5623,19 +5623,19 @@
         <v>45</v>
       </c>
       <c r="E109" t="n">
-        <v>0.000460275759074983</v>
+        <v>0.000372037680607373</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0154595654749953</v>
+        <v>0.0136058231189924</v>
       </c>
       <c r="G109" t="n">
-        <v>0.000735384080024626</v>
+        <v>0.000372665297104605</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0196892616448011</v>
+        <v>0.0136080196892962</v>
       </c>
       <c r="I109" t="n">
-        <v>37.4101545603803</v>
+        <v>0.168412916927802</v>
       </c>
       <c r="J109" t="n">
         <v>1356</v>
@@ -5655,19 +5655,19 @@
         <v>46</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000372635495498422</v>
+        <v>0.000372178470069345</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0135957114997655</v>
+        <v>0.0135939806715859</v>
       </c>
       <c r="G110" t="n">
-        <v>0.000753935471340845</v>
+        <v>0.000372098558584909</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0199579393025595</v>
+        <v>0.013591277479007</v>
       </c>
       <c r="I110" t="n">
-        <v>50.5746168387986</v>
+        <v>-0.0214758919625895</v>
       </c>
       <c r="J110" t="n">
         <v>1356</v>
@@ -5687,19 +5687,19 @@
         <v>47</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000419914446872027</v>
+        <v>0.000372353989403331</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0147594544162674</v>
+        <v>0.0136134716016774</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000735219851009424</v>
+        <v>0.000372454111679961</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0196882780414298</v>
+        <v>0.0136155275231696</v>
       </c>
       <c r="I111" t="n">
-        <v>42.8858665478763</v>
+        <v>0.0268817750939161</v>
       </c>
       <c r="J111" t="n">
         <v>1356</v>
@@ -5719,19 +5719,19 @@
         <v>45</v>
       </c>
       <c r="E112" t="n">
-        <v>0.000556976662982256</v>
+        <v>0.000430247083492509</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0169489803740928</v>
+        <v>0.0144986640399565</v>
       </c>
       <c r="G112" t="n">
-        <v>0.000950515010948565</v>
+        <v>0.000429339663370881</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0211287599650894</v>
+        <v>0.0144881553284123</v>
       </c>
       <c r="I112" t="n">
-        <v>41.4026441911293</v>
+        <v>-0.211352502236495</v>
       </c>
       <c r="J112" t="n">
         <v>904</v>
@@ -5753,10 +5753,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>1768531608388.9</v>
+        <v>2404425827.57745</v>
       </c>
       <c r="H113" t="n">
-        <v>60662.5350541879</v>
+        <v>2441.41900095336</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5777,19 +5777,19 @@
         <v>46</v>
       </c>
       <c r="E114" t="n">
-        <v>0.000475030824112494</v>
+        <v>0.00047481267349847</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0158137921898062</v>
+        <v>0.0158020596421369</v>
       </c>
       <c r="G114" t="n">
-        <v>0.000893115052846344</v>
+        <v>0.000474785434639685</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0204773957244897</v>
+        <v>0.015802429815078</v>
       </c>
       <c r="I114" t="n">
-        <v>46.8119115674315</v>
+        <v>-0.00573708812409808</v>
       </c>
       <c r="J114" t="n">
         <v>904</v>
@@ -5809,19 +5809,19 @@
         <v>47</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000452900106800729</v>
+        <v>0.000426323956195014</v>
       </c>
       <c r="F115" t="n">
-        <v>0.01511371327175</v>
+        <v>0.0143969066963335</v>
       </c>
       <c r="G115" t="n">
-        <v>0.000948842693042261</v>
+        <v>0.000426430494028449</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0211014650212186</v>
+        <v>0.0144006440582725</v>
       </c>
       <c r="I115" t="n">
-        <v>52.268156763836</v>
+        <v>0.024983633892737</v>
       </c>
       <c r="J115" t="n">
         <v>904</v>
@@ -5841,19 +5841,19 @@
         <v>45</v>
       </c>
       <c r="E116" t="n">
-        <v>0.00304336952537612</v>
+        <v>0.00264507419461069</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0419078785036758</v>
+        <v>0.0395668341708678</v>
       </c>
       <c r="G116" t="n">
-        <v>0.00343609047654079</v>
+        <v>0.00264374727335584</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0431945002207375</v>
+        <v>0.0395842296870537</v>
       </c>
       <c r="I116" t="n">
-        <v>11.4292959933939</v>
+        <v>-0.0501909266527926</v>
       </c>
       <c r="J116" t="n">
         <v>143</v>
@@ -5873,19 +5873,19 @@
         <v>46</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265249259145161</v>
+        <v>0.00265430512021248</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0398489481441051</v>
+        <v>0.0397867992543847</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00335032619018976</v>
+        <v>0.00265606610089042</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0428265570563388</v>
+        <v>0.0397978844452308</v>
       </c>
       <c r="I117" t="n">
-        <v>20.8288255866402</v>
+        <v>0.0663003333140252</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5905,19 +5905,19 @@
         <v>47</v>
       </c>
       <c r="E118" t="n">
-        <v>0.00291073655636375</v>
+        <v>0.0026436180559364</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0406406323655378</v>
+        <v>0.0395675236212835</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0034375067249464</v>
+        <v>0.00266118006855168</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0432185949428478</v>
+        <v>0.0396564853719766</v>
       </c>
       <c r="I118" t="n">
-        <v>15.3241931065855</v>
+        <v>0.65993326880865</v>
       </c>
       <c r="J118" t="n">
         <v>143</v>
@@ -5937,19 +5937,19 @@
         <v>45</v>
       </c>
       <c r="E119" t="n">
-        <v>0.00127105199934514</v>
+        <v>0.00109659728499065</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0280532916236113</v>
+        <v>0.0251716101575497</v>
       </c>
       <c r="G119" t="n">
-        <v>0.002049776669016</v>
+        <v>0.0011011767812125</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0322109390321017</v>
+        <v>0.0252106974181872</v>
       </c>
       <c r="I119" t="n">
-        <v>37.9907080338022</v>
+        <v>0.415872937023671</v>
       </c>
       <c r="J119" t="n">
         <v>59</v>
@@ -5971,10 +5971,10 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00325706987894512</v>
+        <v>0.00332991506408016</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0487731170286883</v>
+        <v>0.0495576820432755</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5995,19 +5995,19 @@
         <v>46</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00114272630182692</v>
+        <v>0.00109380089856025</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0256183597323261</v>
+        <v>0.0250853144212491</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00263331395073391</v>
+        <v>0.0010917498849824</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0349598022116142</v>
+        <v>0.0249999291145625</v>
       </c>
       <c r="I121" t="n">
-        <v>56.6050109023863</v>
+        <v>-0.187864785337626</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -6027,19 +6027,19 @@
         <v>47</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0011952008913465</v>
+        <v>0.00109552929555283</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0265416745844629</v>
+        <v>0.0251751710585347</v>
       </c>
       <c r="G122" t="n">
-        <v>0.00146819505729097</v>
+        <v>0.0010996173179241</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0268634058876088</v>
+        <v>0.0252785527858619</v>
       </c>
       <c r="I122" t="n">
-        <v>18.5938622112097</v>
+        <v>0.371767732704645</v>
       </c>
       <c r="J122" t="n">
         <v>59</v>
@@ -6059,19 +6059,19 @@
         <v>45</v>
       </c>
       <c r="E123" t="n">
-        <v>0.000834640060914697</v>
+        <v>0.000583114699007834</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0203156602440779</v>
+        <v>0.0163907440330837</v>
       </c>
       <c r="G123" t="n">
-        <v>0.00149328715761598</v>
+        <v>0.000583629701596443</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0266914786575965</v>
+        <v>0.0164130089692977</v>
       </c>
       <c r="I123" t="n">
-        <v>44.1071962175585</v>
+        <v>0.0882413261697233</v>
       </c>
       <c r="J123" t="n">
         <v>1356</v>
@@ -6091,19 +6091,19 @@
         <v>46</v>
       </c>
       <c r="E124" t="n">
-        <v>0.000592385827291352</v>
+        <v>0.00058577207704044</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164963569444326</v>
+        <v>0.0164477758402155</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00162159938843061</v>
+        <v>0.000585337474035628</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0276969657539496</v>
+        <v>0.0164460564430517</v>
       </c>
       <c r="I124" t="n">
-        <v>63.4690397938135</v>
+        <v>-0.0742482796831417</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -6123,19 +6123,19 @@
         <v>47</v>
       </c>
       <c r="E125" t="n">
-        <v>0.000695978345772829</v>
+        <v>0.000580640319003607</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0185735745112158</v>
+        <v>0.0163772188180764</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0014846285618468</v>
+        <v>0.000581112557127129</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0266212297714026</v>
+        <v>0.0163734630386546</v>
       </c>
       <c r="I125" t="n">
-        <v>53.1210456501612</v>
+        <v>0.0812644844325099</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -6155,19 +6155,19 @@
         <v>45</v>
       </c>
       <c r="E126" t="n">
-        <v>0.00095791899027418</v>
+        <v>0.000701011849004057</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0204631528694467</v>
+        <v>0.0165500009792045</v>
       </c>
       <c r="G126" t="n">
-        <v>0.00161359173085168</v>
+        <v>0.000703590516628169</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0268389712829653</v>
+        <v>0.0165515635423077</v>
       </c>
       <c r="I126" t="n">
-        <v>40.6343641976541</v>
+        <v>0.366501191128925</v>
       </c>
       <c r="J126" t="n">
         <v>1356</v>
@@ -6187,19 +6187,19 @@
         <v>46</v>
       </c>
       <c r="E127" t="n">
-        <v>0.000714478016389551</v>
+        <v>0.000703491137037103</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0166438495698014</v>
+        <v>0.0165951422151892</v>
       </c>
       <c r="G127" t="n">
-        <v>0.00174154205285966</v>
+        <v>0.00070418541068741</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0278444583793183</v>
+        <v>0.0165951031675481</v>
       </c>
       <c r="I127" t="n">
-        <v>58.9744034480041</v>
+        <v>0.0985924501942939</v>
       </c>
       <c r="J127" t="n">
         <v>1356</v>
@@ -6219,19 +6219,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.00081724874693477</v>
+        <v>0.000699943310634201</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0187210671365845</v>
+        <v>0.0165193797318583</v>
       </c>
       <c r="G128" t="n">
-        <v>0.00160416785931435</v>
+        <v>0.000699644450085555</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0267687223967713</v>
+        <v>0.0165256257125</v>
       </c>
       <c r="I128" t="n">
-        <v>49.0546614439667</v>
+        <v>-0.0427160607948698</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -6251,19 +6251,19 @@
         <v>45</v>
       </c>
       <c r="E129" t="n">
-        <v>0.000760349947994583</v>
+        <v>0.00051561448815992</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0200946649926265</v>
+        <v>0.0161707100818756</v>
       </c>
       <c r="G129" t="n">
-        <v>0.00142345366466475</v>
+        <v>0.000516400009244666</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0264704834061451</v>
+        <v>0.0161947442356071</v>
       </c>
       <c r="I129" t="n">
-        <v>46.5841448254193</v>
+        <v>0.15211484715015</v>
       </c>
       <c r="J129" t="n">
         <v>1356</v>
@@ -6283,19 +6283,19 @@
         <v>46</v>
       </c>
       <c r="E130" t="n">
-        <v>0.000519873864036648</v>
+        <v>0.000518336549636704</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0162753616929812</v>
+        <v>0.0162281209096157</v>
       </c>
       <c r="G130" t="n">
-        <v>0.00155230816074539</v>
+        <v>0.000518131388393137</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0274759705024981</v>
+        <v>0.016225891041967</v>
       </c>
       <c r="I130" t="n">
-        <v>66.5096224330216</v>
+        <v>-0.039596374232995</v>
       </c>
       <c r="J130" t="n">
         <v>1356</v>
@@ -6315,19 +6315,19 @@
         <v>47</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000624697706668463</v>
+        <v>0.000513712075162741</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0183525792597643</v>
+        <v>0.0161503679252733</v>
       </c>
       <c r="G131" t="n">
-        <v>0.00141594171816286</v>
+        <v>0.000514671814590104</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0264002345199511</v>
+        <v>0.0161581125851082</v>
       </c>
       <c r="I131" t="n">
-        <v>55.8811144092154</v>
+        <v>0.186476002795646</v>
       </c>
       <c r="J131" t="n">
         <v>1356</v>
@@ -6347,19 +6347,19 @@
         <v>45</v>
       </c>
       <c r="E132" t="n">
-        <v>0.000760358921134274</v>
+        <v>0.0005164595300636</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0200949086792281</v>
+        <v>0.0162013589034783</v>
       </c>
       <c r="G132" t="n">
-        <v>0.00142345772358765</v>
+        <v>0.000516404958274734</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0264707270927467</v>
+        <v>0.0161907914102341</v>
       </c>
       <c r="I132" t="n">
-        <v>46.5836667619546</v>
+        <v>-0.0105676345650642</v>
       </c>
       <c r="J132" t="n">
         <v>1356</v>
@@ -6379,19 +6379,19 @@
         <v>46</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000519880876449824</v>
+        <v>0.000518164540278918</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0162756053795828</v>
+        <v>0.016227675782918</v>
       </c>
       <c r="G133" t="n">
-        <v>0.00155231162172431</v>
+        <v>0.00051797644827207</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0274762141890998</v>
+        <v>0.0162213557028169</v>
       </c>
       <c r="I133" t="n">
-        <v>66.5092453619371</v>
+        <v>-0.0363128492571698</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6411,19 +6411,19 @@
         <v>47</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000624703361327589</v>
+        <v>0.000514147577262644</v>
       </c>
       <c r="F134" t="n">
-        <v>0.018352822946366</v>
+        <v>0.0161578907158738</v>
       </c>
       <c r="G134" t="n">
-        <v>0.00141594451270085</v>
+        <v>0.000513996383004751</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0264004782065528</v>
+        <v>0.0161581364752911</v>
       </c>
       <c r="I134" t="n">
-        <v>55.8808021271965</v>
+        <v>-0.0294154322659313</v>
       </c>
       <c r="J134" t="n">
         <v>1356</v>
@@ -6443,19 +6443,19 @@
         <v>45</v>
       </c>
       <c r="E135" t="n">
-        <v>0.000656438659693344</v>
+        <v>0.000483696176071203</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0193480765924229</v>
+        <v>0.0161514498131664</v>
       </c>
       <c r="G135" t="n">
-        <v>0.00158607731286337</v>
+        <v>0.00048363747201322</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0280659856877547</v>
+        <v>0.0161320677623141</v>
       </c>
       <c r="I135" t="n">
-        <v>58.6124425102414</v>
+        <v>-0.0121380292844216</v>
       </c>
       <c r="J135" t="n">
         <v>904</v>
@@ -6475,19 +6475,19 @@
         <v>46</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000489024284254164</v>
+        <v>0.000490878552965174</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0163417846277859</v>
+        <v>0.0163559905371373</v>
       </c>
       <c r="G136" t="n">
-        <v>0.00141619698839945</v>
+        <v>0.000490877120900325</v>
       </c>
       <c r="H136" t="n">
-        <v>0.026345669505885</v>
+        <v>0.0163552668770838</v>
       </c>
       <c r="I136" t="n">
-        <v>65.4691904968074</v>
+        <v>-0.000291735912561912</v>
       </c>
       <c r="J136" t="n">
         <v>904</v>
@@ -6507,19 +6507,19 @@
         <v>47</v>
       </c>
       <c r="E137" t="n">
-        <v>0.000595357264073576</v>
+        <v>0.000468225507564071</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0183082485829566</v>
+        <v>0.0157496314303574</v>
       </c>
       <c r="G137" t="n">
-        <v>0.00154520165160374</v>
+        <v>0.000468566827262995</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0275704790218442</v>
+        <v>0.0157574433843928</v>
       </c>
       <c r="I137" t="n">
-        <v>61.4705780662566</v>
+        <v>0.0728433339846137</v>
       </c>
       <c r="J137" t="n">
         <v>904</v>
@@ -6567,13 +6567,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00122289804016409</v>
+        <v>0.00119438462163363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00149018877607356</v>
+        <v>0.00119458865439075</v>
       </c>
       <c r="F2" t="n">
-        <v>14.5764022514469</v>
+        <v>0.00432327902818693</v>
       </c>
     </row>
     <row r="3">
@@ -6587,13 +6587,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5643892635268247638808646400268444866604422246662886446064668886866</v>
+        <v>204068095915965596048606064040008626646608662620602282860082228</v>
       </c>
       <c r="E3" t="n">
-        <v>636063108412288001582868404402008686028264826628420000466680642086</v>
+        <v>172347176483064089728824868042480486644022666402082820442844882</v>
       </c>
       <c r="F3" t="n">
-        <v>-145.082665377057</v>
+        <v>-347.999551434823</v>
       </c>
     </row>
     <row r="4">
@@ -6607,13 +6607,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00122309536991237</v>
+        <v>0.00119687559853821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00127529233645623</v>
+        <v>0.00119964779467855</v>
       </c>
       <c r="F4" t="n">
-        <v>3.78398659963748</v>
+        <v>0.280699383754543</v>
       </c>
     </row>
     <row r="5">
@@ -6627,13 +6627,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00200750122425062</v>
+        <v>0.00119426830507788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00141410018480556</v>
+        <v>0.00119492420734497</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.345498461416</v>
+        <v>0.167347775489478</v>
       </c>
     </row>
     <row r="6">
@@ -6647,13 +6647,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00147404247585011</v>
+        <v>0.00147367991211808</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00164544533055419</v>
+        <v>0.00147377279850152</v>
       </c>
       <c r="F6" t="n">
-        <v>8.54342240742218</v>
+        <v>0.0111663216390704</v>
       </c>
     </row>
     <row r="7">
@@ -6667,13 +6667,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00161699808116297</v>
+        <v>0.00146785114231172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00166849276643273</v>
+        <v>0.00147077944151031</v>
       </c>
       <c r="F7" t="n">
-        <v>2.68440940149086</v>
+        <v>0.193507005688194</v>
       </c>
     </row>
     <row r="8">
@@ -6687,13 +6687,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00178156133399491</v>
+        <v>0.00146848151570725</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00166950441374756</v>
+        <v>0.00146917557330902</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.589167053101053</v>
+        <v>0.0703911481313604</v>
       </c>
     </row>
     <row r="9">
@@ -6707,13 +6707,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000420442751359355</v>
+        <v>0.000420995033227226</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000964849694681266</v>
+        <v>0.000420968343805203</v>
       </c>
       <c r="F9" t="n">
-        <v>44.4550792434805</v>
+        <v>-0.0106010101340321</v>
       </c>
     </row>
     <row r="10">
@@ -6727,13 +6727,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.185006901319567</v>
-      </c>
-      <c r="E10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F10" t="e">
-        <v>#NUM!</v>
+        <v>0.000077465382529251</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1202212913.78877</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20.2017001488878</v>
       </c>
     </row>
     <row r="11">
@@ -6747,13 +6747,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000458151750898465</v>
+        <v>0.000401195013699451</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000974270260966051</v>
+        <v>0.000401244934038553</v>
       </c>
       <c r="F11" t="n">
-        <v>42.2205438191006</v>
+        <v>-0.000936654916328482</v>
       </c>
     </row>
     <row r="12">
@@ -6767,13 +6767,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000539006016490791</v>
+        <v>0.000405740573891695</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00102640535804487</v>
+        <v>0.000405335934856396</v>
       </c>
       <c r="F12" t="n">
-        <v>39.2632734975296</v>
+        <v>-0.0549187632471368</v>
       </c>
     </row>
     <row r="13">
@@ -6787,13 +6787,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000444463295766473</v>
+        <v>0.000441735800708</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00093421883064313</v>
+        <v>0.000441908939559101</v>
       </c>
       <c r="F13" t="n">
-        <v>46.1834751533618</v>
+        <v>0.0338578772468445</v>
       </c>
     </row>
     <row r="14">
@@ -6807,13 +6807,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00288992326088907</v>
+        <v>0.00126737962284537</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00338537724287846</v>
+        <v>0.0476740802699269</v>
       </c>
       <c r="F14" t="n">
-        <v>14.6351188196718</v>
+        <v>97.3415750955874</v>
       </c>
     </row>
     <row r="15">
@@ -6827,13 +6827,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00049801420996493</v>
+        <v>0.000441033836231684</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000925035040635355</v>
+        <v>0.000440791671477844</v>
       </c>
       <c r="F15" t="n">
-        <v>38.5349314031048</v>
+        <v>-0.0257227692296976</v>
       </c>
     </row>
     <row r="16">
@@ -6847,13 +6847,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000564172721720605</v>
+        <v>0.000441233106081816</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000926210103693905</v>
+        <v>0.000441353918125393</v>
       </c>
       <c r="F16" t="n">
-        <v>35.2744623291997</v>
+        <v>-0.00853668951284678</v>
       </c>
     </row>
     <row r="17">
@@ -6867,13 +6867,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000566864538383626</v>
+        <v>0.000562486819220138</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00105637356394547</v>
+        <v>0.00056262271171133</v>
       </c>
       <c r="F17" t="n">
-        <v>36.8758870480142</v>
+        <v>0.00664190236030689</v>
       </c>
     </row>
     <row r="18">
@@ -6887,13 +6887,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00300201472520252</v>
+        <v>0.00139923667934089</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00352000526075389</v>
+        <v>0.0401467513215883</v>
       </c>
       <c r="F18" t="n">
-        <v>14.7156182215599</v>
+        <v>96.5146951290465</v>
       </c>
     </row>
     <row r="19">
@@ -6907,13 +6907,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000617768245051037</v>
+        <v>0.000561615703718293</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00104753115474387</v>
+        <v>0.000561745154859598</v>
       </c>
       <c r="F19" t="n">
-        <v>31.4134602399129</v>
+        <v>0.0141322824365427</v>
       </c>
     </row>
     <row r="20">
@@ -6927,13 +6927,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000682082238639235</v>
+        <v>0.000562101115733087</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00104852753825891</v>
+        <v>0.000562277221475015</v>
       </c>
       <c r="F20" t="n">
-        <v>28.3816054503917</v>
+        <v>0.034905024434848</v>
       </c>
     </row>
     <row r="21">
@@ -6947,13 +6947,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000372209682600528</v>
+        <v>0.000371618187243728</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000862253928920611</v>
+        <v>0.000371537410807743</v>
       </c>
       <c r="F21" t="n">
-        <v>59.7906301657345</v>
+        <v>-0.0232679423810507</v>
       </c>
     </row>
     <row r="22">
@@ -6967,13 +6967,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00283232732982418</v>
+        <v>0.0011909338917502</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00329816452440475</v>
+        <v>0.077263352385427</v>
       </c>
       <c r="F22" t="n">
-        <v>14.1241345340298</v>
+        <v>98.4586044289028</v>
       </c>
     </row>
     <row r="23">
@@ -6987,13 +6987,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000429862535735296</v>
+        <v>0.000371119428807199</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000852658911242194</v>
+        <v>0.000371207471883822</v>
       </c>
       <c r="F23" t="n">
-        <v>48.3196728563233</v>
+        <v>0.0559880603139178</v>
       </c>
     </row>
     <row r="24">
@@ -7007,13 +7007,13 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000498404360509496</v>
+        <v>0.000370854209337636</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000853999566200343</v>
+        <v>0.000371157071802815</v>
       </c>
       <c r="F24" t="n">
-        <v>44.7177197935208</v>
+        <v>0.02410405454677</v>
       </c>
     </row>
     <row r="25">
@@ -7027,13 +7027,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000373297090319744</v>
+        <v>0.000372465254807651</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000863260284111033</v>
+        <v>0.000372454341469131</v>
       </c>
       <c r="F25" t="n">
-        <v>59.7350482387684</v>
+        <v>-0.0110665697011557</v>
       </c>
     </row>
     <row r="26">
@@ -7047,13 +7047,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00283428653203367</v>
+        <v>0.00119384242110496</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00330431176954839</v>
+        <v>0.0549912899133693</v>
       </c>
       <c r="F26" t="n">
-        <v>14.2246031941156</v>
+        <v>97.8290336106215</v>
       </c>
     </row>
     <row r="27">
@@ -7067,13 +7067,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000431081071094256</v>
+        <v>0.000372007783974588</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000853766109971245</v>
+        <v>0.000371960103763357</v>
       </c>
       <c r="F27" t="n">
-        <v>48.2858193938591</v>
+        <v>0.0513897624480853</v>
       </c>
     </row>
     <row r="28">
@@ -7087,13 +7087,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000499239431635763</v>
+        <v>0.000372413903396481</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000855004337513719</v>
+        <v>0.000372263069999716</v>
       </c>
       <c r="F28" t="n">
-        <v>44.699105893503</v>
+        <v>-0.0352566570274457</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Stress_Testing.xlsx
+++ b/results/consolidated/Stress_Testing.xlsx
@@ -2199,19 +2199,19 @@
         <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000166975655869404</v>
+        <v>0.000167060051091674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00971884369055118</v>
+        <v>0.0097160293461996</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000167029188787356</v>
+        <v>0.00328773065419902</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00972204490336474</v>
+        <v>0.0321242332832427</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0320500376853902</v>
+        <v>94.9186819522971</v>
       </c>
       <c r="J2" t="n">
         <v>143</v>
@@ -2231,19 +2231,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000166623099547765</v>
+        <v>0.000166755786760434</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00968673040252878</v>
+        <v>0.00969366653972052</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000166658220256576</v>
+        <v>476993.796423682</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00968888945248574</v>
+        <v>292.946375698563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0210734932587545</v>
+        <v>99.9999999650403</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2263,19 +2263,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000166779464254165</v>
+        <v>0.000167140278532068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00971431830743773</v>
+        <v>0.00972534093221202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000167656262280561</v>
+        <v>0.000190817373937572</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00972477388730238</v>
+        <v>0.0106581633526229</v>
       </c>
       <c r="I4" t="n">
-        <v>0.522973621426244</v>
+        <v>12.4082492683557</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2295,19 +2295,19 @@
         <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0000387529867485644</v>
+        <v>0.0000387064223420935</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0047560746412279</v>
+        <v>0.00475033304294473</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0000388761729144754</v>
+        <v>0.0000727079147849368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00475593030482492</v>
+        <v>0.00641436896930559</v>
       </c>
       <c r="I5" t="n">
-        <v>0.316868036835829</v>
+        <v>46.7644994955728</v>
       </c>
       <c r="J5" t="n">
         <v>59</v>
@@ -2327,19 +2327,19 @@
         <v>48</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00005188244047529</v>
+        <v>0.0000519664519178929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00560945424675768</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0000519156255095034</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.00561282084118335</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.063921090977316</v>
+        <v>0.00561745478287671</v>
+      </c>
+      <c r="G6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J6" t="n">
         <v>59</v>
@@ -2359,19 +2359,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000038789703972998</v>
+        <v>0.0000388421863096695</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00474498436217047</v>
+        <v>0.00475591982179513</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0000388226486434652</v>
+        <v>0.00467847599491846</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00474836262751274</v>
+        <v>0.0384358019317937</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0848594096958848</v>
+        <v>99.1697683956943</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2391,19 +2391,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000388322277887795</v>
+        <v>0.0000386734603413487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00476963030530809</v>
+        <v>0.00475809499589118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000390652226066273</v>
+        <v>0.0000490139724867914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00478304488823398</v>
+        <v>0.0053785055710382</v>
       </c>
       <c r="I8" t="n">
-        <v>0.59642516361405</v>
+        <v>21.0970701226663</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2423,19 +2423,19 @@
         <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000908500432055289</v>
+        <v>0.0000908530260677112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00366144759262836</v>
+        <v>0.0036598614011438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000909047514344009</v>
+        <v>1.19897610341558</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00365937401654808</v>
+        <v>0.272513373333378</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0601819244965666</v>
+        <v>99.9924224489705</v>
       </c>
       <c r="J9" t="n">
         <v>1356</v>
@@ -2455,19 +2455,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000907881022416117</v>
+        <v>0.0000909058233194078</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00366274543637718</v>
+        <v>0.00366204608945209</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0000908255312470966</v>
+        <v>79590280149677662626600282426</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00366243203274201</v>
+        <v>22785314919975.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0412097842654498</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
         <v>1356</v>
@@ -2487,19 +2487,19 @@
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000908659761228335</v>
+        <v>0.0000908219625815204</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00366422488581416</v>
+        <v>0.00366156762489663</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0000909124217328905</v>
+        <v>0.000122645237714701</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0036662156162488</v>
+        <v>0.00494707153174301</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0510882992353598</v>
+        <v>25.9474201576489</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2519,19 +2519,19 @@
         <v>45</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000210487894573113</v>
+        <v>0.000210440650302616</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00380404588370665</v>
+        <v>0.00381368557338174</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00021055999906374</v>
+        <v>1.11328722884577</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00380876291675883</v>
+        <v>0.229242682497363</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0342441541353146</v>
+        <v>99.9810973624012</v>
       </c>
       <c r="J12" t="n">
         <v>1356</v>
@@ -2551,19 +2551,19 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000210365644683591</v>
+        <v>0.000210321003057071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00380965898302289</v>
+        <v>0.00380946777652011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000210254566395277</v>
+        <v>143346779720594072920624864</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00380964040699412</v>
+        <v>2982687618779.47</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0528303809131359</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2583,19 +2583,19 @@
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000210445822558821</v>
+        <v>0.000210497563522436</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00381416811668865</v>
+        <v>0.00381282956103804</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000210599898708509</v>
+        <v>0.00022724872491064</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00381185189380868</v>
+        <v>0.0048538575703426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0731606000916672</v>
+        <v>7.37128949559183</v>
       </c>
       <c r="J14" t="n">
         <v>1356</v>
@@ -2615,19 +2615,19 @@
         <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000221013282657426</v>
+        <v>0.0000220700115744689</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00344483672031824</v>
+        <v>0.00344752879381929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000022050045074368</v>
+        <v>0.858209591340179</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00344311381585274</v>
+        <v>0.174482027461516</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.232576356200572</v>
+        <v>99.9974283657748</v>
       </c>
       <c r="J15" t="n">
         <v>1356</v>
@@ -2647,19 +2647,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000220856600770798</v>
+        <v>0.0000220791358433378</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00344589947323064</v>
+        <v>0.00344540410793817</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000220794946898927</v>
+        <v>1012256000407748953060624</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00344529895644092</v>
+        <v>293373131630.919</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0279235882599467</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2679,19 +2679,19 @@
         <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000220744797670718</v>
+        <v>0.0000221043240948469</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00344320429605973</v>
+        <v>0.00344604214680494</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000221126924486366</v>
+        <v>0.0000483573504865673</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00345014366094921</v>
+        <v>0.00451164268300031</v>
       </c>
       <c r="I17" t="n">
-        <v>0.172808814004054</v>
+        <v>54.2896294514997</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2711,19 +2711,19 @@
         <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0000222198005873354</v>
+        <v>0.0000222144749748038</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00345413849557914</v>
+        <v>0.00345182587736224</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0000221860582840762</v>
+        <v>50.469578319931</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00345218027556308</v>
+        <v>1.13814338041259</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.152087868998985</v>
+        <v>99.9999559844252</v>
       </c>
       <c r="J18" t="n">
         <v>1356</v>
@@ -2743,19 +2743,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000221935207418048</v>
+        <v>0.0000221899397717547</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00344952925812622</v>
+        <v>0.00344935610141183</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0000221873690607457</v>
+        <v>22093466622569025230488646208080</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00344901448342143</v>
+        <v>750158314826588</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0277260500885203</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2775,19 +2775,19 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000222512168252761</v>
+        <v>0.0000221621863859769</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00345906227230867</v>
+        <v>0.00344669411046873</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0000222355213399453</v>
+        <v>0.0000415033355219271</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00345531687924491</v>
+        <v>0.00448558088531735</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0705874402078275</v>
+        <v>46.6014330962192</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2807,19 +2807,19 @@
         <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000116862525201323</v>
+        <v>0.000117013322846653</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00991193503139734</v>
+        <v>0.00991926777378683</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000117018105317552</v>
+        <v>0.196507617775403</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00991772106130117</v>
+        <v>0.140496923242639</v>
       </c>
       <c r="I21" t="n">
-        <v>0.132953884193425</v>
+        <v>99.9404535436482</v>
       </c>
       <c r="J21" t="n">
         <v>904</v>
@@ -2839,19 +2839,19 @@
         <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000116124435981526</v>
+        <v>0.000116107422763441</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00987579603880344</v>
+        <v>0.00987489884426407</v>
       </c>
       <c r="G22" t="n">
-        <v>0.000116087830766764</v>
+        <v>1649104605170274664488</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00987493499361322</v>
+        <v>12592265813.8566</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0315323445365218</v>
+        <v>100</v>
       </c>
       <c r="J22" t="n">
         <v>904</v>
@@ -2871,19 +2871,19 @@
         <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000119676038804887</v>
+        <v>0.000117780516126009</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0100502253803307</v>
+        <v>0.00996031268921406</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000119709692720434</v>
+        <v>0.000234010887217031</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0100505312813093</v>
+        <v>0.0113190628409199</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0281129412187687</v>
+        <v>49.6687878385868</v>
       </c>
       <c r="J23" t="n">
         <v>904</v>
@@ -2903,19 +2903,19 @@
         <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000238433575010785</v>
+        <v>0.000237810446967516</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0116980409942627</v>
+        <v>0.0116771875486134</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000238237291908681</v>
+        <v>0.000824772299302325</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0116865692551256</v>
+        <v>0.0195641193646096</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08238974701692</v>
+        <v>71.1665332154487</v>
       </c>
       <c r="J24" t="n">
         <v>143</v>
@@ -2935,19 +2935,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000240210439988377</v>
+        <v>0.000240095309032806</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0117459522096261</v>
+        <v>0.0117446656744815</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000240203684583164</v>
+        <v>372.715580003421</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0117485267320475</v>
+        <v>9.23458240590991</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.00281236535753252</v>
+        <v>99.9999355821645</v>
       </c>
       <c r="J25" t="n">
         <v>143</v>
@@ -2967,19 +2967,19 @@
         <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000238330500883258</v>
+        <v>0.000237641945124602</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0116789856809294</v>
+        <v>0.0116837603236573</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00023782144737888</v>
+        <v>0.000237680524574997</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0116983580133469</v>
+        <v>0.0117016020283172</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.214048610833162</v>
+        <v>0.0162316413869237</v>
       </c>
       <c r="J26" t="n">
         <v>143</v>
@@ -2999,19 +2999,19 @@
         <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0000963882221354587</v>
+        <v>0.0000960855694598312</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00736458489875018</v>
+        <v>0.00735163006510339</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0000963673756623975</v>
+        <v>0.000142573897090336</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00737103094844691</v>
+        <v>0.00895306342534568</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0216322930015033</v>
+        <v>32.6064788711283</v>
       </c>
       <c r="J27" t="n">
         <v>59</v>
@@ -3031,19 +3031,19 @@
         <v>48</v>
       </c>
       <c r="E28" t="n">
-        <v>612204287747896810964022862642648446286204606266886448642622288</v>
+        <v>20550049848822609652222466022864684268462482642842808624042226604</v>
       </c>
       <c r="F28" t="n">
-        <v>3221233282482193816646060260448</v>
-      </c>
-      <c r="G28" t="n">
-        <v>689388705932256358982286242068620624466088444608028280668266228</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3418267739420846032424404222606</v>
-      </c>
-      <c r="I28" t="n">
-        <v>11.1960665325933</v>
+        <v>18662956080103713416062444664040</v>
+      </c>
+      <c r="G28" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H28" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I28" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J28" t="n">
         <v>59</v>
@@ -3063,19 +3063,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000969790974229639</v>
+        <v>0.0000969738124565842</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00737412319549455</v>
+        <v>0.00737052206623287</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000097007669782765</v>
+        <v>0.136663566801025</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00737491167293084</v>
+        <v>0.205452551057615</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0294537121293056</v>
+        <v>99.9290419423944</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -3095,19 +3095,19 @@
         <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000966635055018119</v>
+        <v>0.0000965364261830818</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00736185351195423</v>
+        <v>0.00737234648717838</v>
       </c>
       <c r="G30" t="n">
-        <v>0.000097004870398268</v>
+        <v>0.0000953293779213857</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00739429506696414</v>
+        <v>0.00726469957227106</v>
       </c>
       <c r="I30" t="n">
-        <v>0.351904904418262</v>
+        <v>-1.26618707476675</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -3127,19 +3127,19 @@
         <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>0.000103412008896841</v>
+        <v>0.000103391180028753</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00454089266379086</v>
+        <v>0.00454661968561084</v>
       </c>
       <c r="G31" t="n">
-        <v>0.000103216771941774</v>
+        <v>0.0633262859850293</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00454904266084343</v>
+        <v>0.0717343823747028</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.189152355177928</v>
+        <v>99.8367326009721</v>
       </c>
       <c r="J31" t="n">
         <v>1356</v>
@@ -3159,19 +3159,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000103488761085417</v>
+        <v>0.00010356670821453</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0045485746511353</v>
+        <v>0.00454853769130572</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000103471462951834</v>
+        <v>331135294676860640864826464280</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00454828929035417</v>
+        <v>126303315030649</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0167177819757007</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
         <v>1356</v>
@@ -3191,19 +3191,19 @@
         <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000103384723050186</v>
+        <v>0.000103401244854563</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00454416547755314</v>
+        <v>0.00454618914655762</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00010341731907531</v>
+        <v>0.000109508688398545</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00454751898718663</v>
+        <v>0.00491832194956059</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0315189229575538</v>
+        <v>5.57713148910596</v>
       </c>
       <c r="J33" t="n">
         <v>1356</v>
@@ -3223,19 +3223,19 @@
         <v>45</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000222504719111438</v>
+        <v>0.000222708168574501</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00469565026177085</v>
+        <v>0.00469172678876375</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000222716544460445</v>
+        <v>0.216064461026026</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00469862990205204</v>
+        <v>0.13383874235707</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0951098399627156</v>
+        <v>99.8969251271047</v>
       </c>
       <c r="J34" t="n">
         <v>1356</v>
@@ -3255,19 +3255,19 @@
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000222782784816604</v>
+        <v>0.000223034876668562</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00469545401808677</v>
+        <v>0.00469604929680897</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000222994993646178</v>
+        <v>423283843977773232044284424062</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00469607553390421</v>
+        <v>84279365970437.2</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0951630465348463</v>
+        <v>100</v>
       </c>
       <c r="J35" t="n">
         <v>1356</v>
@@ -3287,19 +3287,19 @@
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00022267611953299</v>
+        <v>0.00022266429351872</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00469255800349099</v>
+        <v>0.00469598445609856</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000222790312671865</v>
+        <v>0.000398989220843613</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00469432823552905</v>
+        <v>0.00660599276976911</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0512558815981108</v>
+        <v>44.192904999307</v>
       </c>
       <c r="J36" t="n">
         <v>1356</v>
@@ -3319,19 +3319,19 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0000352106424578699</v>
+        <v>0.0000352578047765636</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00432578147147118</v>
+        <v>0.00433474934788131</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000035225587417495</v>
+        <v>0.0245124452952953</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00433223868747209</v>
+        <v>0.0422022588207407</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0424264312414262</v>
+        <v>99.8561636574735</v>
       </c>
       <c r="J37" t="n">
         <v>1356</v>
@@ -3351,19 +3351,19 @@
         <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000352777641430168</v>
+        <v>0.0000352748739793425</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00433104936916655</v>
+        <v>0.00433061563328579</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0000352728063311057</v>
+        <v>2832239377119420632848226424</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00433055528120916</v>
+        <v>12918355194499.3</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0140556208216387</v>
+        <v>100</v>
       </c>
       <c r="J38" t="n">
         <v>1356</v>
@@ -3383,19 +3383,19 @@
         <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000352544369019043</v>
+        <v>0.0000352521091629185</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00433091566399898</v>
+        <v>0.00433498539112052</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000352005574784481</v>
+        <v>0.0000408254576366535</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00432983392803921</v>
+        <v>0.00470502015939213</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.153064119763288</v>
+        <v>13.6516497214504</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3415,19 +3415,19 @@
         <v>45</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0000352639620878871</v>
+        <v>0.0000352775343435518</v>
       </c>
       <c r="F40" t="n">
-        <v>0.00433302368838828</v>
+        <v>0.00433183398371391</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0000352594939516534</v>
+        <v>0.122907505900349</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00433066709372014</v>
+        <v>0.115840018899355</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0126721507684874</v>
+        <v>99.9712974939284</v>
       </c>
       <c r="J40" t="n">
         <v>1356</v>
@@ -3447,19 +3447,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000353267430775126</v>
+        <v>0.0000353338580682214</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00433236727156954</v>
+        <v>0.00433350095598423</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0000353377960853952</v>
+        <v>485348844557453183328442444</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00433364119492039</v>
+        <v>5424648465412.42</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0312781472161651</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3479,19 +3479,19 @@
         <v>47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000352613726673386</v>
+        <v>0.0000352922150212067</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00433019146758099</v>
+        <v>0.00433419638527062</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0000353512393979318</v>
+        <v>0.0000387233237395473</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00433518527011683</v>
+        <v>0.00456580257928379</v>
       </c>
       <c r="I42" t="n">
-        <v>0.254210975693382</v>
+        <v>8.86057390480792</v>
       </c>
       <c r="J42" t="n">
         <v>1356</v>
@@ -3511,19 +3511,19 @@
         <v>45</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000131633261572373</v>
+        <v>0.000131599806306761</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0101685698362659</v>
+        <v>0.0101649976404406</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000131613341682797</v>
+        <v>0.0235760523769521</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0101676381933407</v>
+        <v>0.0477939251229977</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0151351597954805</v>
+        <v>99.4418072873158</v>
       </c>
       <c r="J43" t="n">
         <v>904</v>
@@ -3543,19 +3543,19 @@
         <v>48</v>
       </c>
       <c r="E44" t="n">
-        <v>0.000077465382529251</v>
+        <v>0.000172634239481751</v>
       </c>
       <c r="F44" t="n">
-        <v>0.00711849067465625</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.0000970764824235429</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.00720892912690086</v>
-      </c>
-      <c r="I44" t="n">
-        <v>20.2017001488878</v>
+        <v>0.00737802669561499</v>
+      </c>
+      <c r="G44" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H44" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I44" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J44" t="n">
         <v>904</v>
@@ -3575,19 +3575,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000141496954720349</v>
+        <v>0.000141492473882068</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106223569086999</v>
+        <v>0.0106222471145851</v>
       </c>
       <c r="G45" t="n">
-        <v>0.000141490832642518</v>
+        <v>14139917182090323968</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0106225236769855</v>
+        <v>1449468707.07312</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0043268370935821</v>
+        <v>100</v>
       </c>
       <c r="J45" t="n">
         <v>904</v>
@@ -3607,19 +3607,19 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000132421764575771</v>
+        <v>0.000133533157198412</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0102031709782539</v>
+        <v>0.0102552792148694</v>
       </c>
       <c r="G46" t="n">
-        <v>0.000132459368149486</v>
+        <v>0.000130404667349873</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0102070433375184</v>
+        <v>0.010110690636959</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0283887612031127</v>
+        <v>-2.39906278825532</v>
       </c>
       <c r="J46" t="n">
         <v>904</v>
@@ -3639,19 +3639,19 @@
         <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000513634953433287</v>
+        <v>0.000516898359983477</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0163887856590667</v>
+        <v>0.0164537007635467</v>
       </c>
       <c r="G47" t="n">
-        <v>0.000515061057736428</v>
+        <v>0.00672227768036403</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0164191249369147</v>
+        <v>0.0569507738137068</v>
       </c>
       <c r="I47" t="n">
-        <v>0.276880630309853</v>
+        <v>92.3106663461203</v>
       </c>
       <c r="J47" t="n">
         <v>143</v>
@@ -3671,19 +3671,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000512420613474496</v>
+        <v>0.000512805185536126</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0165023326369671</v>
+        <v>0.0165141031041208</v>
       </c>
       <c r="G48" t="n">
-        <v>0.00051253702683908</v>
+        <v>63.2334328341575</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0165034993382382</v>
+        <v>4.48352617511119</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0227131618767188</v>
+        <v>99.9991890283944</v>
       </c>
       <c r="J48" t="n">
         <v>143</v>
@@ -3703,19 +3703,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000515500557734305</v>
+        <v>0.000514414720028956</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0163775155955427</v>
+        <v>0.0164082834804659</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000516327501169937</v>
+        <v>0.000567633847934421</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0164027625450333</v>
+        <v>0.0170010781805506</v>
       </c>
       <c r="I49" t="n">
-        <v>0.160158704263957</v>
+        <v>9.37560860740169</v>
       </c>
       <c r="J49" t="n">
         <v>143</v>
@@ -3735,19 +3735,19 @@
         <v>45</v>
       </c>
       <c r="E50" t="n">
-        <v>0.000259075197226633</v>
+        <v>0.000259090603437036</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0121467247127419</v>
+        <v>0.0121132767157572</v>
       </c>
       <c r="G50" t="n">
-        <v>0.000259594127605636</v>
+        <v>0.0227135457480371</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0121257200722259</v>
+        <v>0.0641698362868067</v>
       </c>
       <c r="I50" t="n">
-        <v>0.199900661771232</v>
+        <v>98.8593123842876</v>
       </c>
       <c r="J50" t="n">
         <v>59</v>
@@ -3767,19 +3767,19 @@
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000256387712229557</v>
+        <v>0.000256275590331901</v>
       </c>
       <c r="F51" t="n">
-        <v>0.012046976225777</v>
+        <v>0.0120349024924798</v>
       </c>
       <c r="G51" t="n">
-        <v>0.000256439953420989</v>
+        <v>0.324125248755212</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0120476809335599</v>
+        <v>0.271176176385608</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0203717052414264</v>
+        <v>99.9209331604631</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -3799,19 +3799,19 @@
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000259161899672062</v>
+        <v>0.000258608791905769</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0121223043326171</v>
+        <v>0.0120775213251645</v>
       </c>
       <c r="G52" t="n">
-        <v>0.000259258311222197</v>
+        <v>0.00025833072598055</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0121315531126409</v>
+        <v>0.0120370570207408</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0371874481787432</v>
+        <v>-0.107639509068291</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -3831,19 +3831,19 @@
         <v>45</v>
       </c>
       <c r="E53" t="n">
-        <v>0.000162387417615191</v>
+        <v>0.000161996719777218</v>
       </c>
       <c r="F53" t="n">
-        <v>0.00771083590853</v>
+        <v>0.00770662990197058</v>
       </c>
       <c r="G53" t="n">
-        <v>0.000162216879884625</v>
+        <v>28.4592466355662</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00770719465294139</v>
+        <v>0.918873498432765</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1051294604401</v>
+        <v>99.9994307765</v>
       </c>
       <c r="J53" t="n">
         <v>1356</v>
@@ -3863,19 +3863,19 @@
         <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000163090445932847</v>
+        <v>0.000162936394336284</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00777030568950593</v>
+        <v>0.00777321122475771</v>
       </c>
       <c r="G54" t="n">
-        <v>0.000163193764237668</v>
+        <v>64872258042531621180042628</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00777158450559627</v>
+        <v>1265125020188.92</v>
       </c>
       <c r="I54" t="n">
-        <v>0.063310203856969</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
         <v>1356</v>
@@ -3895,19 +3895,19 @@
         <v>47</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000162365700272085</v>
+        <v>0.000162457369401621</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00770775530677447</v>
+        <v>0.00771760981263804</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000162161556343121</v>
+        <v>0.000208242918747596</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00770914884765274</v>
+        <v>0.0091429860135175</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.125889226501892</v>
+        <v>21.9866056533095</v>
       </c>
       <c r="J55" t="n">
         <v>1356</v>
@@ -3927,19 +3927,19 @@
         <v>45</v>
       </c>
       <c r="E56" t="n">
-        <v>0.000281953746038375</v>
+        <v>0.000282162393030149</v>
       </c>
       <c r="F56" t="n">
-        <v>0.00784839686136849</v>
+        <v>0.00786710338272792</v>
       </c>
       <c r="G56" t="n">
-        <v>0.000281571714960163</v>
+        <v>0.499471513491229</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00784888747889857</v>
+        <v>0.225271659119233</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.135678073440989</v>
+        <v>99.9435078106741</v>
       </c>
       <c r="J56" t="n">
         <v>1356</v>
@@ -3959,19 +3959,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000283168488724989</v>
+        <v>0.000282691544712139</v>
       </c>
       <c r="F57" t="n">
-        <v>0.00792060821505393</v>
+        <v>0.0079187349956235</v>
       </c>
       <c r="G57" t="n">
-        <v>0.000282785382435605</v>
+        <v>54521462547176333712068624646</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0079191046915603</v>
+        <v>34148062945790.2</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.135475987508478</v>
+        <v>100</v>
       </c>
       <c r="J57" t="n">
         <v>1356</v>
@@ -3991,19 +3991,19 @@
         <v>47</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000281842886108609</v>
+        <v>0.000281883867607197</v>
       </c>
       <c r="F58" t="n">
-        <v>0.00785243779506888</v>
+        <v>0.00785294302036169</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000281618324319048</v>
+        <v>0.000338926210911476</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00785159540277762</v>
+        <v>0.00902298689417835</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0797397648408809</v>
+        <v>16.8303133448649</v>
       </c>
       <c r="J58" t="n">
         <v>1356</v>
@@ -4023,19 +4023,19 @@
         <v>45</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000093650537012908</v>
+        <v>0.0000934678826093097</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00749000546595306</v>
+        <v>0.00747749308205695</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0000936083195331897</v>
+        <v>0.430717169883635</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00749222813993131</v>
+        <v>0.258443396499492</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0451001363220467</v>
+        <v>99.9782994760495</v>
       </c>
       <c r="J59" t="n">
         <v>1356</v>
@@ -4055,19 +4055,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000941131161883826</v>
+        <v>0.0000941021049618432</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00755450332212559</v>
+        <v>0.00755398213416622</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0000940820034171474</v>
+        <v>25993300365478964622462262</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0075531979911619</v>
+        <v>798646102857.306</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.033069843439938</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
         <v>1356</v>
@@ -4087,19 +4087,19 @@
         <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0000935582587996006</v>
+        <v>0.0000935576641844215</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00748673256073213</v>
+        <v>0.0074931473835255</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0000938058467000785</v>
+        <v>0.000184210207525231</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00750256257840865</v>
+        <v>0.00901052929801279</v>
       </c>
       <c r="I61" t="n">
-        <v>0.263936534008903</v>
+        <v>49.2114658349717</v>
       </c>
       <c r="J61" t="n">
         <v>1356</v>
@@ -4119,19 +4119,19 @@
         <v>45</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0000937892842699788</v>
+        <v>0.0000936084344559735</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00749913675084782</v>
+        <v>0.00748578956440812</v>
       </c>
       <c r="G62" t="n">
-        <v>0.000093703895094768</v>
+        <v>1373.83754924098</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00749744734017311</v>
+        <v>3.38104440980681</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0911266016470713</v>
+        <v>99.9999931863535</v>
       </c>
       <c r="J62" t="n">
         <v>1356</v>
@@ -4151,19 +4151,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0000942545915039134</v>
+        <v>0.000094213837536071</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00755899640407504</v>
+        <v>0.00755827763414994</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0000942251996567323</v>
+        <v>1022690007578979313122068</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00755813979959274</v>
+        <v>222989842506.015</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0311931917237968</v>
+        <v>100</v>
       </c>
       <c r="J63" t="n">
         <v>1356</v>
@@ -4183,19 +4183,19 @@
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000093784760405989</v>
+        <v>0.0000938023185618277</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00749224168741644</v>
+        <v>0.00750019406804445</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0000939409172444899</v>
+        <v>0.000121987180398559</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00750530345037232</v>
+        <v>0.00836182890784391</v>
       </c>
       <c r="I64" t="n">
-        <v>0.166228777705527</v>
+        <v>23.104773587393</v>
       </c>
       <c r="J64" t="n">
         <v>1356</v>
@@ -4215,19 +4215,19 @@
         <v>45</v>
       </c>
       <c r="E65" t="n">
-        <v>0.000210915795851206</v>
+        <v>0.000210771324927241</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0120824872299155</v>
+        <v>0.0120815506917163</v>
       </c>
       <c r="G65" t="n">
-        <v>0.000210723521187492</v>
+        <v>0.0154317419068159</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0120821328586473</v>
+        <v>0.0693317777618018</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0912449937385992</v>
+        <v>98.6341702304252</v>
       </c>
       <c r="J65" t="n">
         <v>904</v>
@@ -4247,19 +4247,19 @@
         <v>46</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000226771873595338</v>
+        <v>0.000226750590680147</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126567783717109</v>
+        <v>0.0126574308833276</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00022673317812646</v>
+        <v>25401963998635433656020</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0126563933660829</v>
+        <v>21633075516.239</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0170665225080432</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
         <v>904</v>
@@ -4279,19 +4279,19 @@
         <v>47</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000209598483836291</v>
+        <v>0.000210525717982336</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0120244544670814</v>
+        <v>0.0120606430542286</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000209235213268818</v>
+        <v>0.000840917160048174</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0120262433067877</v>
+        <v>0.0169269028980926</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.173618274762424</v>
+        <v>74.9647494444904</v>
       </c>
       <c r="J67" t="n">
         <v>904</v>
@@ -4311,19 +4311,19 @@
         <v>45</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00358831963302271</v>
+        <v>0.00358387157044838</v>
       </c>
       <c r="F68" t="n">
-        <v>0.049352249036705</v>
+        <v>0.0493364444901825</v>
       </c>
       <c r="G68" t="n">
-        <v>0.00358854016147951</v>
+        <v>0.608779530630297</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0493736119703092</v>
+        <v>0.362590527319204</v>
       </c>
       <c r="I68" t="n">
-        <v>0.00614535289769085</v>
+        <v>99.4113022218835</v>
       </c>
       <c r="J68" t="n">
         <v>143</v>
@@ -4343,19 +4343,19 @@
         <v>46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00359372246920314</v>
+        <v>0.00359502479333836</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493701156250663</v>
+        <v>0.0493763369337629</v>
       </c>
       <c r="G69" t="n">
-        <v>0.00359246003044369</v>
+        <v>7047.3211462347</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0493534074943766</v>
+        <v>28.8493215133236</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0351413446150215</v>
+        <v>99.9999489873568</v>
       </c>
       <c r="J69" t="n">
         <v>143</v>
@@ -4375,19 +4375,19 @@
         <v>47</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00357941998493728</v>
+        <v>0.00357679062606319</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0493382234908209</v>
+        <v>0.0492817116517857</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00357620020383322</v>
+        <v>0.00358441266364974</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0492959819944264</v>
+        <v>0.0494023386746975</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0900335809111892</v>
+        <v>0.212643975506576</v>
       </c>
       <c r="J70" t="n">
         <v>143</v>
@@ -4407,19 +4407,19 @@
         <v>45</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00346619295684648</v>
+        <v>0.00345810733818811</v>
       </c>
       <c r="F71" t="n">
-        <v>0.045522417557489</v>
+        <v>0.0454179258879109</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0034569158472051</v>
+        <v>0.617585087312466</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0454668090346793</v>
+        <v>0.291337231983611</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.26836376849837</v>
+        <v>99.4400597732635</v>
       </c>
       <c r="J71" t="n">
         <v>59</v>
@@ -4439,19 +4439,19 @@
         <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>164973292377.312</v>
+        <v>11617076644.9822</v>
       </c>
       <c r="F72" t="n">
-        <v>52891.6448218613</v>
+        <v>14091.0570142307</v>
       </c>
       <c r="G72" t="n">
-        <v>14280204136.97</v>
+        <v>98686184067844248880206820246448844202864282224060202022424</v>
       </c>
       <c r="H72" t="n">
-        <v>15585.1734490631</v>
+        <v>40964071373466186350464620806</v>
       </c>
       <c r="I72" t="n">
-        <v>-1055.25864192804</v>
+        <v>100</v>
       </c>
       <c r="J72" t="n">
         <v>59</v>
@@ -4471,19 +4471,19 @@
         <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00346451598006494</v>
+        <v>0.00346479565387934</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0454618197385731</v>
+        <v>0.0454561980324347</v>
       </c>
       <c r="G73" t="n">
-        <v>0.00346841488231196</v>
+        <v>27.446773701895</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0455020007603141</v>
+        <v>2.24203355433515</v>
       </c>
       <c r="I73" t="n">
-        <v>0.112411645645508</v>
+        <v>99.9873763099025</v>
       </c>
       <c r="J73" t="n">
         <v>59</v>
@@ -4503,19 +4503,19 @@
         <v>47</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00347175170535522</v>
+        <v>0.00347482056360249</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0455466503000288</v>
+        <v>0.0456364005307156</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00348447291649426</v>
+        <v>0.00345898815143245</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0456351055023932</v>
+        <v>0.0454178943324778</v>
       </c>
       <c r="I74" t="n">
-        <v>0.365082795702598</v>
+        <v>-0.457718022638554</v>
       </c>
       <c r="J74" t="n">
         <v>59</v>
@@ -4535,19 +4535,19 @@
         <v>45</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00126814074662105</v>
+        <v>0.00126743755408719</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0253224037176126</v>
+        <v>0.0252893636753448</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00126830098205465</v>
+        <v>4.19711424570925</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0253008155919592</v>
+        <v>0.39326635483392</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0126338649793709</v>
+        <v>99.9698021669202</v>
       </c>
       <c r="J75" t="n">
         <v>1356</v>
@@ -4567,19 +4567,19 @@
         <v>48</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00126737962284537</v>
+        <v>0.00126981598313535</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0253396543796739</v>
+        <v>0.0253205493057644</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0476740802699269</v>
+        <v>3891958770768186368</v>
       </c>
       <c r="H76" t="n">
-        <v>0.086950006724609</v>
+        <v>157366716.694124</v>
       </c>
       <c r="I76" t="n">
-        <v>97.3415750955874</v>
+        <v>100</v>
       </c>
       <c r="J76" t="n">
         <v>1356</v>
@@ -4599,19 +4599,19 @@
         <v>46</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00126790280520765</v>
+        <v>0.00126818006312231</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0252632634526161</v>
+        <v>0.025265116575941</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00126869256733436</v>
+        <v>163941934067150003146866682</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0252667249380251</v>
+        <v>2105266773348.41</v>
       </c>
       <c r="I77" t="n">
-        <v>0.062250079100793</v>
+        <v>100</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4631,19 +4631,19 @@
         <v>47</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00126871855780403</v>
+        <v>0.00126692827297682</v>
       </c>
       <c r="F78" t="n">
-        <v>0.025350417074483</v>
+        <v>0.025340129088533</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00126725713720342</v>
+        <v>0.00127249900827644</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0253373841693409</v>
+        <v>0.0253673150301437</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.115321552169981</v>
+        <v>0.437779146654712</v>
       </c>
       <c r="J78" t="n">
         <v>1356</v>
@@ -4663,19 +4663,19 @@
         <v>45</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00139747804311291</v>
+        <v>0.00139584231057744</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0254540198754749</v>
+        <v>0.0254340673315814</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00139650843874228</v>
+        <v>43.5087833764608</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0254599863261398</v>
+        <v>0.733447488666945</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0694306130723901</v>
+        <v>99.9967918148883</v>
       </c>
       <c r="J79" t="n">
         <v>1356</v>
@@ -4695,19 +4695,19 @@
         <v>48</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00139923667934089</v>
+        <v>0.00139629764952591</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0254945276878685</v>
+        <v>0.0254750017706653</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0401467513215883</v>
+        <v>15367693778721796096</v>
       </c>
       <c r="H80" t="n">
-        <v>0.084425542768168</v>
+        <v>204263259.645897</v>
       </c>
       <c r="I80" t="n">
-        <v>96.5146951290465</v>
+        <v>100</v>
       </c>
       <c r="J80" t="n">
         <v>1356</v>
@@ -4727,19 +4727,19 @@
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00139762228241484</v>
+        <v>0.00139816382524416</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0254116454194006</v>
+        <v>0.0254110492089136</v>
       </c>
       <c r="G81" t="n">
-        <v>0.00139797367528815</v>
+        <v>1747664775381163614180604</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0254136981068695</v>
+        <v>190017383380.999</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0251358719782645</v>
+        <v>100</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4759,19 +4759,19 @@
         <v>47</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00139727300982023</v>
+        <v>0.00139826064262992</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0254941635545517</v>
+        <v>0.0255219684056149</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00139822107399483</v>
+        <v>0.00139983957158799</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0255160695676328</v>
+        <v>0.0254880646205058</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0678050268466785</v>
+        <v>0.112793565071455</v>
       </c>
       <c r="J82" t="n">
         <v>1356</v>
@@ -4791,19 +4791,19 @@
         <v>45</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00118665269433373</v>
+        <v>0.00118784056233316</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0251061204978485</v>
+        <v>0.0251172118020489</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00118703387208131</v>
+        <v>0.215834450403935</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0251184418312433</v>
+        <v>0.172602637261507</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0321117835429696</v>
+        <v>99.4496520086992</v>
       </c>
       <c r="J83" t="n">
         <v>1356</v>
@@ -4823,19 +4823,19 @@
         <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0011909338917502</v>
+        <v>0.00118824749843996</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0251811060622614</v>
+        <v>0.0251239628336549</v>
       </c>
       <c r="G84" t="n">
-        <v>0.077263352385427</v>
+        <v>14935385816631754752</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0936994652377659</v>
+        <v>281259385.993308</v>
       </c>
       <c r="I84" t="n">
-        <v>98.4586044289028</v>
+        <v>100</v>
       </c>
       <c r="J84" t="n">
         <v>1356</v>
@@ -4855,19 +4855,19 @@
         <v>46</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118765357717191</v>
+        <v>0.00118755373237</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0250722273406622</v>
+        <v>0.0250713846383668</v>
       </c>
       <c r="G85" t="n">
-        <v>0.00118744332279492</v>
+        <v>2245437036143935222626242060</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0250709158498084</v>
+        <v>9835319440850.51</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0177064768445678</v>
+        <v>100</v>
       </c>
       <c r="J85" t="n">
         <v>1356</v>
@@ -4887,19 +4887,19 @@
         <v>47</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00118934171838292</v>
+        <v>0.00118879690315476</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0251559367898753</v>
+        <v>0.0251780189016543</v>
       </c>
       <c r="G86" t="n">
-        <v>0.00118910353401773</v>
+        <v>0.00118737299691941</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0251537757484337</v>
+        <v>0.0251874396451509</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.0200305825676022</v>
+        <v>-0.119920719019478</v>
       </c>
       <c r="J86" t="n">
         <v>1356</v>
@@ -4919,19 +4919,19 @@
         <v>45</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00119471316276271</v>
+        <v>0.001194311139798</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0251767449313413</v>
+        <v>0.025171618477303</v>
       </c>
       <c r="G87" t="n">
-        <v>0.00119335871728846</v>
+        <v>1.89985023546212</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0251405650844172</v>
+        <v>0.313956727764779</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.113498603112869</v>
+        <v>99.9371365638457</v>
       </c>
       <c r="J87" t="n">
         <v>1356</v>
@@ -4951,19 +4951,19 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00119384242110496</v>
+        <v>0.00119220020257798</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0251674930444885</v>
+        <v>0.0251745889953397</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0549912899133693</v>
+        <v>753935276335988352</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0836052192825909</v>
+        <v>122574432.731125</v>
       </c>
       <c r="I88" t="n">
-        <v>97.8290336106215</v>
+        <v>100</v>
       </c>
       <c r="J88" t="n">
         <v>1356</v>
@@ -4983,19 +4983,19 @@
         <v>46</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00119267366317441</v>
+        <v>0.0011929133347853</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0250987995034159</v>
+        <v>0.025100252089435</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00119290067715493</v>
+        <v>1181770801180423225364</v>
       </c>
       <c r="H89" t="n">
-        <v>0.025099507536383</v>
+        <v>7707532718.59548</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0190304176089771</v>
+        <v>100</v>
       </c>
       <c r="J89" t="n">
         <v>1356</v>
@@ -5015,19 +5015,19 @@
         <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00119424778728295</v>
+        <v>0.0011945894740644</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0251954808661812</v>
+        <v>0.0251893094399388</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00119378244991306</v>
+        <v>0.00119440288996759</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0251905143398555</v>
+        <v>0.0252272375706826</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0389800813305539</v>
+        <v>-0.0156215376213368</v>
       </c>
       <c r="J90" t="n">
         <v>1356</v>
@@ -5047,19 +5047,19 @@
         <v>45</v>
       </c>
       <c r="E91" t="n">
-        <v>0.00106108860116156</v>
+        <v>0.00106136464210109</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0228016195775198</v>
+        <v>0.0227805046191611</v>
       </c>
       <c r="G91" t="n">
-        <v>0.00105968350556643</v>
+        <v>0.0219191310133396</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0227512079558229</v>
+        <v>0.0711435611164174</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.132595778621249</v>
+        <v>95.1578160582408</v>
       </c>
       <c r="J91" t="n">
         <v>904</v>
@@ -5079,19 +5079,19 @@
         <v>46</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0010758857086025</v>
+        <v>0.00107584442195268</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230213549370511</v>
+        <v>0.0230224870686247</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00107583566575547</v>
+        <v>8782021827161026560</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0230232013750546</v>
+        <v>840052933.540231</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.00465153262938542</v>
+        <v>100</v>
       </c>
       <c r="J92" t="n">
         <v>904</v>
@@ -5111,19 +5111,19 @@
         <v>47</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00105092433122067</v>
+        <v>0.00105021424522362</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0226246196536464</v>
+        <v>0.0226325756452959</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00105106800880114</v>
+        <v>0.00105850473551286</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0226222921257745</v>
+        <v>0.0227036680124137</v>
       </c>
       <c r="I93" t="n">
-        <v>0.013669674965221</v>
+        <v>0.783226565842317</v>
       </c>
       <c r="J93" t="n">
         <v>904</v>
@@ -5143,19 +5143,19 @@
         <v>45</v>
       </c>
       <c r="E94" t="n">
-        <v>0.00165845108229663</v>
+        <v>0.00166512757914714</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0306081458789955</v>
+        <v>0.0306882526854809</v>
       </c>
       <c r="G94" t="n">
-        <v>0.00166243846658631</v>
+        <v>0.00416719347214774</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0306598247835027</v>
+        <v>0.0440942068988975</v>
       </c>
       <c r="I94" t="n">
-        <v>0.23985154156494</v>
+        <v>60.0419901241364</v>
       </c>
       <c r="J94" t="n">
         <v>143</v>
@@ -5175,19 +5175,19 @@
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0016747977302822</v>
+        <v>0.0016753717741794</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0308221842130781</v>
+        <v>0.0308159057963404</v>
       </c>
       <c r="G95" t="n">
-        <v>0.00167471172799621</v>
+        <v>142818.101065015</v>
       </c>
       <c r="H95" t="n">
-        <v>0.030815115252802</v>
+        <v>103.562636192182</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.005135348642522</v>
+        <v>99.9999988269192</v>
       </c>
       <c r="J95" t="n">
         <v>143</v>
@@ -5207,19 +5207,19 @@
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00166345829012489</v>
+        <v>0.00166125789021181</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0306345735104619</v>
+        <v>0.0306471250386961</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00166549116584759</v>
+        <v>0.00166065028382963</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0306791271618645</v>
+        <v>0.0306414946632502</v>
       </c>
       <c r="I96" t="n">
-        <v>0.122058631374667</v>
+        <v>-0.0365884610441871</v>
       </c>
       <c r="J96" t="n">
         <v>143</v>
@@ -5239,19 +5239,19 @@
         <v>45</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0022086031825195</v>
+        <v>0.00221806825391299</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0350079796666746</v>
+        <v>0.0351430376719977</v>
       </c>
       <c r="G97" t="n">
-        <v>0.00221661493946969</v>
+        <v>0.00629598210125899</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0350961492671635</v>
+        <v>0.0512743682975707</v>
       </c>
       <c r="I97" t="n">
-        <v>0.361441078806009</v>
+        <v>64.7700991165549</v>
       </c>
       <c r="J97" t="n">
         <v>59</v>
@@ -5271,19 +5271,19 @@
         <v>46</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00221583433755109</v>
+        <v>0.00221604586015262</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0350624018790841</v>
+        <v>0.0350654343235738</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00221509688720289</v>
+        <v>0.0780871810213552</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0350428452614733</v>
+        <v>0.181176702115937</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0332920132053774</v>
+        <v>97.1620875140229</v>
       </c>
       <c r="J98" t="n">
         <v>59</v>
@@ -5303,19 +5303,19 @@
         <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00221931495735858</v>
+        <v>0.00221506669068248</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0350702991969525</v>
+        <v>0.0350179282760485</v>
       </c>
       <c r="G99" t="n">
-        <v>0.00221846812942584</v>
+        <v>0.0022195351198017</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0350930821033542</v>
+        <v>0.0351445245920978</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.03817174209104</v>
+        <v>0.201322749045753</v>
       </c>
       <c r="J99" t="n">
         <v>59</v>
@@ -5335,19 +5335,19 @@
         <v>45</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000439493721144453</v>
+        <v>0.000439196071214006</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0138083178066177</v>
+        <v>0.0138146220512591</v>
       </c>
       <c r="G100" t="n">
-        <v>0.000439854421840459</v>
+        <v>0.0990906561079029</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0138251144451137</v>
+        <v>0.121393231996092</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0820045628952869</v>
+        <v>99.5567734754569</v>
       </c>
       <c r="J100" t="n">
         <v>1356</v>
@@ -5367,19 +5367,19 @@
         <v>46</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000439372612740038</v>
+        <v>0.000439981119663258</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0138085522023891</v>
+        <v>0.013812874190963</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000439932837548017</v>
+        <v>10848664601456551846408080</v>
       </c>
       <c r="H101" t="n">
-        <v>0.013813507073151</v>
+        <v>846133160396.443</v>
       </c>
       <c r="I101" t="n">
-        <v>0.127343257916698</v>
+        <v>100</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5399,19 +5399,19 @@
         <v>47</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000440227741137358</v>
+        <v>0.000438981599825951</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0138392780569769</v>
+        <v>0.0138334368122082</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000439889037385186</v>
+        <v>0.000439292226322175</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0138201674235698</v>
+        <v>0.013824060792627</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.076997543331736</v>
+        <v>0.0707106744921736</v>
       </c>
       <c r="J102" t="n">
         <v>1356</v>
@@ -5431,19 +5431,19 @@
         <v>45</v>
       </c>
       <c r="E103" t="n">
-        <v>0.000559170442558627</v>
+        <v>0.000558798164577488</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0139902568196337</v>
+        <v>0.0139743854695192</v>
       </c>
       <c r="G103" t="n">
-        <v>0.000558716114995292</v>
+        <v>0.108249795012728</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0139783759557194</v>
+        <v>0.113327011910173</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0813163521044881</v>
+        <v>99.483788246886</v>
       </c>
       <c r="J103" t="n">
         <v>1356</v>
@@ -5463,19 +5463,19 @@
         <v>46</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000557490577643694</v>
+        <v>0.00055818095311996</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139575795695807</v>
+        <v>0.0139589845681622</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000557542241815354</v>
+        <v>36902820963009901616042682220602</v>
       </c>
       <c r="H104" t="n">
-        <v>0.013957339772375</v>
+        <v>800733440939525</v>
       </c>
       <c r="I104" t="n">
-        <v>0.00926641387605065</v>
+        <v>100</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5495,19 +5495,19 @@
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>0.00055751307365491</v>
+        <v>0.000559873314724679</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0139653203313397</v>
+        <v>0.013989174368609</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000557596869377783</v>
+        <v>0.000557660362669065</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0139731596377678</v>
+        <v>0.0139754776541956</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0150280117185506</v>
+        <v>-0.396827926772795</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5527,19 +5527,19 @@
         <v>45</v>
       </c>
       <c r="E106" t="n">
-        <v>0.000371895565795647</v>
+        <v>0.000372037724034667</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0135897678788862</v>
+        <v>0.0135968400352563</v>
       </c>
       <c r="G106" t="n">
-        <v>0.000372624597465856</v>
+        <v>0.116525122599012</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0136089745245126</v>
+        <v>0.102525765975784</v>
       </c>
       <c r="I106" t="n">
-        <v>0.195647757868694</v>
+        <v>99.6807231644673</v>
       </c>
       <c r="J106" t="n">
         <v>1356</v>
@@ -5559,19 +5559,19 @@
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000372242456245276</v>
+        <v>0.000372174611960337</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0135937467540886</v>
+        <v>0.0135926151975848</v>
       </c>
       <c r="G107" t="n">
-        <v>0.000372215449220261</v>
+        <v>19406642626673284940226008666</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0135938511228356</v>
+        <v>26418811675231.6</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.00725575068721788</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5591,19 +5591,19 @@
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000372775603828952</v>
+        <v>0.000372722713321479</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0136278137891505</v>
+        <v>0.013626199446616</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000372350386067935</v>
+        <v>0.000372616176314987</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136145057252948</v>
+        <v>0.0136245443942668</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.114198286594205</v>
+        <v>-0.0285916214228612</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5623,19 +5623,19 @@
         <v>45</v>
       </c>
       <c r="E109" t="n">
-        <v>0.000372037680607373</v>
+        <v>0.00037258813190111</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0136058231189924</v>
+        <v>0.0136141959046559</v>
       </c>
       <c r="G109" t="n">
-        <v>0.000372665297104605</v>
+        <v>2.3411406348586</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0136080196892962</v>
+        <v>0.327002529302158</v>
       </c>
       <c r="I109" t="n">
-        <v>0.168412916927802</v>
+        <v>99.9840851879484</v>
       </c>
       <c r="J109" t="n">
         <v>1356</v>
@@ -5655,19 +5655,19 @@
         <v>46</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000372178470069345</v>
+        <v>0.000372134981902324</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0135939806715859</v>
+        <v>0.0135933121017579</v>
       </c>
       <c r="G110" t="n">
-        <v>0.000372098558584909</v>
+        <v>14999272694359400687462440848648</v>
       </c>
       <c r="H110" t="n">
-        <v>0.013591277479007</v>
+        <v>317768517041104</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0214758919625895</v>
+        <v>100</v>
       </c>
       <c r="J110" t="n">
         <v>1356</v>
@@ -5687,19 +5687,19 @@
         <v>47</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000372353989403331</v>
+        <v>0.000372394122503187</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0136134716016774</v>
+        <v>0.0136220571093058</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000372454111679961</v>
+        <v>0.000373348612259274</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0136155275231696</v>
+        <v>0.0136305973758667</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0268817750939161</v>
+        <v>0.255656436034763</v>
       </c>
       <c r="J111" t="n">
         <v>1356</v>
@@ -5719,19 +5719,19 @@
         <v>45</v>
       </c>
       <c r="E112" t="n">
-        <v>0.000430247083492509</v>
+        <v>0.00042983900654174</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0144986640399565</v>
+        <v>0.0145012150868917</v>
       </c>
       <c r="G112" t="n">
-        <v>0.000429339663370881</v>
+        <v>0.173715916716294</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0144881553284123</v>
+        <v>0.130015680713026</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.211352502236495</v>
+        <v>99.7525621056108</v>
       </c>
       <c r="J112" t="n">
         <v>904</v>
@@ -5750,15 +5750,21 @@
       <c r="D113" t="s">
         <v>48</v>
       </c>
-      <c r="E113"/>
-      <c r="F113"/>
+      <c r="E113" t="n">
+        <v>861893.605040586</v>
+      </c>
+      <c r="F113" t="n">
+        <v>49.7583417996184</v>
+      </c>
       <c r="G113" t="n">
-        <v>2404425827.57745</v>
+        <v>13543458499145224238680400860686622806280800646222062882668608862624644824002402060446260406822800866626406420420444040804264064828420668242262084040440440440</v>
       </c>
       <c r="H113" t="n">
-        <v>2441.41900095336</v>
-      </c>
-      <c r="I113"/>
+        <v>122404361775533301320082440804666288464884402046880244442066644062020822284068</v>
+      </c>
+      <c r="I113" t="n">
+        <v>100</v>
+      </c>
       <c r="J113" t="n">
         <v>904</v>
       </c>
@@ -5777,19 +5783,19 @@
         <v>46</v>
       </c>
       <c r="E114" t="n">
-        <v>0.00047481267349847</v>
+        <v>0.000474841069596145</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0158020596421369</v>
+        <v>0.0158033446461774</v>
       </c>
       <c r="G114" t="n">
-        <v>0.000474785434639685</v>
+        <v>1269699275060422009788228882886</v>
       </c>
       <c r="H114" t="n">
-        <v>0.015802429815078</v>
+        <v>176798610659430</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.00573708812409808</v>
+        <v>100</v>
       </c>
       <c r="J114" t="n">
         <v>904</v>
@@ -5809,19 +5815,19 @@
         <v>47</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000426323956195014</v>
+        <v>0.000425595138372357</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0143969066963335</v>
+        <v>0.014374237939056</v>
       </c>
       <c r="G115" t="n">
-        <v>0.000426430494028449</v>
+        <v>0.000428598860635481</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0144006440582725</v>
+        <v>0.0144500733452299</v>
       </c>
       <c r="I115" t="n">
-        <v>0.024983633892737</v>
+        <v>0.70082366963619</v>
       </c>
       <c r="J115" t="n">
         <v>904</v>
@@ -5841,19 +5847,19 @@
         <v>45</v>
       </c>
       <c r="E116" t="n">
-        <v>0.00264507419461069</v>
+        <v>0.00264100909534991</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0395668341708678</v>
+        <v>0.039543968831032</v>
       </c>
       <c r="G116" t="n">
-        <v>0.00264374727335584</v>
+        <v>0.00574199846516128</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0395842296870537</v>
+        <v>0.0548040541278418</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0501909266527926</v>
+        <v>54.0054022763357</v>
       </c>
       <c r="J116" t="n">
         <v>143</v>
@@ -5873,19 +5879,19 @@
         <v>46</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265430512021248</v>
+        <v>0.00265426336980726</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0397867992543847</v>
+        <v>0.03979370193923</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00265606610089042</v>
+        <v>335241.314716146</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0397978844452308</v>
+        <v>253.63394832117</v>
       </c>
       <c r="I117" t="n">
-        <v>0.0663003333140252</v>
+        <v>99.9999992082529</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5905,19 +5911,19 @@
         <v>47</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0026436180559364</v>
+        <v>0.00264653742910922</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0395675236212835</v>
+        <v>0.0395832558915342</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00266118006855168</v>
+        <v>0.00266440647433599</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0396564853719766</v>
+        <v>0.0398249296019305</v>
       </c>
       <c r="I118" t="n">
-        <v>0.65993326880865</v>
+        <v>0.670657626712882</v>
       </c>
       <c r="J118" t="n">
         <v>143</v>
@@ -5937,19 +5943,19 @@
         <v>45</v>
       </c>
       <c r="E119" t="n">
-        <v>0.00109659728499065</v>
+        <v>0.00109254338330587</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0251716101575497</v>
+        <v>0.0251817429619777</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0011011767812125</v>
+        <v>0.00137954121846074</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0252106974181872</v>
+        <v>0.0289339747292865</v>
       </c>
       <c r="I119" t="n">
-        <v>0.415872937023671</v>
+        <v>20.8038608281016</v>
       </c>
       <c r="J119" t="n">
         <v>59</v>
@@ -5968,15 +5974,21 @@
       <c r="D120" t="s">
         <v>48</v>
       </c>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120" t="n">
-        <v>0.00332991506408016</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.0495576820432755</v>
-      </c>
-      <c r="I120"/>
+      <c r="E120" t="n">
+        <v>0.0033324142801694</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.0495795501894736</v>
+      </c>
+      <c r="G120" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H120" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="I120" t="e">
+        <v>#NUM!</v>
+      </c>
       <c r="J120" t="n">
         <v>59</v>
       </c>
@@ -5995,19 +6007,19 @@
         <v>46</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00109380089856025</v>
+        <v>0.00109079005040239</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0250853144212491</v>
+        <v>0.025027597860864</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0010917498849824</v>
+        <v>38.1771348238671</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0249999291145625</v>
+        <v>2.75179086235585</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.187864785337626</v>
+        <v>99.9971428184555</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -6027,19 +6039,19 @@
         <v>47</v>
       </c>
       <c r="E122" t="n">
-        <v>0.00109552929555283</v>
+        <v>0.00109497787505133</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0251751710585347</v>
+        <v>0.0251798795846931</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0010996173179241</v>
+        <v>0.00110131294451049</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0252785527858619</v>
+        <v>0.0253913687011055</v>
       </c>
       <c r="I122" t="n">
-        <v>0.371767732704645</v>
+        <v>0.575228820357692</v>
       </c>
       <c r="J122" t="n">
         <v>59</v>
@@ -6059,19 +6071,19 @@
         <v>45</v>
       </c>
       <c r="E123" t="n">
-        <v>0.000583114699007834</v>
+        <v>0.000584890388651837</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0163907440330837</v>
+        <v>0.0164159722224607</v>
       </c>
       <c r="G123" t="n">
-        <v>0.000583629701596443</v>
+        <v>0.0899802296332344</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0164130089692977</v>
+        <v>0.0815518453341899</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0882413261697233</v>
+        <v>99.3499789997915</v>
       </c>
       <c r="J123" t="n">
         <v>1356</v>
@@ -6091,19 +6103,19 @@
         <v>46</v>
       </c>
       <c r="E124" t="n">
-        <v>0.00058577207704044</v>
+        <v>0.00058686123540664</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164477758402155</v>
+        <v>0.0164496828267809</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000585337474035628</v>
+        <v>114795639390473819512682440600</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0164460564430517</v>
+        <v>88253646804332.2</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0742482796831417</v>
+        <v>100</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -6123,19 +6135,19 @@
         <v>47</v>
       </c>
       <c r="E125" t="n">
-        <v>0.000580640319003607</v>
+        <v>0.000580794092966429</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0163772188180764</v>
+        <v>0.0163908667506472</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000581112557127129</v>
+        <v>0.000582134170835339</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0163734630386546</v>
+        <v>0.0163813312438403</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0812644844325099</v>
+        <v>0.23020086022223</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -6155,19 +6167,19 @@
         <v>45</v>
       </c>
       <c r="E126" t="n">
-        <v>0.000701011849004057</v>
+        <v>0.000702770158500836</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0165500009792045</v>
+        <v>0.0165672406145152</v>
       </c>
       <c r="G126" t="n">
-        <v>0.000703590516628169</v>
+        <v>1.45368439778653</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0165515635423077</v>
+        <v>0.32563833453619</v>
       </c>
       <c r="I126" t="n">
-        <v>0.366501191128925</v>
+        <v>99.9516559330505</v>
       </c>
       <c r="J126" t="n">
         <v>1356</v>
@@ -6187,19 +6199,19 @@
         <v>46</v>
       </c>
       <c r="E127" t="n">
-        <v>0.000703491137037103</v>
+        <v>0.000704167769198529</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0165951422151892</v>
+        <v>0.0165915862716347</v>
       </c>
       <c r="G127" t="n">
-        <v>0.00070418541068741</v>
+        <v>2287091785802414670820044226</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0165951031675481</v>
+        <v>12813265000812.2</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0985924501942939</v>
+        <v>100</v>
       </c>
       <c r="J127" t="n">
         <v>1356</v>
@@ -6219,19 +6231,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000699943310634201</v>
+        <v>0.000698653502862149</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0165193797318583</v>
+        <v>0.016509070825696</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000699644450085555</v>
+        <v>0.000701151689077348</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0165256257125</v>
+        <v>0.0165616799806974</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0427160607948698</v>
+        <v>0.356297539336568</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -6251,19 +6263,19 @@
         <v>45</v>
       </c>
       <c r="E129" t="n">
-        <v>0.00051561448815992</v>
+        <v>0.00051611964022504</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0161707100818756</v>
+        <v>0.0161712808536966</v>
       </c>
       <c r="G129" t="n">
-        <v>0.000516400009244666</v>
+        <v>0.188159849984457</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0161947442356071</v>
+        <v>0.125803072521358</v>
       </c>
       <c r="I129" t="n">
-        <v>0.15211484715015</v>
+        <v>99.7257015031274</v>
       </c>
       <c r="J129" t="n">
         <v>1356</v>
@@ -6283,19 +6295,19 @@
         <v>46</v>
       </c>
       <c r="E130" t="n">
-        <v>0.000518336549636704</v>
+        <v>0.000518224079072012</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0162281209096157</v>
+        <v>0.0162278462992002</v>
       </c>
       <c r="G130" t="n">
-        <v>0.000518131388393137</v>
+        <v>3611279088162450896840248488</v>
       </c>
       <c r="H130" t="n">
-        <v>0.016225891041967</v>
+        <v>9285196149815.07</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.039596374232995</v>
+        <v>100</v>
       </c>
       <c r="J130" t="n">
         <v>1356</v>
@@ -6315,19 +6327,19 @@
         <v>47</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000513712075162741</v>
+        <v>0.000514774311335651</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0161503679252733</v>
+        <v>0.0161765616308586</v>
       </c>
       <c r="G131" t="n">
-        <v>0.000514671814590104</v>
+        <v>0.000515329870477427</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0161581125851082</v>
+        <v>0.0161704093524285</v>
       </c>
       <c r="I131" t="n">
-        <v>0.186476002795646</v>
+        <v>0.107806508724465</v>
       </c>
       <c r="J131" t="n">
         <v>1356</v>
@@ -6347,19 +6359,19 @@
         <v>45</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0005164595300636</v>
+        <v>0.000516257903246968</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0162013589034783</v>
+        <v>0.0161829799181657</v>
       </c>
       <c r="G132" t="n">
-        <v>0.000516404958274734</v>
+        <v>2.81294250975771</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0161907914102341</v>
+        <v>0.381154742877235</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0105676345650642</v>
+        <v>99.9816470510344</v>
       </c>
       <c r="J132" t="n">
         <v>1356</v>
@@ -6379,19 +6391,19 @@
         <v>46</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000518164540278918</v>
+        <v>0.000518211563612468</v>
       </c>
       <c r="F133" t="n">
-        <v>0.016227675782918</v>
+        <v>0.0162294617466609</v>
       </c>
       <c r="G133" t="n">
-        <v>0.00051797644827207</v>
+        <v>9709264699689948861806026</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0162213557028169</v>
+        <v>853133628221.636</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0363128492571698</v>
+        <v>100</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6411,19 +6423,19 @@
         <v>47</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000514147577262644</v>
+        <v>0.000514380004990233</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0161578907158738</v>
+        <v>0.0161483359148394</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000513996383004751</v>
+        <v>0.000515076463171466</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0161581364752911</v>
+        <v>0.0161796361912256</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0294154322659313</v>
+        <v>0.135214522703015</v>
       </c>
       <c r="J134" t="n">
         <v>1356</v>
@@ -6443,19 +6455,19 @@
         <v>45</v>
       </c>
       <c r="E135" t="n">
-        <v>0.000483696176071203</v>
+        <v>0.00048217775559389</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0161514498131664</v>
+        <v>0.0161317617890898</v>
       </c>
       <c r="G135" t="n">
-        <v>0.00048363747201322</v>
+        <v>0.201609693366624</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0161320677623141</v>
+        <v>0.135172981048068</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0121380292844216</v>
+        <v>99.7608360255193</v>
       </c>
       <c r="J135" t="n">
         <v>904</v>
@@ -6475,19 +6487,19 @@
         <v>46</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000490878552965174</v>
+        <v>0.000490915983527293</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0163559905371373</v>
+        <v>0.0163565847599263</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000490877120900325</v>
+        <v>47959938651757136</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0163552668770838</v>
+        <v>80311395.1988989</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.000291735912561912</v>
+        <v>100</v>
       </c>
       <c r="J136" t="n">
         <v>904</v>
@@ -6507,19 +6519,19 @@
         <v>47</v>
       </c>
       <c r="E137" t="n">
-        <v>0.000468225507564071</v>
+        <v>0.000481860985723337</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0157496314303574</v>
+        <v>0.016085970191462</v>
       </c>
       <c r="G137" t="n">
-        <v>0.000468566827262995</v>
+        <v>0.000636602152815492</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0157574433843928</v>
+        <v>0.0181907760742858</v>
       </c>
       <c r="I137" t="n">
-        <v>0.0728433339846137</v>
+        <v>24.3073584353718</v>
       </c>
       <c r="J137" t="n">
         <v>904</v>
@@ -6567,13 +6579,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119438462163363</v>
+        <v>0.00119395385892208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00119458865439075</v>
+        <v>11.0279104997224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00432327902818693</v>
+        <v>99.3610583568221</v>
       </c>
     </row>
     <row r="3">
@@ -6587,13 +6599,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>204068095915965596048606064040008626646608662620602282860082228</v>
-      </c>
-      <c r="E3" t="n">
-        <v>172347176483064089728824868042480486644022666402082820442844882</v>
+        <v>5137512462205652413888644088246426842648628468268202486068884406</v>
+      </c>
+      <c r="E3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>-347.999551434823</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -6607,13 +6619,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00119687559853821</v>
+        <v>0.00119644730129442</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119964779467855</v>
+        <v>0.00119708504868889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.280699383754543</v>
+        <v>3.3403461809327</v>
       </c>
     </row>
     <row r="5">
@@ -6627,13 +6639,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00119426830507788</v>
+        <v>0.00119376692844099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00119492420734497</v>
+        <v>0.108031573032016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.167347775489478</v>
+        <v>60.5407184114848</v>
       </c>
     </row>
     <row r="6">
@@ -6647,13 +6659,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00147367991211808</v>
+        <v>0.00147405270310906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00147377279850152</v>
+        <v>160422.747060652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0111663216390704</v>
+        <v>99.9998452663547</v>
       </c>
     </row>
     <row r="7">
@@ -6667,13 +6679,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00146785114231172</v>
+        <v>0.00146729714817831</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00147077944151031</v>
+        <v>0.00148426686137706</v>
       </c>
       <c r="F7" t="n">
-        <v>0.193507005688194</v>
+        <v>3.77446710971993</v>
       </c>
     </row>
     <row r="8">
@@ -6687,13 +6699,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00146848151570725</v>
+        <v>0.00146862951716468</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00146917557330902</v>
+        <v>0.104920583866912</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0703911481313604</v>
+        <v>78.642429356037</v>
       </c>
     </row>
     <row r="9">
@@ -6707,13 +6719,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000420995033227226</v>
+        <v>0.000420991993733629</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000420968343805203</v>
+        <v>211616550355743410346440804604</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0106010101340321</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -6727,13 +6739,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000077465382529251</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1202212913.78877</v>
+        <v>430946.80260661</v>
+      </c>
+      <c r="E10" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F10" t="n">
-        <v>20.2017001488878</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -6747,13 +6759,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000401195013699451</v>
+        <v>0.000403251626771012</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000401244934038553</v>
+        <v>0.000554839743929818</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.000936654916328482</v>
+        <v>24.670980527612</v>
       </c>
     </row>
     <row r="12">
@@ -6767,13 +6779,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000405740573891695</v>
+        <v>0.00040546097638623</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000405335934856396</v>
+        <v>0.105460025525905</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0549187632471368</v>
+        <v>98.78127420846</v>
       </c>
     </row>
     <row r="13">
@@ -6787,13 +6799,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000441735800708</v>
+        <v>0.000442071890677071</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000441908939559101</v>
+        <v>87626812845620546344446028886</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0338578772468445</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -6807,13 +6819,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00126737962284537</v>
+        <v>0.00126981598313535</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0476740802699269</v>
+        <v>3891958770768186368</v>
       </c>
       <c r="F14" t="n">
-        <v>97.3415750955874</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6827,13 +6839,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000441033836231684</v>
+        <v>0.000440564090434484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000440791671477844</v>
+        <v>0.000455720375049133</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0257227692296976</v>
+        <v>9.04164133023891</v>
       </c>
     </row>
     <row r="16">
@@ -6847,13 +6859,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000441233106081816</v>
+        <v>0.000441294156637787</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000441353918125393</v>
+        <v>5.68462235940287</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.00853668951284678</v>
+        <v>99.7841900781019</v>
       </c>
     </row>
     <row r="17">
@@ -6867,13 +6879,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000562486819220138</v>
+        <v>0.000562759995333404</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00056262271171133</v>
+        <v>6230509742627524840868808024046</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00664190236030689</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -6887,13 +6899,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00139923667934089</v>
+        <v>0.00139629764952591</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0401467513215883</v>
+        <v>15367693778721796096</v>
       </c>
       <c r="F18" t="n">
-        <v>96.5146951290465</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -6907,13 +6919,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000561615703718293</v>
+        <v>0.000561972197477516</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000561745154859598</v>
+        <v>0.000603969296666689</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0141322824365427</v>
+        <v>11.4111285028998</v>
       </c>
     </row>
     <row r="20">
@@ -6927,13 +6939,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.000562101115733087</v>
+        <v>0.000562120307593838</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000562277221475015</v>
+        <v>7.81659012877052</v>
       </c>
       <c r="F20" t="n">
-        <v>0.034905024434848</v>
+        <v>99.8756277158341</v>
       </c>
     </row>
     <row r="21">
@@ -6947,13 +6959,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000371618187243728</v>
+        <v>0.000371568089697812</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000371537410807743</v>
+        <v>4687100614077496512422062024</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0232679423810507</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -6967,13 +6979,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0011909338917502</v>
+        <v>0.00118824749843996</v>
       </c>
       <c r="E22" t="n">
-        <v>0.077263352385427</v>
+        <v>14935385816631754752</v>
       </c>
       <c r="F22" t="n">
-        <v>98.4586044289028</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -6987,13 +6999,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000371119428807199</v>
+        <v>0.000371201337542346</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000371207471883822</v>
+        <v>0.000391452009893379</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0559880603139178</v>
+        <v>19.518673196034</v>
       </c>
     </row>
     <row r="24">
@@ -7007,13 +7019,13 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000370854209337636</v>
+        <v>0.000371132270925534</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000371157071802815</v>
+        <v>0.305659771584419</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02410405454677</v>
+        <v>99.7813280292653</v>
       </c>
     </row>
     <row r="25">
@@ -7027,13 +7039,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000372465254807651</v>
+        <v>0.000372499585946023</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000372454341469131</v>
+        <v>6182205899818243228462262084622</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0110665697011557</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -7047,13 +7059,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00119384242110496</v>
+        <v>0.00119220020257798</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0549912899133693</v>
+        <v>753935276335988352</v>
       </c>
       <c r="F26" t="n">
-        <v>97.8290336106215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -7067,13 +7079,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000372007783974588</v>
+        <v>0.000372103386921139</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000371960103763357</v>
+        <v>0.000380840300843061</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0513897624480853</v>
+        <v>13.1570050015894</v>
       </c>
     </row>
     <row r="28">
@@ -7087,13 +7099,13 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000372413903396481</v>
+        <v>0.000372376269786734</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000372263069999716</v>
+        <v>238.580661407815</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0352566570274457</v>
+        <v>99.9790192445893</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Stress_Testing.xlsx
+++ b/results/consolidated/Stress_Testing.xlsx
@@ -2198,21 +2198,15 @@
       <c r="D2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.000167060051091674</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0097160293461996</v>
-      </c>
+      <c r="E2"/>
+      <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.00328773065419902</v>
+        <v>0.000168012848226876</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0321242332832427</v>
-      </c>
-      <c r="I2" t="n">
-        <v>94.9186819522971</v>
-      </c>
+        <v>0.00973553854254884</v>
+      </c>
+      <c r="I2"/>
       <c r="J2" t="n">
         <v>143</v>
       </c>
@@ -2231,19 +2225,19 @@
         <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000166755786760434</v>
+        <v>0.000166579194872054</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00969366653972052</v>
+        <v>0.00968593764702744</v>
       </c>
       <c r="G3" t="n">
-        <v>476993.796423682</v>
+        <v>0.000166381990293448</v>
       </c>
       <c r="H3" t="n">
-        <v>292.946375698563</v>
+        <v>0.00976701803883266</v>
       </c>
       <c r="I3" t="n">
-        <v>99.9999999650403</v>
+        <v>-0.118525195099978</v>
       </c>
       <c r="J3" t="n">
         <v>143</v>
@@ -2263,19 +2257,19 @@
         <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000167140278532068</v>
+        <v>0.000166815781257125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00972534093221202</v>
+        <v>0.00971650641276406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000190817373937572</v>
+        <v>0.0001669427015022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0106581633526229</v>
+        <v>0.00965139999178962</v>
       </c>
       <c r="I4" t="n">
-        <v>12.4082492683557</v>
+        <v>0.076026231714664</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -2294,21 +2288,15 @@
       <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.0000387064223420935</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.00475033304294473</v>
-      </c>
+      <c r="E5"/>
+      <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.0000727079147849368</v>
+        <v>0.0000394838595218529</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00641436896930559</v>
-      </c>
-      <c r="I5" t="n">
-        <v>46.7644994955728</v>
-      </c>
+        <v>0.00479387637026704</v>
+      </c>
+      <c r="I5"/>
       <c r="J5" t="n">
         <v>59</v>
       </c>
@@ -2326,21 +2314,15 @@
       <c r="D6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.0000519664519178929</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.00561745478287671</v>
-      </c>
-      <c r="G6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I6" t="e">
-        <v>#NUM!</v>
-      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6" t="n">
+        <v>0.0000389778236759456</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.00477347833269457</v>
+      </c>
+      <c r="I6"/>
       <c r="J6" t="n">
         <v>59</v>
       </c>
@@ -2359,19 +2341,19 @@
         <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000388421863096695</v>
+        <v>0.0000387957070981156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00475591982179513</v>
+        <v>0.00474667517951247</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00467847599491846</v>
+        <v>0.0000399185335244449</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0384358019317937</v>
+        <v>0.0048028757742464</v>
       </c>
       <c r="I7" t="n">
-        <v>99.1697683956943</v>
+        <v>2.81279477774816</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -2391,19 +2373,19 @@
         <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000386734603413487</v>
+        <v>0.0000387570034031266</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00475809499589118</v>
+        <v>0.00476039850152443</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000490139724867914</v>
+        <v>0.0000396218173989364</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0053785055710382</v>
+        <v>0.00485875183121341</v>
       </c>
       <c r="I8" t="n">
-        <v>21.0970701226663</v>
+        <v>2.18267119628144</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -2422,21 +2404,15 @@
       <c r="D9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.0000908530260677112</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0036598614011438</v>
-      </c>
+      <c r="E9"/>
+      <c r="F9"/>
       <c r="G9" t="n">
-        <v>1.19897610341558</v>
+        <v>0.0000909163197171449</v>
       </c>
       <c r="H9" t="n">
-        <v>0.272513373333378</v>
-      </c>
-      <c r="I9" t="n">
-        <v>99.9924224489705</v>
-      </c>
+        <v>0.00367913244714291</v>
+      </c>
+      <c r="I9"/>
       <c r="J9" t="n">
         <v>1356</v>
       </c>
@@ -2455,19 +2431,19 @@
         <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000909058233194078</v>
+        <v>0.000090804601785614</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00366204608945209</v>
+        <v>0.00366257576200618</v>
       </c>
       <c r="G10" t="n">
-        <v>79590280149677662626600282426</v>
+        <v>0.0000909780585583841</v>
       </c>
       <c r="H10" t="n">
-        <v>22785314919975.8</v>
+        <v>0.00368940049730537</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>0.190657808617485</v>
       </c>
       <c r="J10" t="n">
         <v>1356</v>
@@ -2487,19 +2463,19 @@
         <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000908219625815204</v>
+        <v>0.0000908485643974246</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00366156762489663</v>
+        <v>0.00366297948091831</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000122645237714701</v>
+        <v>0.0000909876459286935</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00494707153174301</v>
+        <v>0.00367675730170656</v>
       </c>
       <c r="I11" t="n">
-        <v>25.9474201576489</v>
+        <v>0.152857599346914</v>
       </c>
       <c r="J11" t="n">
         <v>1356</v>
@@ -2518,21 +2494,15 @@
       <c r="D12" t="s">
         <v>45</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.000210440650302616</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.00381368557338174</v>
-      </c>
+      <c r="E12"/>
+      <c r="F12"/>
       <c r="G12" t="n">
-        <v>1.11328722884577</v>
+        <v>0.000210879445356703</v>
       </c>
       <c r="H12" t="n">
-        <v>0.229242682497363</v>
-      </c>
-      <c r="I12" t="n">
-        <v>99.9810973624012</v>
-      </c>
+        <v>0.00384133893310973</v>
+      </c>
+      <c r="I12"/>
       <c r="J12" t="n">
         <v>1356</v>
       </c>
@@ -2551,19 +2521,19 @@
         <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000210321003057071</v>
+        <v>0.000210254496800259</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00380946777652011</v>
+        <v>0.00380997113314445</v>
       </c>
       <c r="G13" t="n">
-        <v>143346779720594072920624864</v>
+        <v>0.000210763566417222</v>
       </c>
       <c r="H13" t="n">
-        <v>2982687618779.47</v>
+        <v>0.00382248703932163</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>0.24153587150642</v>
       </c>
       <c r="J13" t="n">
         <v>1356</v>
@@ -2583,19 +2553,19 @@
         <v>47</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000210497563522436</v>
+        <v>0.000210377572519542</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00381282956103804</v>
+        <v>0.00380676293636833</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00022724872491064</v>
+        <v>0.000210894180591132</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0048538575703426</v>
+        <v>0.00384833573944941</v>
       </c>
       <c r="I14" t="n">
-        <v>7.37128949559183</v>
+        <v>0.2449607998388</v>
       </c>
       <c r="J14" t="n">
         <v>1356</v>
@@ -2614,21 +2584,15 @@
       <c r="D15" t="s">
         <v>45</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.0000220700115744689</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.00344752879381929</v>
-      </c>
+      <c r="E15"/>
+      <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.858209591340179</v>
+        <v>0.0000223524231367376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.174482027461516</v>
-      </c>
-      <c r="I15" t="n">
-        <v>99.9974283657748</v>
-      </c>
+        <v>0.00347565341858694</v>
+      </c>
+      <c r="I15"/>
       <c r="J15" t="n">
         <v>1356</v>
       </c>
@@ -2647,19 +2611,19 @@
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0000220791358433378</v>
+        <v>0.0000220799266004002</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00344540410793817</v>
+        <v>0.00344540137862936</v>
       </c>
       <c r="G16" t="n">
-        <v>1012256000407748953060624</v>
+        <v>0.0000226853640530436</v>
       </c>
       <c r="H16" t="n">
-        <v>293373131630.919</v>
+        <v>0.00349702121223252</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>2.66884609489955</v>
       </c>
       <c r="J16" t="n">
         <v>1356</v>
@@ -2679,19 +2643,19 @@
         <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000221043240948469</v>
+        <v>0.0000220949205839129</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00344604214680494</v>
+        <v>0.00344600852605675</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000483573504865673</v>
+        <v>0.0000221917077748464</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00451164268300031</v>
+        <v>0.00345762203315949</v>
       </c>
       <c r="I17" t="n">
-        <v>54.2896294514997</v>
+        <v>0.436141246611149</v>
       </c>
       <c r="J17" t="n">
         <v>1356</v>
@@ -2710,21 +2674,15 @@
       <c r="D18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.0000222144749748038</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.00345182587736224</v>
-      </c>
+      <c r="E18"/>
+      <c r="F18"/>
       <c r="G18" t="n">
-        <v>50.469578319931</v>
+        <v>0.0000224495910178183</v>
       </c>
       <c r="H18" t="n">
-        <v>1.13814338041259</v>
-      </c>
-      <c r="I18" t="n">
-        <v>99.9999559844252</v>
-      </c>
+        <v>0.00348469207961156</v>
+      </c>
+      <c r="I18"/>
       <c r="J18" t="n">
         <v>1356</v>
       </c>
@@ -2743,19 +2701,19 @@
         <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000221899397717547</v>
+        <v>0.0000221881623882588</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00344935610141183</v>
+        <v>0.00344875678687075</v>
       </c>
       <c r="G19" t="n">
-        <v>22093466622569025230488646208080</v>
+        <v>0.000022618362592109</v>
       </c>
       <c r="H19" t="n">
-        <v>750158314826588</v>
+        <v>0.00349553787471214</v>
       </c>
       <c r="I19" t="n">
-        <v>100</v>
+        <v>1.90199534603052</v>
       </c>
       <c r="J19" t="n">
         <v>1356</v>
@@ -2775,19 +2733,19 @@
         <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000221621863859769</v>
+        <v>0.0000222193652751415</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00344669411046873</v>
+        <v>0.00345373535608392</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0000415033355219271</v>
+        <v>0.0000222949695610232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00448558088531735</v>
+        <v>0.00346402184601575</v>
       </c>
       <c r="I20" t="n">
-        <v>46.6014330962192</v>
+        <v>0.339109168437254</v>
       </c>
       <c r="J20" t="n">
         <v>1356</v>
@@ -2806,21 +2764,15 @@
       <c r="D21" t="s">
         <v>45</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.000117013322846653</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.00991926777378683</v>
-      </c>
+      <c r="E21"/>
+      <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.196507617775403</v>
+        <v>0.000118104628623601</v>
       </c>
       <c r="H21" t="n">
-        <v>0.140496923242639</v>
-      </c>
-      <c r="I21" t="n">
-        <v>99.9404535436482</v>
-      </c>
+        <v>0.00996703116283773</v>
+      </c>
+      <c r="I21"/>
       <c r="J21" t="n">
         <v>904</v>
       </c>
@@ -2839,19 +2791,19 @@
         <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000116107422763441</v>
+        <v>0.000116117870014879</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00987489884426407</v>
+        <v>0.00987555242494208</v>
       </c>
       <c r="G22" t="n">
-        <v>1649104605170274664488</v>
+        <v>0.00011779484283482</v>
       </c>
       <c r="H22" t="n">
-        <v>12592265813.8566</v>
+        <v>0.00994643555308831</v>
       </c>
       <c r="I22" t="n">
-        <v>100</v>
+        <v>1.42363857328857</v>
       </c>
       <c r="J22" t="n">
         <v>904</v>
@@ -2871,19 +2823,19 @@
         <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000117780516126009</v>
+        <v>0.000117764638153365</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00996031268921406</v>
+        <v>0.00995610033257308</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000234010887217031</v>
+        <v>0.000117576650393178</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0113190628409199</v>
+        <v>0.00994260516877633</v>
       </c>
       <c r="I23" t="n">
-        <v>49.6687878385868</v>
+        <v>-0.15988528296921</v>
       </c>
       <c r="J23" t="n">
         <v>904</v>
@@ -2902,21 +2854,15 @@
       <c r="D24" t="s">
         <v>45</v>
       </c>
-      <c r="E24" t="n">
-        <v>0.000237810446967516</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0116771875486134</v>
-      </c>
+      <c r="E24"/>
+      <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.000824772299302325</v>
+        <v>0.000237924019937213</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0195641193646096</v>
-      </c>
-      <c r="I24" t="n">
-        <v>71.1665332154487</v>
-      </c>
+        <v>0.0117325121427731</v>
+      </c>
+      <c r="I24"/>
       <c r="J24" t="n">
         <v>143</v>
       </c>
@@ -2935,19 +2881,19 @@
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000240095309032806</v>
+        <v>0.000239922191818838</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0117446656744815</v>
+        <v>0.0117376735301604</v>
       </c>
       <c r="G25" t="n">
-        <v>372.715580003421</v>
+        <v>0.000234691761195535</v>
       </c>
       <c r="H25" t="n">
-        <v>9.23458240590991</v>
+        <v>0.0115964821194843</v>
       </c>
       <c r="I25" t="n">
-        <v>99.9999355821645</v>
+        <v>-2.22863836236042</v>
       </c>
       <c r="J25" t="n">
         <v>143</v>
@@ -2967,19 +2913,19 @@
         <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000237641945124602</v>
+        <v>0.000238480446974561</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0116837603236573</v>
+        <v>0.0116987687972906</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000237680524574997</v>
+        <v>0.000238722857025175</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0117016020283172</v>
+        <v>0.0117013659047123</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0162316413869237</v>
+        <v>0.101544549874364</v>
       </c>
       <c r="J26" t="n">
         <v>143</v>
@@ -2998,21 +2944,15 @@
       <c r="D27" t="s">
         <v>45</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.0000960855694598312</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.00735163006510339</v>
-      </c>
+      <c r="E27"/>
+      <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.000142573897090336</v>
+        <v>0.0000995129810803254</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00895306342534568</v>
-      </c>
-      <c r="I27" t="n">
-        <v>32.6064788711283</v>
-      </c>
+        <v>0.00755756152295052</v>
+      </c>
+      <c r="I27"/>
       <c r="J27" t="n">
         <v>59</v>
       </c>
@@ -3030,21 +2970,15 @@
       <c r="D28" t="s">
         <v>48</v>
       </c>
-      <c r="E28" t="n">
-        <v>20550049848822609652222466022864684268462482642842808624042226604</v>
-      </c>
-      <c r="F28" t="n">
-        <v>18662956080103713416062444664040</v>
-      </c>
-      <c r="G28" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H28" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I28" t="e">
-        <v>#NUM!</v>
-      </c>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28" t="n">
+        <v>0.292582175522293</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0833950533585992</v>
+      </c>
+      <c r="I28"/>
       <c r="J28" t="n">
         <v>59</v>
       </c>
@@ -3063,19 +2997,19 @@
         <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0000969738124565842</v>
+        <v>0.0000969867893887012</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00737052206623287</v>
+        <v>0.00737232284431006</v>
       </c>
       <c r="G29" t="n">
-        <v>0.136663566801025</v>
+        <v>0.0000948206981424455</v>
       </c>
       <c r="H29" t="n">
-        <v>0.205452551057615</v>
+        <v>0.00730920197224464</v>
       </c>
       <c r="I29" t="n">
-        <v>99.9290419423944</v>
+        <v>-2.28440761214565</v>
       </c>
       <c r="J29" t="n">
         <v>59</v>
@@ -3095,19 +3029,19 @@
         <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000965364261830818</v>
+        <v>0.0000965179057205221</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00737234648717838</v>
+        <v>0.00737682748491134</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0000953293779213857</v>
+        <v>0.0000955396205013617</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00726469957227106</v>
+        <v>0.00735827515496806</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.26618707476675</v>
+        <v>-1.0239576146804</v>
       </c>
       <c r="J30" t="n">
         <v>59</v>
@@ -3126,21 +3060,15 @@
       <c r="D31" t="s">
         <v>45</v>
       </c>
-      <c r="E31" t="n">
-        <v>0.000103391180028753</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.00454661968561084</v>
-      </c>
+      <c r="E31"/>
+      <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.0633262859850293</v>
+        <v>0.000103469299681138</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0717343823747028</v>
-      </c>
-      <c r="I31" t="n">
-        <v>99.8367326009721</v>
-      </c>
+        <v>0.00456600302431706</v>
+      </c>
+      <c r="I31"/>
       <c r="J31" t="n">
         <v>1356</v>
       </c>
@@ -3159,19 +3087,19 @@
         <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00010356670821453</v>
+        <v>0.000103558342650404</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00454853769130572</v>
+        <v>0.00454856448760986</v>
       </c>
       <c r="G32" t="n">
-        <v>331135294676860640864826464280</v>
+        <v>0.000103780232663501</v>
       </c>
       <c r="H32" t="n">
-        <v>126303315030649</v>
+        <v>0.00456031986314871</v>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>0.21380758878851</v>
       </c>
       <c r="J32" t="n">
         <v>1356</v>
@@ -3191,19 +3119,19 @@
         <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000103401244854563</v>
+        <v>0.000103480317007531</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00454618914655762</v>
+        <v>0.00455117280744454</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000109508688398545</v>
+        <v>0.000103467514539824</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00491832194956059</v>
+        <v>0.00455643765317813</v>
       </c>
       <c r="I33" t="n">
-        <v>5.57713148910596</v>
+        <v>-0.012373417651068</v>
       </c>
       <c r="J33" t="n">
         <v>1356</v>
@@ -3222,21 +3150,15 @@
       <c r="D34" t="s">
         <v>45</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.000222708168574501</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.00469172678876375</v>
-      </c>
+      <c r="E34"/>
+      <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.216064461026026</v>
+        <v>0.000222689674794028</v>
       </c>
       <c r="H34" t="n">
-        <v>0.13383874235707</v>
-      </c>
-      <c r="I34" t="n">
-        <v>99.8969251271047</v>
-      </c>
+        <v>0.00470639606659162</v>
+      </c>
+      <c r="I34"/>
       <c r="J34" t="n">
         <v>1356</v>
       </c>
@@ -3255,19 +3177,19 @@
         <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000223034876668562</v>
+        <v>0.000222923978069179</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00469604929680897</v>
+        <v>0.00469593411546063</v>
       </c>
       <c r="G35" t="n">
-        <v>423283843977773232044284424062</v>
+        <v>0.00022233574224847</v>
       </c>
       <c r="H35" t="n">
-        <v>84279365970437.2</v>
+        <v>0.004715386664599</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>-0.264570965855422</v>
       </c>
       <c r="J35" t="n">
         <v>1356</v>
@@ -3287,19 +3209,19 @@
         <v>47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00022266429351872</v>
+        <v>0.000222673200796565</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00469598445609856</v>
+        <v>0.004690670067332</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000398989220843613</v>
+        <v>0.00022289278399334</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00660599276976911</v>
+        <v>0.00469636719445802</v>
       </c>
       <c r="I36" t="n">
-        <v>44.192904999307</v>
+        <v>0.0985151662791784</v>
       </c>
       <c r="J36" t="n">
         <v>1356</v>
@@ -3318,21 +3240,15 @@
       <c r="D37" t="s">
         <v>45</v>
       </c>
-      <c r="E37" t="n">
-        <v>0.0000352578047765636</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.00433474934788131</v>
-      </c>
+      <c r="E37"/>
+      <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.0245124452952953</v>
+        <v>0.0000354850101297475</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0422022588207407</v>
-      </c>
-      <c r="I37" t="n">
-        <v>99.8561636574735</v>
-      </c>
+        <v>0.00434752632850846</v>
+      </c>
+      <c r="I37"/>
       <c r="J37" t="n">
         <v>1356</v>
       </c>
@@ -3351,19 +3267,19 @@
         <v>46</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000352748739793425</v>
+        <v>0.0000352705477561542</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00433061563328579</v>
+        <v>0.00433052523885052</v>
       </c>
       <c r="G38" t="n">
-        <v>2832239377119420632848226424</v>
+        <v>0.0000360503228540325</v>
       </c>
       <c r="H38" t="n">
-        <v>12918355194499.3</v>
+        <v>0.00439270892941174</v>
       </c>
       <c r="I38" t="n">
-        <v>100</v>
+        <v>2.16301834808957</v>
       </c>
       <c r="J38" t="n">
         <v>1356</v>
@@ -3383,19 +3299,19 @@
         <v>47</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000352521091629185</v>
+        <v>0.0000352540528602681</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00433498539112052</v>
+        <v>0.00433415790010168</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0000408254576366535</v>
+        <v>0.0000352804169931256</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00470502015939213</v>
+        <v>0.00434821739079862</v>
       </c>
       <c r="I39" t="n">
-        <v>13.6516497214504</v>
+        <v>0.0747273844938758</v>
       </c>
       <c r="J39" t="n">
         <v>1356</v>
@@ -3414,21 +3330,15 @@
       <c r="D40" t="s">
         <v>45</v>
       </c>
-      <c r="E40" t="n">
-        <v>0.0000352775343435518</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.00433183398371391</v>
-      </c>
+      <c r="E40"/>
+      <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.122907505900349</v>
+        <v>0.0000352589255565391</v>
       </c>
       <c r="H40" t="n">
-        <v>0.115840018899355</v>
-      </c>
-      <c r="I40" t="n">
-        <v>99.9712974939284</v>
-      </c>
+        <v>0.00434582816655067</v>
+      </c>
+      <c r="I40"/>
       <c r="J40" t="n">
         <v>1356</v>
       </c>
@@ -3447,19 +3357,19 @@
         <v>46</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000353338580682214</v>
+        <v>0.0000353374215145726</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00433350095598423</v>
+        <v>0.00433360658217021</v>
       </c>
       <c r="G41" t="n">
-        <v>485348844557453183328442444</v>
+        <v>0.000035523145871124</v>
       </c>
       <c r="H41" t="n">
-        <v>5424648465412.42</v>
+        <v>0.00437914514010886</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>0.5228263206902</v>
       </c>
       <c r="J41" t="n">
         <v>1356</v>
@@ -3479,19 +3389,19 @@
         <v>47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000352922150212067</v>
+        <v>0.0000352947558372005</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00433419638527062</v>
+        <v>0.00433255926073636</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0000387233237395473</v>
+        <v>0.0000354714422896823</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00456580257928379</v>
+        <v>0.00435047976478737</v>
       </c>
       <c r="I42" t="n">
-        <v>8.86057390480792</v>
+        <v>0.498109016935064</v>
       </c>
       <c r="J42" t="n">
         <v>1356</v>
@@ -3510,21 +3420,15 @@
       <c r="D43" t="s">
         <v>45</v>
       </c>
-      <c r="E43" t="n">
-        <v>0.000131599806306761</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.0101649976404406</v>
-      </c>
+      <c r="E43"/>
+      <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.0235760523769521</v>
+        <v>0.000131827964784891</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0477939251229977</v>
-      </c>
-      <c r="I43" t="n">
-        <v>99.4418072873158</v>
-      </c>
+        <v>0.0101806329983924</v>
+      </c>
+      <c r="I43"/>
       <c r="J43" t="n">
         <v>904</v>
       </c>
@@ -3542,21 +3446,15 @@
       <c r="D44" t="s">
         <v>48</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.000172634239481751</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.00737802669561499</v>
-      </c>
-      <c r="G44" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H44" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I44" t="e">
-        <v>#NUM!</v>
-      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44" t="n">
+        <v>0.000118803372758431</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.00954154013277616</v>
+      </c>
+      <c r="I44"/>
       <c r="J44" t="n">
         <v>904</v>
       </c>
@@ -3575,19 +3473,19 @@
         <v>46</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000141492473882068</v>
+        <v>0.000141502112838174</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0106222471145851</v>
+        <v>0.0106226318347252</v>
       </c>
       <c r="G45" t="n">
-        <v>14139917182090323968</v>
+        <v>0.000126356938748648</v>
       </c>
       <c r="H45" t="n">
-        <v>1449468707.07312</v>
+        <v>0.00989127942739404</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>-11.9860248590325</v>
       </c>
       <c r="J45" t="n">
         <v>904</v>
@@ -3607,19 +3505,19 @@
         <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000133533157198412</v>
+        <v>0.000133508605603922</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0102552792148694</v>
+        <v>0.0102553218812643</v>
       </c>
       <c r="G46" t="n">
-        <v>0.000130404667349873</v>
+        <v>0.000130276196310112</v>
       </c>
       <c r="H46" t="n">
-        <v>0.010110690636959</v>
+        <v>0.010102478483756</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.39906278825532</v>
+        <v>-2.48119716829631</v>
       </c>
       <c r="J46" t="n">
         <v>904</v>
@@ -3638,21 +3536,15 @@
       <c r="D47" t="s">
         <v>45</v>
       </c>
-      <c r="E47" t="n">
-        <v>0.000516898359983477</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.0164537007635467</v>
-      </c>
+      <c r="E47"/>
+      <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.00672227768036403</v>
+        <v>0.000516616822406843</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0569507738137068</v>
-      </c>
-      <c r="I47" t="n">
-        <v>92.3106663461203</v>
-      </c>
+        <v>0.0165168297565646</v>
+      </c>
+      <c r="I47"/>
       <c r="J47" t="n">
         <v>143</v>
       </c>
@@ -3671,19 +3563,19 @@
         <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000512805185536126</v>
+        <v>0.000512237657541394</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0165141031041208</v>
+        <v>0.0164991733133728</v>
       </c>
       <c r="G48" t="n">
-        <v>63.2334328341575</v>
+        <v>0.000517788662744236</v>
       </c>
       <c r="H48" t="n">
-        <v>4.48352617511119</v>
+        <v>0.0164971593411957</v>
       </c>
       <c r="I48" t="n">
-        <v>99.9991890283944</v>
+        <v>1.07206001255832</v>
       </c>
       <c r="J48" t="n">
         <v>143</v>
@@ -3703,19 +3595,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000514414720028956</v>
+        <v>0.000514503411521935</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0164082834804659</v>
+        <v>0.016415180534575</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000567633847934421</v>
+        <v>0.000513591561800653</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0170010781805506</v>
+        <v>0.0164713489784217</v>
       </c>
       <c r="I49" t="n">
-        <v>9.37560860740169</v>
+        <v>-0.17754375054089</v>
       </c>
       <c r="J49" t="n">
         <v>143</v>
@@ -3734,21 +3626,15 @@
       <c r="D50" t="s">
         <v>45</v>
       </c>
-      <c r="E50" t="n">
-        <v>0.000259090603437036</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.0121132767157572</v>
-      </c>
+      <c r="E50"/>
+      <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.0227135457480371</v>
+        <v>0.00025887137451676</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0641698362868067</v>
-      </c>
-      <c r="I50" t="n">
-        <v>98.8593123842876</v>
-      </c>
+        <v>0.0121919229021894</v>
+      </c>
+      <c r="I50"/>
       <c r="J50" t="n">
         <v>59</v>
       </c>
@@ -3767,19 +3653,19 @@
         <v>46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000256275590331901</v>
+        <v>0.000256250073183886</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0120349024924798</v>
+        <v>0.0120320930555684</v>
       </c>
       <c r="G51" t="n">
-        <v>0.324125248755212</v>
+        <v>0.00025262803724549</v>
       </c>
       <c r="H51" t="n">
-        <v>0.271176176385608</v>
+        <v>0.0119162024329556</v>
       </c>
       <c r="I51" t="n">
-        <v>99.9209331604631</v>
+        <v>-1.43374265892586</v>
       </c>
       <c r="J51" t="n">
         <v>59</v>
@@ -3799,19 +3685,19 @@
         <v>47</v>
       </c>
       <c r="E52" t="n">
-        <v>0.000258608791905769</v>
+        <v>0.000258896743109604</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0120775213251645</v>
+        <v>0.0120753234149388</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00025833072598055</v>
+        <v>0.000259288302320898</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0120370570207408</v>
+        <v>0.0120670563421511</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.107639509068291</v>
+        <v>0.151013064526809</v>
       </c>
       <c r="J52" t="n">
         <v>59</v>
@@ -3830,21 +3716,15 @@
       <c r="D53" t="s">
         <v>45</v>
       </c>
-      <c r="E53" t="n">
-        <v>0.000161996719777218</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.00770662990197058</v>
-      </c>
+      <c r="E53"/>
+      <c r="F53"/>
       <c r="G53" t="n">
-        <v>28.4592466355662</v>
+        <v>0.000162906224822172</v>
       </c>
       <c r="H53" t="n">
-        <v>0.918873498432765</v>
-      </c>
-      <c r="I53" t="n">
-        <v>99.9994307765</v>
-      </c>
+        <v>0.0077507945516883</v>
+      </c>
+      <c r="I53"/>
       <c r="J53" t="n">
         <v>1356</v>
       </c>
@@ -3863,19 +3743,19 @@
         <v>46</v>
       </c>
       <c r="E54" t="n">
-        <v>0.000162936394336284</v>
+        <v>0.00016337415444829</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00777321122475771</v>
+        <v>0.00777268899685002</v>
       </c>
       <c r="G54" t="n">
-        <v>64872258042531621180042628</v>
+        <v>0.000162666790246751</v>
       </c>
       <c r="H54" t="n">
-        <v>1265125020188.92</v>
+        <v>0.00775820310463819</v>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>-0.43485471156455</v>
       </c>
       <c r="J54" t="n">
         <v>1356</v>
@@ -3895,19 +3775,19 @@
         <v>47</v>
       </c>
       <c r="E55" t="n">
-        <v>0.000162457369401621</v>
+        <v>0.000161871965830635</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00771760981263804</v>
+        <v>0.00770386615219731</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000208242918747596</v>
+        <v>0.00016255809225367</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0091429860135175</v>
+        <v>0.00773755598539883</v>
       </c>
       <c r="I55" t="n">
-        <v>21.9866056533095</v>
+        <v>0.4220807549618</v>
       </c>
       <c r="J55" t="n">
         <v>1356</v>
@@ -3926,21 +3806,15 @@
       <c r="D56" t="s">
         <v>45</v>
       </c>
-      <c r="E56" t="n">
-        <v>0.000282162393030149</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.00786710338272792</v>
-      </c>
+      <c r="E56"/>
+      <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.499471513491229</v>
+        <v>0.000283212431303479</v>
       </c>
       <c r="H56" t="n">
-        <v>0.225271659119233</v>
-      </c>
-      <c r="I56" t="n">
-        <v>99.9435078106741</v>
-      </c>
+        <v>0.00787760802375231</v>
+      </c>
+      <c r="I56"/>
       <c r="J56" t="n">
         <v>1356</v>
       </c>
@@ -3959,19 +3833,19 @@
         <v>46</v>
       </c>
       <c r="E57" t="n">
-        <v>0.000282691544712139</v>
+        <v>0.000283340925311542</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0079187349956235</v>
+        <v>0.00791906766263462</v>
       </c>
       <c r="G57" t="n">
-        <v>54521462547176333712068624646</v>
+        <v>0.000282196361704233</v>
       </c>
       <c r="H57" t="n">
-        <v>34148062945790.2</v>
+        <v>0.00791488543901683</v>
       </c>
       <c r="I57" t="n">
-        <v>100</v>
+        <v>-0.405591199119753</v>
       </c>
       <c r="J57" t="n">
         <v>1356</v>
@@ -3991,19 +3865,19 @@
         <v>47</v>
       </c>
       <c r="E58" t="n">
-        <v>0.000281883867607197</v>
+        <v>0.000281290039124655</v>
       </c>
       <c r="F58" t="n">
-        <v>0.00785294302036169</v>
+        <v>0.00785205113299153</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000338926210911476</v>
+        <v>0.000283006146848539</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00902298689417835</v>
+        <v>0.00789952222352718</v>
       </c>
       <c r="I58" t="n">
-        <v>16.8303133448649</v>
+        <v>0.606385318126041</v>
       </c>
       <c r="J58" t="n">
         <v>1356</v>
@@ -4022,21 +3896,15 @@
       <c r="D59" t="s">
         <v>45</v>
       </c>
-      <c r="E59" t="n">
-        <v>0.0000934678826093097</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.00747749308205695</v>
-      </c>
+      <c r="E59"/>
+      <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.430717169883635</v>
+        <v>0.0000940229083161743</v>
       </c>
       <c r="H59" t="n">
-        <v>0.258443396499492</v>
-      </c>
-      <c r="I59" t="n">
-        <v>99.9782994760495</v>
-      </c>
+        <v>0.00752134277093106</v>
+      </c>
+      <c r="I59"/>
       <c r="J59" t="n">
         <v>1356</v>
       </c>
@@ -4055,19 +3923,19 @@
         <v>46</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000941021049618432</v>
+        <v>0.0000941208636101574</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00755398213416622</v>
+        <v>0.00755422214047339</v>
       </c>
       <c r="G60" t="n">
-        <v>25993300365478964622462262</v>
+        <v>0.0000934753542243088</v>
       </c>
       <c r="H60" t="n">
-        <v>798646102857.306</v>
+        <v>0.00750695747425842</v>
       </c>
       <c r="I60" t="n">
-        <v>100</v>
+        <v>-0.690566397105697</v>
       </c>
       <c r="J60" t="n">
         <v>1356</v>
@@ -4087,19 +3955,19 @@
         <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0000935576641844215</v>
+        <v>0.0000936888679510478</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0074931473835255</v>
+        <v>0.00749167019092085</v>
       </c>
       <c r="G61" t="n">
-        <v>0.000184210207525231</v>
+        <v>0.0000942811552980978</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00901052929801279</v>
+        <v>0.00753898218570277</v>
       </c>
       <c r="I61" t="n">
-        <v>49.2114658349717</v>
+        <v>0.628213925866043</v>
       </c>
       <c r="J61" t="n">
         <v>1356</v>
@@ -4118,21 +3986,15 @@
       <c r="D62" t="s">
         <v>45</v>
       </c>
-      <c r="E62" t="n">
-        <v>0.0000936084344559735</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.00748578956440812</v>
-      </c>
+      <c r="E62"/>
+      <c r="F62"/>
       <c r="G62" t="n">
-        <v>1373.83754924098</v>
+        <v>0.0000947962811010623</v>
       </c>
       <c r="H62" t="n">
-        <v>3.38104440980681</v>
-      </c>
-      <c r="I62" t="n">
-        <v>99.9999931863535</v>
-      </c>
+        <v>0.00755875345228711</v>
+      </c>
+      <c r="I62"/>
       <c r="J62" t="n">
         <v>1356</v>
       </c>
@@ -4151,19 +4013,19 @@
         <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0.000094213837536071</v>
+        <v>0.000094222014330965</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00755827763414994</v>
+        <v>0.00755759678244724</v>
       </c>
       <c r="G63" t="n">
-        <v>1022690007578979313122068</v>
+        <v>0.0000938142965855758</v>
       </c>
       <c r="H63" t="n">
-        <v>222989842506.015</v>
+        <v>0.0075175861579488</v>
       </c>
       <c r="I63" t="n">
-        <v>100</v>
+        <v>-0.43460086599625</v>
       </c>
       <c r="J63" t="n">
         <v>1356</v>
@@ -4183,19 +4045,19 @@
         <v>47</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0000938023185618277</v>
+        <v>0.0000937305224087627</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00750019406804445</v>
+        <v>0.00750008127891087</v>
       </c>
       <c r="G64" t="n">
-        <v>0.000121987180398559</v>
+        <v>0.0000942778270800512</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00836182890784391</v>
+        <v>0.0075251859606301</v>
       </c>
       <c r="I64" t="n">
-        <v>23.104773587393</v>
+        <v>0.580523213399648</v>
       </c>
       <c r="J64" t="n">
         <v>1356</v>
@@ -4214,21 +4076,15 @@
       <c r="D65" t="s">
         <v>45</v>
       </c>
-      <c r="E65" t="n">
-        <v>0.000210771324927241</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.0120815506917163</v>
-      </c>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.0154317419068159</v>
+        <v>0.000217078768001028</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0693317777618018</v>
-      </c>
-      <c r="I65" t="n">
-        <v>98.6341702304252</v>
-      </c>
+        <v>0.0123170236265169</v>
+      </c>
+      <c r="I65"/>
       <c r="J65" t="n">
         <v>904</v>
       </c>
@@ -4247,19 +4103,19 @@
         <v>46</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000226750590680147</v>
+        <v>0.000226689707408496</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0126574308833276</v>
+        <v>0.0126554229379965</v>
       </c>
       <c r="G66" t="n">
-        <v>25401963998635433656020</v>
+        <v>0.000215394276598182</v>
       </c>
       <c r="H66" t="n">
-        <v>21633075516.239</v>
+        <v>0.0122400174835535</v>
       </c>
       <c r="I66" t="n">
-        <v>100</v>
+        <v>-5.24407193575782</v>
       </c>
       <c r="J66" t="n">
         <v>904</v>
@@ -4279,19 +4135,19 @@
         <v>47</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000210525717982336</v>
+        <v>0.000210506370743563</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0120606430542286</v>
+        <v>0.0120614823691069</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000840917160048174</v>
+        <v>0.000218369603078567</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0169269028980926</v>
+        <v>0.0123428273035239</v>
       </c>
       <c r="I67" t="n">
-        <v>74.9647494444904</v>
+        <v>3.60088227672188</v>
       </c>
       <c r="J67" t="n">
         <v>904</v>
@@ -4310,21 +4166,15 @@
       <c r="D68" t="s">
         <v>45</v>
       </c>
-      <c r="E68" t="n">
-        <v>0.00358387157044838</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.0493364444901825</v>
-      </c>
+      <c r="E68"/>
+      <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.608779530630297</v>
+        <v>0.00356738074628703</v>
       </c>
       <c r="H68" t="n">
-        <v>0.362590527319204</v>
-      </c>
-      <c r="I68" t="n">
-        <v>99.4113022218835</v>
-      </c>
+        <v>0.0491665162131087</v>
+      </c>
+      <c r="I68"/>
       <c r="J68" t="n">
         <v>143</v>
       </c>
@@ -4343,19 +4193,19 @@
         <v>46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00359502479333836</v>
+        <v>0.00359274668000417</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0493763369337629</v>
+        <v>0.0493797517999935</v>
       </c>
       <c r="G69" t="n">
-        <v>7047.3211462347</v>
+        <v>0.00356547121089913</v>
       </c>
       <c r="H69" t="n">
-        <v>28.8493215133236</v>
+        <v>0.0493410102398191</v>
       </c>
       <c r="I69" t="n">
-        <v>99.9999489873568</v>
+        <v>-0.764989183523831</v>
       </c>
       <c r="J69" t="n">
         <v>143</v>
@@ -4375,19 +4225,19 @@
         <v>47</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00357679062606319</v>
+        <v>0.00357751466931278</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0492817116517857</v>
+        <v>0.0492565648253414</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00358441266364974</v>
+        <v>0.00358463161868233</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0494023386746975</v>
+        <v>0.049377752825185</v>
       </c>
       <c r="I70" t="n">
-        <v>0.212643975506576</v>
+        <v>0.198540606863619</v>
       </c>
       <c r="J70" t="n">
         <v>143</v>
@@ -4406,21 +4256,15 @@
       <c r="D71" t="s">
         <v>45</v>
       </c>
-      <c r="E71" t="n">
-        <v>0.00345810733818811</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.0454179258879109</v>
-      </c>
+      <c r="E71"/>
+      <c r="F71"/>
       <c r="G71" t="n">
-        <v>0.617585087312466</v>
+        <v>0.00341654496767278</v>
       </c>
       <c r="H71" t="n">
-        <v>0.291337231983611</v>
-      </c>
-      <c r="I71" t="n">
-        <v>99.4400597732635</v>
-      </c>
+        <v>0.0450729748215993</v>
+      </c>
+      <c r="I71"/>
       <c r="J71" t="n">
         <v>59</v>
       </c>
@@ -4438,21 +4282,15 @@
       <c r="D72" t="s">
         <v>48</v>
       </c>
-      <c r="E72" t="n">
-        <v>11617076644.9822</v>
-      </c>
-      <c r="F72" t="n">
-        <v>14091.0570142307</v>
-      </c>
+      <c r="E72"/>
+      <c r="F72"/>
       <c r="G72" t="n">
-        <v>98686184067844248880206820246448844202864282224060202022424</v>
+        <v>3.63887703743687</v>
       </c>
       <c r="H72" t="n">
-        <v>40964071373466186350464620806</v>
-      </c>
-      <c r="I72" t="n">
-        <v>100</v>
-      </c>
+        <v>1.90392326750234</v>
+      </c>
+      <c r="I72"/>
       <c r="J72" t="n">
         <v>59</v>
       </c>
@@ -4471,19 +4309,19 @@
         <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00346479565387934</v>
+        <v>0.00347387441468728</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0454561980324347</v>
+        <v>0.0455389314011757</v>
       </c>
       <c r="G73" t="n">
-        <v>27.446773701895</v>
+        <v>0.00348489813973122</v>
       </c>
       <c r="H73" t="n">
-        <v>2.24203355433515</v>
+        <v>0.0458027226678801</v>
       </c>
       <c r="I73" t="n">
-        <v>99.9873763099025</v>
+        <v>0.316328472223076</v>
       </c>
       <c r="J73" t="n">
         <v>59</v>
@@ -4503,19 +4341,19 @@
         <v>47</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00347482056360249</v>
+        <v>0.00347290358277441</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0456364005307156</v>
+        <v>0.0455568013520611</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00345898815143245</v>
+        <v>0.00346848935051976</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0454178943324778</v>
+        <v>0.0455099318904424</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.457718022638554</v>
+        <v>-0.127266709179406</v>
       </c>
       <c r="J74" t="n">
         <v>59</v>
@@ -4534,21 +4372,15 @@
       <c r="D75" t="s">
         <v>45</v>
       </c>
-      <c r="E75" t="n">
-        <v>0.00126743755408719</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.0252893636753448</v>
-      </c>
+      <c r="E75"/>
+      <c r="F75"/>
       <c r="G75" t="n">
-        <v>4.19711424570925</v>
+        <v>0.00127102451828977</v>
       </c>
       <c r="H75" t="n">
-        <v>0.39326635483392</v>
-      </c>
-      <c r="I75" t="n">
-        <v>99.9698021669202</v>
-      </c>
+        <v>0.0254054156272021</v>
+      </c>
+      <c r="I75"/>
       <c r="J75" t="n">
         <v>1356</v>
       </c>
@@ -4566,21 +4398,15 @@
       <c r="D76" t="s">
         <v>48</v>
       </c>
-      <c r="E76" t="n">
-        <v>0.00126981598313535</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.0253205493057644</v>
-      </c>
+      <c r="E76"/>
+      <c r="F76"/>
       <c r="G76" t="n">
-        <v>3891958770768186368</v>
+        <v>0.00132600454120009</v>
       </c>
       <c r="H76" t="n">
-        <v>157366716.694124</v>
-      </c>
-      <c r="I76" t="n">
-        <v>100</v>
-      </c>
+        <v>0.0261248962873394</v>
+      </c>
+      <c r="I76"/>
       <c r="J76" t="n">
         <v>1356</v>
       </c>
@@ -4599,19 +4425,19 @@
         <v>46</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00126818006312231</v>
+        <v>0.0012685726404705</v>
       </c>
       <c r="F77" t="n">
-        <v>0.025265116575941</v>
+        <v>0.0252666077553319</v>
       </c>
       <c r="G77" t="n">
-        <v>163941934067150003146866682</v>
+        <v>0.00128777797228235</v>
       </c>
       <c r="H77" t="n">
-        <v>2105266773348.41</v>
+        <v>0.025607806161668</v>
       </c>
       <c r="I77" t="n">
-        <v>100</v>
+        <v>1.49135427264764</v>
       </c>
       <c r="J77" t="n">
         <v>1356</v>
@@ -4631,19 +4457,19 @@
         <v>47</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00126692827297682</v>
+        <v>0.00126991325453974</v>
       </c>
       <c r="F78" t="n">
-        <v>0.025340129088533</v>
+        <v>0.0253662681892662</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00127249900827644</v>
+        <v>0.0012737914897854</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0253673150301437</v>
+        <v>0.0253774323395449</v>
       </c>
       <c r="I78" t="n">
-        <v>0.437779146654712</v>
+        <v>0.304463899841954</v>
       </c>
       <c r="J78" t="n">
         <v>1356</v>
@@ -4662,21 +4488,15 @@
       <c r="D79" t="s">
         <v>45</v>
       </c>
-      <c r="E79" t="n">
-        <v>0.00139584231057744</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.0254340673315814</v>
-      </c>
+      <c r="E79"/>
+      <c r="F79"/>
       <c r="G79" t="n">
-        <v>43.5087833764608</v>
+        <v>0.00139537058258905</v>
       </c>
       <c r="H79" t="n">
-        <v>0.733447488666945</v>
-      </c>
-      <c r="I79" t="n">
-        <v>99.9967918148883</v>
-      </c>
+        <v>0.0255640283794976</v>
+      </c>
+      <c r="I79"/>
       <c r="J79" t="n">
         <v>1356</v>
       </c>
@@ -4694,21 +4514,15 @@
       <c r="D80" t="s">
         <v>48</v>
       </c>
-      <c r="E80" t="n">
-        <v>0.00139629764952591</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.0254750017706653</v>
-      </c>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="G80" t="n">
-        <v>15367693778721796096</v>
+        <v>0.00145079580549807</v>
       </c>
       <c r="H80" t="n">
-        <v>204263259.645897</v>
-      </c>
-      <c r="I80" t="n">
-        <v>100</v>
-      </c>
+        <v>0.0261332599473246</v>
+      </c>
+      <c r="I80"/>
       <c r="J80" t="n">
         <v>1356</v>
       </c>
@@ -4727,19 +4541,19 @@
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00139816382524416</v>
+        <v>0.00139839621798504</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0254110492089136</v>
+        <v>0.0254118907800693</v>
       </c>
       <c r="G81" t="n">
-        <v>1747664775381163614180604</v>
+        <v>0.00142062886297171</v>
       </c>
       <c r="H81" t="n">
-        <v>190017383380.999</v>
+        <v>0.0258848789138574</v>
       </c>
       <c r="I81" t="n">
-        <v>100</v>
+        <v>1.56498615269326</v>
       </c>
       <c r="J81" t="n">
         <v>1356</v>
@@ -4759,19 +4573,19 @@
         <v>47</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00139826064262992</v>
+        <v>0.00139878135600393</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0255219684056149</v>
+        <v>0.0255142556648408</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00139983957158799</v>
+        <v>0.0014026983407856</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0254880646205058</v>
+        <v>0.0255688810284551</v>
       </c>
       <c r="I82" t="n">
-        <v>0.112793565071455</v>
+        <v>0.279246411561525</v>
       </c>
       <c r="J82" t="n">
         <v>1356</v>
@@ -4790,21 +4604,15 @@
       <c r="D83" t="s">
         <v>45</v>
       </c>
-      <c r="E83" t="n">
-        <v>0.00118784056233316</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.0251172118020489</v>
-      </c>
+      <c r="E83"/>
+      <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.215834450403935</v>
+        <v>0.00118969188335669</v>
       </c>
       <c r="H83" t="n">
-        <v>0.172602637261507</v>
-      </c>
-      <c r="I83" t="n">
-        <v>99.4496520086992</v>
-      </c>
+        <v>0.0251362024641074</v>
+      </c>
+      <c r="I83"/>
       <c r="J83" t="n">
         <v>1356</v>
       </c>
@@ -4822,21 +4630,15 @@
       <c r="D84" t="s">
         <v>48</v>
       </c>
-      <c r="E84" t="n">
-        <v>0.00118824749843996</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.0251239628336549</v>
-      </c>
+      <c r="E84"/>
+      <c r="F84"/>
       <c r="G84" t="n">
-        <v>14935385816631754752</v>
+        <v>0.00122942243707141</v>
       </c>
       <c r="H84" t="n">
-        <v>281259385.993308</v>
-      </c>
-      <c r="I84" t="n">
-        <v>100</v>
-      </c>
+        <v>0.0258462960203753</v>
+      </c>
+      <c r="I84"/>
       <c r="J84" t="n">
         <v>1356</v>
       </c>
@@ -4855,19 +4657,19 @@
         <v>46</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00118755373237</v>
+        <v>0.00118764030089331</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0250713846383668</v>
+        <v>0.0250740024016863</v>
       </c>
       <c r="G85" t="n">
-        <v>2245437036143935222626242060</v>
+        <v>0.00121013119315511</v>
       </c>
       <c r="H85" t="n">
-        <v>9835319440850.51</v>
+        <v>0.0253788415332881</v>
       </c>
       <c r="I85" t="n">
-        <v>100</v>
+        <v>1.85854991500286</v>
       </c>
       <c r="J85" t="n">
         <v>1356</v>
@@ -4887,19 +4689,19 @@
         <v>47</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00118879690315476</v>
+        <v>0.00118941767173867</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0251780189016543</v>
+        <v>0.0251840053554258</v>
       </c>
       <c r="G86" t="n">
-        <v>0.00118737299691941</v>
+        <v>0.00118445226493201</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0251874396451509</v>
+        <v>0.0250926907302168</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.119920719019478</v>
+        <v>-0.41921544275538</v>
       </c>
       <c r="J86" t="n">
         <v>1356</v>
@@ -4918,21 +4720,15 @@
       <c r="D87" t="s">
         <v>45</v>
       </c>
-      <c r="E87" t="n">
-        <v>0.001194311139798</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.025171618477303</v>
-      </c>
+      <c r="E87"/>
+      <c r="F87"/>
       <c r="G87" t="n">
-        <v>1.89985023546212</v>
+        <v>0.00119494092599386</v>
       </c>
       <c r="H87" t="n">
-        <v>0.313956727764779</v>
-      </c>
-      <c r="I87" t="n">
-        <v>99.9371365638457</v>
-      </c>
+        <v>0.0252271464217868</v>
+      </c>
+      <c r="I87"/>
       <c r="J87" t="n">
         <v>1356</v>
       </c>
@@ -4950,21 +4746,15 @@
       <c r="D88" t="s">
         <v>48</v>
       </c>
-      <c r="E88" t="n">
-        <v>0.00119220020257798</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.0251745889953397</v>
-      </c>
+      <c r="E88"/>
+      <c r="F88"/>
       <c r="G88" t="n">
-        <v>753935276335988352</v>
+        <v>0.0012256506558025</v>
       </c>
       <c r="H88" t="n">
-        <v>122574432.731125</v>
-      </c>
-      <c r="I88" t="n">
-        <v>100</v>
-      </c>
+        <v>0.0257399812323785</v>
+      </c>
+      <c r="I88"/>
       <c r="J88" t="n">
         <v>1356</v>
       </c>
@@ -4983,19 +4773,19 @@
         <v>46</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0011929133347853</v>
+        <v>0.00119286529559714</v>
       </c>
       <c r="F89" t="n">
-        <v>0.025100252089435</v>
+        <v>0.0250992365475009</v>
       </c>
       <c r="G89" t="n">
-        <v>1181770801180423225364</v>
+        <v>0.00121106520071367</v>
       </c>
       <c r="H89" t="n">
-        <v>7707532718.59548</v>
+        <v>0.0255288068710381</v>
       </c>
       <c r="I89" t="n">
-        <v>100</v>
+        <v>1.50280142686067</v>
       </c>
       <c r="J89" t="n">
         <v>1356</v>
@@ -5015,19 +4805,19 @@
         <v>47</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0011945894740644</v>
+        <v>0.00119563051313478</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0251893094399388</v>
+        <v>0.0252055096901397</v>
       </c>
       <c r="G90" t="n">
-        <v>0.00119440288996759</v>
+        <v>0.00119230807525417</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0252272375706826</v>
+        <v>0.0251552896825112</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0156215376213368</v>
+        <v>-0.278655990809954</v>
       </c>
       <c r="J90" t="n">
         <v>1356</v>
@@ -5046,21 +4836,15 @@
       <c r="D91" t="s">
         <v>45</v>
       </c>
-      <c r="E91" t="n">
-        <v>0.00106136464210109</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.0227805046191611</v>
-      </c>
+      <c r="E91"/>
+      <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.0219191310133396</v>
+        <v>0.00106852558466791</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0711435611164174</v>
-      </c>
-      <c r="I91" t="n">
-        <v>95.1578160582408</v>
-      </c>
+        <v>0.0228609518991435</v>
+      </c>
+      <c r="I91"/>
       <c r="J91" t="n">
         <v>904</v>
       </c>
@@ -5079,19 +4863,19 @@
         <v>46</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00107584442195268</v>
+        <v>0.00107572076843033</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0230224870686247</v>
+        <v>0.0230190060949334</v>
       </c>
       <c r="G92" t="n">
-        <v>8782021827161026560</v>
+        <v>0.00104957668514342</v>
       </c>
       <c r="H92" t="n">
-        <v>840052933.540231</v>
+        <v>0.0225658851696662</v>
       </c>
       <c r="I92" t="n">
-        <v>100</v>
+        <v>-2.49091692460143</v>
       </c>
       <c r="J92" t="n">
         <v>904</v>
@@ -5111,19 +4895,19 @@
         <v>47</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00105021424522362</v>
+        <v>0.00105065903943165</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0226325756452959</v>
+        <v>0.0226298271251115</v>
       </c>
       <c r="G93" t="n">
-        <v>0.00105850473551286</v>
+        <v>0.00105699438578322</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0227036680124137</v>
+        <v>0.0227550707412635</v>
       </c>
       <c r="I93" t="n">
-        <v>0.783226565842317</v>
+        <v>0.599373699310908</v>
       </c>
       <c r="J93" t="n">
         <v>904</v>
@@ -5142,21 +4926,15 @@
       <c r="D94" t="s">
         <v>45</v>
       </c>
-      <c r="E94" t="n">
-        <v>0.00166512757914714</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.0306882526854809</v>
-      </c>
+      <c r="E94"/>
+      <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00416719347214774</v>
+        <v>0.00166294658379733</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0440942068988975</v>
-      </c>
-      <c r="I94" t="n">
-        <v>60.0419901241364</v>
-      </c>
+        <v>0.0306831618126738</v>
+      </c>
+      <c r="I94"/>
       <c r="J94" t="n">
         <v>143</v>
       </c>
@@ -5175,19 +4953,19 @@
         <v>46</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0016753717741794</v>
+        <v>0.00167446382351746</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0308159057963404</v>
+        <v>0.0308049751926427</v>
       </c>
       <c r="G95" t="n">
-        <v>142818.101065015</v>
+        <v>0.00164681638293988</v>
       </c>
       <c r="H95" t="n">
-        <v>103.562636192182</v>
+        <v>0.0304164639683291</v>
       </c>
       <c r="I95" t="n">
-        <v>99.9999988269192</v>
+        <v>-1.67884172540377</v>
       </c>
       <c r="J95" t="n">
         <v>143</v>
@@ -5207,19 +4985,19 @@
         <v>47</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00166125789021181</v>
+        <v>0.00166132647085231</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0306471250386961</v>
+        <v>0.030641199663604</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00166065028382963</v>
+        <v>0.00165957255752495</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0306414946632502</v>
+        <v>0.0306197495789312</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0365884610441871</v>
+        <v>-0.105684642674863</v>
       </c>
       <c r="J96" t="n">
         <v>143</v>
@@ -5238,21 +5016,15 @@
       <c r="D97" t="s">
         <v>45</v>
       </c>
-      <c r="E97" t="n">
-        <v>0.00221806825391299</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.0351430376719977</v>
-      </c>
+      <c r="E97"/>
+      <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00629598210125899</v>
+        <v>0.00222281213201907</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0512743682975707</v>
-      </c>
-      <c r="I97" t="n">
-        <v>64.7700991165549</v>
-      </c>
+        <v>0.0352792720029899</v>
+      </c>
+      <c r="I97"/>
       <c r="J97" t="n">
         <v>59</v>
       </c>
@@ -5271,19 +5043,19 @@
         <v>46</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00221604586015262</v>
+        <v>0.00221565566311845</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0350654343235738</v>
+        <v>0.0350498531847752</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0780871810213552</v>
+        <v>0.00223131327357378</v>
       </c>
       <c r="H98" t="n">
-        <v>0.181176702115937</v>
+        <v>0.0352585466745019</v>
       </c>
       <c r="I98" t="n">
-        <v>97.1620875140229</v>
+        <v>0.701721745698603</v>
       </c>
       <c r="J98" t="n">
         <v>59</v>
@@ -5303,19 +5075,19 @@
         <v>47</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00221506669068248</v>
+        <v>0.00221888341250844</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0350179282760485</v>
+        <v>0.0350940188888403</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0022195351198017</v>
+        <v>0.00221480348429939</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0351445245920978</v>
+        <v>0.0350805688266636</v>
       </c>
       <c r="I99" t="n">
-        <v>0.201322749045753</v>
+        <v>-0.184211747812876</v>
       </c>
       <c r="J99" t="n">
         <v>59</v>
@@ -5334,21 +5106,15 @@
       <c r="D100" t="s">
         <v>45</v>
       </c>
-      <c r="E100" t="n">
-        <v>0.000439196071214006</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.0138146220512591</v>
-      </c>
+      <c r="E100"/>
+      <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.0990906561079029</v>
+        <v>0.000440816615549588</v>
       </c>
       <c r="H100" t="n">
-        <v>0.121393231996092</v>
-      </c>
-      <c r="I100" t="n">
-        <v>99.5567734754569</v>
-      </c>
+        <v>0.0138554439799647</v>
+      </c>
+      <c r="I100"/>
       <c r="J100" t="n">
         <v>1356</v>
       </c>
@@ -5367,19 +5133,19 @@
         <v>46</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000439981119663258</v>
+        <v>0.000439811947125764</v>
       </c>
       <c r="F101" t="n">
-        <v>0.013812874190963</v>
+        <v>0.0138123973908828</v>
       </c>
       <c r="G101" t="n">
-        <v>10848664601456551846408080</v>
+        <v>0.000442099720461892</v>
       </c>
       <c r="H101" t="n">
-        <v>846133160396.443</v>
+        <v>0.0138716932381819</v>
       </c>
       <c r="I101" t="n">
-        <v>100</v>
+        <v>0.517479027975316</v>
       </c>
       <c r="J101" t="n">
         <v>1356</v>
@@ -5399,19 +5165,19 @@
         <v>47</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000438981599825951</v>
+        <v>0.000440183333130427</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0138334368122082</v>
+        <v>0.013831044624356</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000439292226322175</v>
+        <v>0.000440023353518348</v>
       </c>
       <c r="H102" t="n">
-        <v>0.013824060792627</v>
+        <v>0.0138360979448112</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0707106744921736</v>
+        <v>-0.0363570730506746</v>
       </c>
       <c r="J102" t="n">
         <v>1356</v>
@@ -5430,21 +5196,15 @@
       <c r="D103" t="s">
         <v>45</v>
       </c>
-      <c r="E103" t="n">
-        <v>0.000558798164577488</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.0139743854695192</v>
-      </c>
+      <c r="E103"/>
+      <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.108249795012728</v>
+        <v>0.000558386378084396</v>
       </c>
       <c r="H103" t="n">
-        <v>0.113327011910173</v>
-      </c>
-      <c r="I103" t="n">
-        <v>99.483788246886</v>
-      </c>
+        <v>0.0139815578548364</v>
+      </c>
+      <c r="I103"/>
       <c r="J103" t="n">
         <v>1356</v>
       </c>
@@ -5463,19 +5223,19 @@
         <v>46</v>
       </c>
       <c r="E104" t="n">
-        <v>0.00055818095311996</v>
+        <v>0.000558979085836902</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0139589845681622</v>
+        <v>0.0139601052284728</v>
       </c>
       <c r="G104" t="n">
-        <v>36902820963009901616042682220602</v>
+        <v>0.000558569581741242</v>
       </c>
       <c r="H104" t="n">
-        <v>800733440939525</v>
+        <v>0.0139778666264226</v>
       </c>
       <c r="I104" t="n">
-        <v>100</v>
+        <v>-0.073312996096805</v>
       </c>
       <c r="J104" t="n">
         <v>1356</v>
@@ -5495,19 +5255,19 @@
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000559873314724679</v>
+        <v>0.000558466510946914</v>
       </c>
       <c r="F105" t="n">
-        <v>0.013989174368609</v>
+        <v>0.0139864001010135</v>
       </c>
       <c r="G105" t="n">
-        <v>0.000557660362669065</v>
+        <v>0.000558833170249471</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0139754776541956</v>
+        <v>0.0139790008758806</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.396827926772795</v>
+        <v>0.0656115853670566</v>
       </c>
       <c r="J105" t="n">
         <v>1356</v>
@@ -5526,21 +5286,15 @@
       <c r="D106" t="s">
         <v>45</v>
       </c>
-      <c r="E106" t="n">
-        <v>0.000372037724034667</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.0135968400352563</v>
-      </c>
+      <c r="E106"/>
+      <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.116525122599012</v>
+        <v>0.00037316380381637</v>
       </c>
       <c r="H106" t="n">
-        <v>0.102525765975784</v>
-      </c>
-      <c r="I106" t="n">
-        <v>99.6807231644673</v>
-      </c>
+        <v>0.0136484122306544</v>
+      </c>
+      <c r="I106"/>
       <c r="J106" t="n">
         <v>1356</v>
       </c>
@@ -5559,19 +5313,19 @@
         <v>46</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000372174611960337</v>
+        <v>0.000372206914217439</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0135926151975848</v>
+        <v>0.0135939271506507</v>
       </c>
       <c r="G107" t="n">
-        <v>19406642626673284940226008666</v>
+        <v>0.000374414058928831</v>
       </c>
       <c r="H107" t="n">
-        <v>26418811675231.6</v>
+        <v>0.013657688429811</v>
       </c>
       <c r="I107" t="n">
-        <v>100</v>
+        <v>0.589493011482079</v>
       </c>
       <c r="J107" t="n">
         <v>1356</v>
@@ -5591,19 +5345,19 @@
         <v>47</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000372722713321479</v>
+        <v>0.000372237890948912</v>
       </c>
       <c r="F108" t="n">
-        <v>0.013626199446616</v>
+        <v>0.0136186378610793</v>
       </c>
       <c r="G108" t="n">
-        <v>0.000372616176314987</v>
+        <v>0.000371891536971461</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136245443942668</v>
+        <v>0.0136016194153773</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0285916214228612</v>
+        <v>-0.0931330624707773</v>
       </c>
       <c r="J108" t="n">
         <v>1356</v>
@@ -5622,21 +5376,15 @@
       <c r="D109" t="s">
         <v>45</v>
       </c>
-      <c r="E109" t="n">
-        <v>0.00037258813190111</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.0136141959046559</v>
-      </c>
+      <c r="E109"/>
+      <c r="F109"/>
       <c r="G109" t="n">
-        <v>2.3411406348586</v>
+        <v>0.000372422171837427</v>
       </c>
       <c r="H109" t="n">
-        <v>0.327002529302158</v>
-      </c>
-      <c r="I109" t="n">
-        <v>99.9840851879484</v>
-      </c>
+        <v>0.0136168888651752</v>
+      </c>
+      <c r="I109"/>
       <c r="J109" t="n">
         <v>1356</v>
       </c>
@@ -5655,19 +5403,19 @@
         <v>46</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000372134981902324</v>
+        <v>0.000372200920185321</v>
       </c>
       <c r="F110" t="n">
-        <v>0.0135933121017579</v>
+        <v>0.0135945199865031</v>
       </c>
       <c r="G110" t="n">
-        <v>14999272694359400687462440848648</v>
+        <v>0.00037445918734155</v>
       </c>
       <c r="H110" t="n">
-        <v>317768517041104</v>
+        <v>0.0136374452795782</v>
       </c>
       <c r="I110" t="n">
-        <v>100</v>
+        <v>0.60307430891484</v>
       </c>
       <c r="J110" t="n">
         <v>1356</v>
@@ -5687,19 +5435,19 @@
         <v>47</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000372394122503187</v>
+        <v>0.000372786459680253</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0136220571093058</v>
+        <v>0.0136151076530698</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000373348612259274</v>
+        <v>0.000371884090415194</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0136305973758667</v>
+        <v>0.0136046291930872</v>
       </c>
       <c r="I111" t="n">
-        <v>0.255656436034763</v>
+        <v>-0.242647988530901</v>
       </c>
       <c r="J111" t="n">
         <v>1356</v>
@@ -5718,21 +5466,15 @@
       <c r="D112" t="s">
         <v>45</v>
       </c>
-      <c r="E112" t="n">
-        <v>0.00042983900654174</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.0145012150868917</v>
-      </c>
+      <c r="E112"/>
+      <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.173715916716294</v>
+        <v>0.000429564891105848</v>
       </c>
       <c r="H112" t="n">
-        <v>0.130015680713026</v>
-      </c>
-      <c r="I112" t="n">
-        <v>99.7525621056108</v>
-      </c>
+        <v>0.014453929976486</v>
+      </c>
+      <c r="I112"/>
       <c r="J112" t="n">
         <v>904</v>
       </c>
@@ -5750,21 +5492,15 @@
       <c r="D113" t="s">
         <v>48</v>
       </c>
-      <c r="E113" t="n">
-        <v>861893.605040586</v>
-      </c>
-      <c r="F113" t="n">
-        <v>49.7583417996184</v>
-      </c>
+      <c r="E113"/>
+      <c r="F113"/>
       <c r="G113" t="n">
-        <v>13543458499145224238680400860686622806280800646222062882668608862624644824002402060446260406822800866626406420420444040804264064828420668242262084040440440440</v>
+        <v>0.328559342634757</v>
       </c>
       <c r="H113" t="n">
-        <v>122404361775533301320082440804666288464884402046880244442066644062020822284068</v>
-      </c>
-      <c r="I113" t="n">
-        <v>100</v>
-      </c>
+        <v>0.572747853933226</v>
+      </c>
+      <c r="I113"/>
       <c r="J113" t="n">
         <v>904</v>
       </c>
@@ -5783,19 +5519,19 @@
         <v>46</v>
       </c>
       <c r="E114" t="n">
-        <v>0.000474841069596145</v>
+        <v>0.000474813210240738</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0158033446461774</v>
+        <v>0.0158034213931333</v>
       </c>
       <c r="G114" t="n">
-        <v>1269699275060422009788228882886</v>
+        <v>0.000432254372596736</v>
       </c>
       <c r="H114" t="n">
-        <v>176798610659430</v>
+        <v>0.014570706438432</v>
       </c>
       <c r="I114" t="n">
-        <v>100</v>
+        <v>-9.84578533892739</v>
       </c>
       <c r="J114" t="n">
         <v>904</v>
@@ -5815,19 +5551,19 @@
         <v>47</v>
       </c>
       <c r="E115" t="n">
-        <v>0.000425595138372357</v>
+        <v>0.000426015483659116</v>
       </c>
       <c r="F115" t="n">
-        <v>0.014374237939056</v>
+        <v>0.0143902783062804</v>
       </c>
       <c r="G115" t="n">
-        <v>0.000428598860635481</v>
+        <v>0.000427138551225284</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0144500733452299</v>
+        <v>0.0144161965338369</v>
       </c>
       <c r="I115" t="n">
-        <v>0.70082366963619</v>
+        <v>0.262928167674439</v>
       </c>
       <c r="J115" t="n">
         <v>904</v>
@@ -5846,21 +5582,15 @@
       <c r="D116" t="s">
         <v>45</v>
       </c>
-      <c r="E116" t="n">
-        <v>0.00264100909534991</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0.039543968831032</v>
-      </c>
+      <c r="E116"/>
+      <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00574199846516128</v>
+        <v>0.00264126842275714</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0548040541278418</v>
-      </c>
-      <c r="I116" t="n">
-        <v>54.0054022763357</v>
-      </c>
+        <v>0.0395253899606345</v>
+      </c>
+      <c r="I116"/>
       <c r="J116" t="n">
         <v>143</v>
       </c>
@@ -5879,19 +5609,19 @@
         <v>46</v>
       </c>
       <c r="E117" t="n">
-        <v>0.00265426336980726</v>
+        <v>0.0026592705188093</v>
       </c>
       <c r="F117" t="n">
-        <v>0.03979370193923</v>
+        <v>0.0398482850501958</v>
       </c>
       <c r="G117" t="n">
-        <v>335241.314716146</v>
+        <v>0.00273546444514271</v>
       </c>
       <c r="H117" t="n">
-        <v>253.63394832117</v>
+        <v>0.0401041405320686</v>
       </c>
       <c r="I117" t="n">
-        <v>99.9999992082529</v>
+        <v>2.78541095530253</v>
       </c>
       <c r="J117" t="n">
         <v>143</v>
@@ -5911,19 +5641,19 @@
         <v>47</v>
       </c>
       <c r="E118" t="n">
-        <v>0.00264653742910922</v>
+        <v>0.0026464465569869</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0395832558915342</v>
+        <v>0.0395419998255718</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00266440647433599</v>
+        <v>0.00266129090458028</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0398249296019305</v>
+        <v>0.0398026822204462</v>
       </c>
       <c r="I118" t="n">
-        <v>0.670657626712882</v>
+        <v>0.557787484556373</v>
       </c>
       <c r="J118" t="n">
         <v>143</v>
@@ -5942,21 +5672,15 @@
       <c r="D119" t="s">
         <v>45</v>
       </c>
-      <c r="E119" t="n">
-        <v>0.00109254338330587</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.0251817429619777</v>
-      </c>
+      <c r="E119"/>
+      <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00137954121846074</v>
+        <v>0.00111985733498714</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0289339747292865</v>
-      </c>
-      <c r="I119" t="n">
-        <v>20.8038608281016</v>
-      </c>
+        <v>0.0256727229218516</v>
+      </c>
+      <c r="I119"/>
       <c r="J119" t="n">
         <v>59</v>
       </c>
@@ -5975,19 +5699,19 @@
         <v>48</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0033324142801694</v>
+        <v>0.00332910450105264</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0495795501894736</v>
-      </c>
-      <c r="G120" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H120" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="I120" t="e">
-        <v>#NUM!</v>
+        <v>0.0495497021961402</v>
+      </c>
+      <c r="G120" t="n">
+        <v>342906794617818002080660646604600242288664084888</v>
+      </c>
+      <c r="H120" t="n">
+        <v>100132562709484509592600</v>
+      </c>
+      <c r="I120" t="n">
+        <v>100</v>
       </c>
       <c r="J120" t="n">
         <v>59</v>
@@ -6007,19 +5731,19 @@
         <v>46</v>
       </c>
       <c r="E121" t="n">
-        <v>0.00109079005040239</v>
+        <v>0.00109181079124808</v>
       </c>
       <c r="F121" t="n">
-        <v>0.025027597860864</v>
+        <v>0.025028505476095</v>
       </c>
       <c r="G121" t="n">
-        <v>38.1771348238671</v>
+        <v>0.00113727899022684</v>
       </c>
       <c r="H121" t="n">
-        <v>2.75179086235585</v>
+        <v>0.0258348123440829</v>
       </c>
       <c r="I121" t="n">
-        <v>99.9971428184555</v>
+        <v>3.99798109078694</v>
       </c>
       <c r="J121" t="n">
         <v>59</v>
@@ -6039,19 +5763,19 @@
         <v>47</v>
       </c>
       <c r="E122" t="n">
-        <v>0.00109497787505133</v>
+        <v>0.00109977537764897</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0251798795846931</v>
+        <v>0.0252160976630994</v>
       </c>
       <c r="G122" t="n">
-        <v>0.00110131294451049</v>
+        <v>0.00109232173280676</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0253913687011055</v>
+        <v>0.0251704909136589</v>
       </c>
       <c r="I122" t="n">
-        <v>0.575228820357692</v>
+        <v>-0.682367165126711</v>
       </c>
       <c r="J122" t="n">
         <v>59</v>
@@ -6070,21 +5794,15 @@
       <c r="D123" t="s">
         <v>45</v>
       </c>
-      <c r="E123" t="n">
-        <v>0.000584890388651837</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.0164159722224607</v>
-      </c>
+      <c r="E123"/>
+      <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.0899802296332344</v>
+        <v>0.000585488887242575</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0815518453341899</v>
-      </c>
-      <c r="I123" t="n">
-        <v>99.3499789997915</v>
-      </c>
+        <v>0.0164735522390298</v>
+      </c>
+      <c r="I123"/>
       <c r="J123" t="n">
         <v>1356</v>
       </c>
@@ -6103,19 +5821,19 @@
         <v>46</v>
       </c>
       <c r="E124" t="n">
-        <v>0.00058686123540664</v>
+        <v>0.000585313350237354</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0164496828267809</v>
+        <v>0.0164419730019161</v>
       </c>
       <c r="G124" t="n">
-        <v>114795639390473819512682440600</v>
+        <v>0.000588949610490605</v>
       </c>
       <c r="H124" t="n">
-        <v>88253646804332.2</v>
+        <v>0.0167378686106602</v>
       </c>
       <c r="I124" t="n">
-        <v>100</v>
+        <v>0.617414493274196</v>
       </c>
       <c r="J124" t="n">
         <v>1356</v>
@@ -6135,19 +5853,19 @@
         <v>47</v>
       </c>
       <c r="E125" t="n">
-        <v>0.000580794092966429</v>
+        <v>0.000581445273653902</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0163908667506472</v>
+        <v>0.0163745350032451</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000582134170835339</v>
+        <v>0.000581359506168332</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0163813312438403</v>
+        <v>0.0163868910364891</v>
       </c>
       <c r="I125" t="n">
-        <v>0.23020086022223</v>
+        <v>-0.0147529170263696</v>
       </c>
       <c r="J125" t="n">
         <v>1356</v>
@@ -6166,21 +5884,15 @@
       <c r="D126" t="s">
         <v>45</v>
       </c>
-      <c r="E126" t="n">
-        <v>0.000702770158500836</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0.0165672406145152</v>
-      </c>
+      <c r="E126"/>
+      <c r="F126"/>
       <c r="G126" t="n">
-        <v>1.45368439778653</v>
+        <v>0.000700504900862355</v>
       </c>
       <c r="H126" t="n">
-        <v>0.32563833453619</v>
-      </c>
-      <c r="I126" t="n">
-        <v>99.9516559330505</v>
-      </c>
+        <v>0.0166025938357234</v>
+      </c>
+      <c r="I126"/>
       <c r="J126" t="n">
         <v>1356</v>
       </c>
@@ -6199,19 +5911,19 @@
         <v>46</v>
       </c>
       <c r="E127" t="n">
-        <v>0.000704167769198529</v>
+        <v>0.000704698971453386</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0165915862716347</v>
+        <v>0.016591874352728</v>
       </c>
       <c r="G127" t="n">
-        <v>2287091785802414670820044226</v>
+        <v>0.000716709589219563</v>
       </c>
       <c r="H127" t="n">
-        <v>12813265000812.2</v>
+        <v>0.016865755957937</v>
       </c>
       <c r="I127" t="n">
-        <v>100</v>
+        <v>1.67579978652937</v>
       </c>
       <c r="J127" t="n">
         <v>1356</v>
@@ -6231,19 +5943,19 @@
         <v>47</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000698653502862149</v>
+        <v>0.000699916193999837</v>
       </c>
       <c r="F128" t="n">
-        <v>0.016509070825696</v>
+        <v>0.0165059890174882</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000701151689077348</v>
+        <v>0.000702378528375307</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0165616799806974</v>
+        <v>0.0165599924985474</v>
       </c>
       <c r="I128" t="n">
-        <v>0.356297539336568</v>
+        <v>0.350570849761879</v>
       </c>
       <c r="J128" t="n">
         <v>1356</v>
@@ -6262,21 +5974,15 @@
       <c r="D129" t="s">
         <v>45</v>
       </c>
-      <c r="E129" t="n">
-        <v>0.00051611964022504</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.0161712808536966</v>
-      </c>
+      <c r="E129"/>
+      <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.188159849984457</v>
+        <v>0.000514549259316455</v>
       </c>
       <c r="H129" t="n">
-        <v>0.125803072521358</v>
-      </c>
-      <c r="I129" t="n">
-        <v>99.7257015031274</v>
-      </c>
+        <v>0.0162028969836989</v>
+      </c>
+      <c r="I129"/>
       <c r="J129" t="n">
         <v>1356</v>
       </c>
@@ -6295,19 +6001,19 @@
         <v>46</v>
       </c>
       <c r="E130" t="n">
-        <v>0.000518224079072012</v>
+        <v>0.000518108683502463</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0162278462992002</v>
+        <v>0.0162262316063826</v>
       </c>
       <c r="G130" t="n">
-        <v>3611279088162450896840248488</v>
+        <v>0.000525793142855905</v>
       </c>
       <c r="H130" t="n">
-        <v>9285196149815.07</v>
+        <v>0.0163912267618802</v>
       </c>
       <c r="I130" t="n">
-        <v>100</v>
+        <v>1.4614985870115</v>
       </c>
       <c r="J130" t="n">
         <v>1356</v>
@@ -6327,19 +6033,19 @@
         <v>47</v>
       </c>
       <c r="E131" t="n">
-        <v>0.000514774311335651</v>
+        <v>0.000513988241218007</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0161765616308586</v>
+        <v>0.0161461767157171</v>
       </c>
       <c r="G131" t="n">
-        <v>0.000515329870477427</v>
+        <v>0.000514259196702202</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0161704093524285</v>
+        <v>0.0161596142359956</v>
       </c>
       <c r="I131" t="n">
-        <v>0.107806508724465</v>
+        <v>0.0526885053164181</v>
       </c>
       <c r="J131" t="n">
         <v>1356</v>
@@ -6358,21 +6064,15 @@
       <c r="D132" t="s">
         <v>45</v>
       </c>
-      <c r="E132" t="n">
-        <v>0.000516257903246968</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.0161829799181657</v>
-      </c>
+      <c r="E132"/>
+      <c r="F132"/>
       <c r="G132" t="n">
-        <v>2.81294250975771</v>
+        <v>0.000521946388799734</v>
       </c>
       <c r="H132" t="n">
-        <v>0.381154742877235</v>
-      </c>
-      <c r="I132" t="n">
-        <v>99.9816470510344</v>
-      </c>
+        <v>0.0163859969308797</v>
+      </c>
+      <c r="I132"/>
       <c r="J132" t="n">
         <v>1356</v>
       </c>
@@ -6391,19 +6091,19 @@
         <v>46</v>
       </c>
       <c r="E133" t="n">
-        <v>0.000518211563612468</v>
+        <v>0.000518086500206077</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0162294617466609</v>
+        <v>0.0162269488002475</v>
       </c>
       <c r="G133" t="n">
-        <v>9709264699689948861806026</v>
+        <v>0.00053046317074484</v>
       </c>
       <c r="H133" t="n">
-        <v>853133628221.636</v>
+        <v>0.0164579027874972</v>
       </c>
       <c r="I133" t="n">
-        <v>100</v>
+        <v>2.33318187224656</v>
       </c>
       <c r="J133" t="n">
         <v>1356</v>
@@ -6423,19 +6123,19 @@
         <v>47</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000514380004990233</v>
+        <v>0.000513640506177613</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0161483359148394</v>
+        <v>0.0161505511777862</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000515076463171466</v>
+        <v>0.000517719971961258</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0161796361912256</v>
+        <v>0.0162272017515998</v>
       </c>
       <c r="I134" t="n">
-        <v>0.135214522703015</v>
+        <v>0.787967628173823</v>
       </c>
       <c r="J134" t="n">
         <v>1356</v>
@@ -6454,21 +6154,15 @@
       <c r="D135" t="s">
         <v>45</v>
       </c>
-      <c r="E135" t="n">
-        <v>0.00048217775559389</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0.0161317617890898</v>
-      </c>
+      <c r="E135"/>
+      <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.201609693366624</v>
+        <v>0.000491732144230916</v>
       </c>
       <c r="H135" t="n">
-        <v>0.135172981048068</v>
-      </c>
-      <c r="I135" t="n">
-        <v>99.7608360255193</v>
-      </c>
+        <v>0.0163977769857078</v>
+      </c>
+      <c r="I135"/>
       <c r="J135" t="n">
         <v>904</v>
       </c>
@@ -6487,19 +6181,19 @@
         <v>46</v>
       </c>
       <c r="E136" t="n">
-        <v>0.000490915983527293</v>
+        <v>0.000490888810518666</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0163565847599263</v>
+        <v>0.0163548668221353</v>
       </c>
       <c r="G136" t="n">
-        <v>47959938651757136</v>
+        <v>0.000504813932367682</v>
       </c>
       <c r="H136" t="n">
-        <v>80311395.1988989</v>
+        <v>0.0166046727409572</v>
       </c>
       <c r="I136" t="n">
-        <v>100</v>
+        <v>2.75846623006307</v>
       </c>
       <c r="J136" t="n">
         <v>904</v>
@@ -6519,19 +6213,19 @@
         <v>47</v>
       </c>
       <c r="E137" t="n">
-        <v>0.000481860985723337</v>
+        <v>0.000480183954863576</v>
       </c>
       <c r="F137" t="n">
-        <v>0.016085970191462</v>
+        <v>0.0160684430286059</v>
       </c>
       <c r="G137" t="n">
-        <v>0.000636602152815492</v>
+        <v>0.000487903880149774</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0181907760742858</v>
+        <v>0.0162526586614581</v>
       </c>
       <c r="I137" t="n">
-        <v>24.3073584353718</v>
+        <v>1.58226355646694</v>
       </c>
       <c r="J137" t="n">
         <v>904</v>
@@ -6579,13 +6273,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00119395385892208</v>
+        <v>0.00119556223978742</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0279104997224</v>
+        <v>0.00120680961207404</v>
       </c>
       <c r="F2" t="n">
-        <v>99.3610583568221</v>
+        <v>0.685112635897545</v>
       </c>
     </row>
     <row r="3">
@@ -6599,10 +6293,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5137512462205652413888644088246426842648628468268202486068884406</v>
-      </c>
-      <c r="E3" t="e">
-        <v>#NUM!</v>
+        <v>0.00332910450105264</v>
+      </c>
+      <c r="E3" t="n">
+        <v>85726698654454500520440464406400868822446026222</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -6619,13 +6313,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00119644730129442</v>
+        <v>0.00119762233752751</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119708504868889</v>
+        <v>0.00119501071797452</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3403461809327</v>
+        <v>0.052646837334809</v>
       </c>
     </row>
     <row r="5">
@@ -6638,14 +6332,14 @@
       <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.00119376692844099</v>
+      <c r="D5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.108031573032016</v>
-      </c>
-      <c r="F5" t="n">
-        <v>60.5407184114848</v>
+        <v>0.00119284710829966</v>
+      </c>
+      <c r="F5" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="6">
@@ -6659,13 +6353,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00147405270310906</v>
+        <v>0.0014742033444272</v>
       </c>
       <c r="E6" t="n">
-        <v>160422.747060652</v>
+        <v>0.00147776907553582</v>
       </c>
       <c r="F6" t="n">
-        <v>99.9998452663547</v>
+        <v>-0.155587249754524</v>
       </c>
     </row>
     <row r="7">
@@ -6679,13 +6373,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00146729714817831</v>
+        <v>0.00146751455615093</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00148426686137706</v>
+        <v>0.00147079203351927</v>
       </c>
       <c r="F7" t="n">
-        <v>3.77446710971993</v>
+        <v>0.108445079965545</v>
       </c>
     </row>
     <row r="8">
@@ -6698,14 +6392,14 @@
       <c r="C8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.00146862951716468</v>
+      <c r="D8" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.104920583866912</v>
-      </c>
-      <c r="F8" t="n">
-        <v>78.642429356037</v>
+        <v>0.00146569157390207</v>
+      </c>
+      <c r="F8" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="9">
@@ -6719,13 +6413,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000420991993733629</v>
+        <v>0.00042095541324188</v>
       </c>
       <c r="E9" t="n">
-        <v>211616550355743410346440804604</v>
+        <v>0.000407698508048248</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>-4.23078237582793</v>
       </c>
     </row>
     <row r="10">
@@ -6738,14 +6432,14 @@
       <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>430946.80260661</v>
-      </c>
-      <c r="E10" t="e">
+      <c r="D10" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F10" t="n">
-        <v>100</v>
+      <c r="E10" t="n">
+        <v>0.164339073003758</v>
+      </c>
+      <c r="F10" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="11">
@@ -6759,13 +6453,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000403251626771012</v>
+        <v>0.000403106348742532</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000554839743929818</v>
+        <v>0.000406376544490023</v>
       </c>
       <c r="F11" t="n">
-        <v>24.670980527612</v>
+        <v>0.567394208151442</v>
       </c>
     </row>
     <row r="12">
@@ -6778,14 +6472,14 @@
       <c r="C12" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.00040546097638623</v>
+      <c r="D12" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.105460025525905</v>
-      </c>
-      <c r="F12" t="n">
-        <v>98.78127420846</v>
+        <v>0.000409472330235699</v>
+      </c>
+      <c r="F12" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="13">
@@ -6799,13 +6493,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000442071890677071</v>
+        <v>0.000441905839452987</v>
       </c>
       <c r="E13" t="n">
-        <v>87626812845620546344446028886</v>
+        <v>0.000446042064117247</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>0.432643079956433</v>
       </c>
     </row>
     <row r="14">
@@ -6818,14 +6512,14 @@
       <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.00126981598313535</v>
+      <c r="D14" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>3891958770768186368</v>
-      </c>
-      <c r="F14" t="n">
-        <v>100</v>
+        <v>0.00132600454120009</v>
+      </c>
+      <c r="F14" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="15">
@@ -6839,13 +6533,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000440564090434484</v>
+        <v>0.00044129045142661</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000455720375049133</v>
+        <v>0.000442031267032378</v>
       </c>
       <c r="F15" t="n">
-        <v>9.04164133023891</v>
+        <v>0.135986474403759</v>
       </c>
     </row>
     <row r="16">
@@ -6858,14 +6552,14 @@
       <c r="C16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.000441294156637787</v>
+      <c r="D16" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>5.68462235940287</v>
-      </c>
-      <c r="F16" t="n">
-        <v>99.7841900781019</v>
+        <v>0.000442436977550397</v>
+      </c>
+      <c r="F16" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="17">
@@ -6879,13 +6573,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000562759995333404</v>
+        <v>0.000563098945909384</v>
       </c>
       <c r="E17" t="n">
-        <v>6230509742627524840868808024046</v>
+        <v>0.000568533950717073</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>0.456474441609512</v>
       </c>
     </row>
     <row r="18">
@@ -6898,14 +6592,14 @@
       <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.00139629764952591</v>
+      <c r="D18" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>15367693778721796096</v>
-      </c>
-      <c r="F18" t="n">
-        <v>100</v>
+        <v>0.00145079580549807</v>
+      </c>
+      <c r="F18" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="19">
@@ -6919,13 +6613,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000561972197477516</v>
+        <v>0.000561917478898573</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000603969296666689</v>
+        <v>0.000563450525140565</v>
       </c>
       <c r="F19" t="n">
-        <v>11.4111285028998</v>
+        <v>0.274215021822413</v>
       </c>
     </row>
     <row r="20">
@@ -6938,14 +6632,14 @@
       <c r="C20" t="n">
         <v>6</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.000562120307593838</v>
+      <c r="D20" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>7.81659012877052</v>
-      </c>
-      <c r="F20" t="n">
-        <v>99.8756277158341</v>
+        <v>0.000561840568831668</v>
+      </c>
+      <c r="F20" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="21">
@@ -6959,13 +6653,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000371568089697812</v>
+        <v>0.000371571206096653</v>
       </c>
       <c r="E21" t="n">
-        <v>4687100614077496512422062024</v>
+        <v>0.000377091572678539</v>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>1.34180659322998</v>
       </c>
     </row>
     <row r="22">
@@ -6978,14 +6672,14 @@
       <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.00118824749843996</v>
+      <c r="D22" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>14935385816631754752</v>
-      </c>
-      <c r="F22" t="n">
-        <v>100</v>
+        <v>0.00122942243707141</v>
+      </c>
+      <c r="F22" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="23">
@@ -6999,13 +6693,13 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000371201337542346</v>
+        <v>0.000371113607550136</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000391452009893379</v>
+        <v>0.000370392713111957</v>
       </c>
       <c r="F23" t="n">
-        <v>19.518673196034</v>
+        <v>0.113237092843555</v>
       </c>
     </row>
     <row r="24">
@@ -7018,14 +6712,14 @@
       <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.000371132270925534</v>
+      <c r="D24" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.305659771584419</v>
-      </c>
-      <c r="F24" t="n">
-        <v>99.7813280292653</v>
+        <v>0.000371544214678696</v>
+      </c>
+      <c r="F24" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="25">
@@ -7039,13 +6733,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000372499585946023</v>
+        <v>0.000372483385703722</v>
       </c>
       <c r="E25" t="n">
-        <v>6182205899818243228462262084622</v>
+        <v>0.000377990560641479</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>1.07154640145775</v>
       </c>
     </row>
     <row r="26">
@@ -7058,14 +6752,14 @@
       <c r="C26" t="n">
         <v>1</v>
       </c>
-      <c r="D26" t="n">
-        <v>0.00119220020257798</v>
+      <c r="D26" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>753935276335988352</v>
-      </c>
-      <c r="F26" t="n">
-        <v>100</v>
+        <v>0.0012256506558025</v>
+      </c>
+      <c r="F26" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="27">
@@ -7079,13 +6773,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000372103386921139</v>
+        <v>0.000372217020418958</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000380840300843061</v>
+        <v>0.00037232606276023</v>
       </c>
       <c r="F27" t="n">
-        <v>13.1570050015894</v>
+        <v>0.280734174600822</v>
       </c>
     </row>
     <row r="28">
@@ -7098,14 +6792,14 @@
       <c r="C28" t="n">
         <v>6</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.000372376269786734</v>
+      <c r="D28" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>238.580661407815</v>
-      </c>
-      <c r="F28" t="n">
-        <v>99.9790192445893</v>
+        <v>0.000373635714051074</v>
+      </c>
+      <c r="F28" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
